--- a/Omakase_Ratings.xlsx
+++ b/Omakase_Ratings.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P189"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -587,13 +587,13 @@
         <v>4.107</v>
       </c>
       <c r="L2" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="M2" t="n">
         <v>4.061</v>
       </c>
       <c r="N2" t="n">
-        <v>30.8</v>
+        <v>29.3</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -639,13 +639,13 @@
         <v>3.545</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>3.563</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -691,13 +691,13 @@
         <v>4.143</v>
       </c>
       <c r="L4" t="n">
-        <v>40.1</v>
+        <v>39</v>
       </c>
       <c r="M4" t="n">
         <v>4.143</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>37.9</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -739,13 +739,13 @@
         <v>3.86</v>
       </c>
       <c r="L5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
         <v>3.88</v>
       </c>
       <c r="N5" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -787,13 +787,13 @@
         <v>3.958</v>
       </c>
       <c r="L6" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="M6" t="n">
         <v>3.886</v>
       </c>
       <c r="N6" t="n">
-        <v>21.1</v>
+        <v>20.2</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -835,13 +835,13 @@
         <v>4.324</v>
       </c>
       <c r="L7" t="n">
-        <v>74.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="M7" t="n">
         <v>4.152</v>
       </c>
       <c r="N7" t="n">
-        <v>40.5</v>
+        <v>38.4</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -887,13 +887,13 @@
         <v>4.25</v>
       </c>
       <c r="L8" t="n">
-        <v>53.5</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
         <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>59.5</v>
+        <v>57.1</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -939,13 +939,13 @@
         <v>4.234</v>
       </c>
       <c r="L9" t="n">
-        <v>51.3</v>
+        <v>50</v>
       </c>
       <c r="M9" t="n">
         <v>4.776</v>
       </c>
       <c r="N9" t="n">
-        <v>98.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1013,13 +1013,13 @@
         <v>3.865</v>
       </c>
       <c r="L11" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>3.957</v>
       </c>
       <c r="N11" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1061,13 +1061,13 @@
         <v>4.389</v>
       </c>
       <c r="L12" t="n">
-        <v>85.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="M12" t="n">
         <v>4.445</v>
       </c>
       <c r="N12" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1113,13 +1113,13 @@
         <v>4.33</v>
       </c>
       <c r="L13" t="n">
-        <v>76.5</v>
+        <v>74</v>
       </c>
       <c r="M13" t="n">
         <v>4.309</v>
       </c>
       <c r="N13" t="n">
-        <v>60</v>
+        <v>57.6</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1165,13 +1165,13 @@
         <v>4.296</v>
       </c>
       <c r="L14" t="n">
-        <v>68.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="M14" t="n">
         <v>4.465</v>
       </c>
       <c r="N14" t="n">
-        <v>80.5</v>
+        <v>76.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1217,13 +1217,13 @@
         <v>4.078</v>
       </c>
       <c r="L15" t="n">
-        <v>28.9</v>
+        <v>28.5</v>
       </c>
       <c r="M15" t="n">
         <v>4.078</v>
       </c>
       <c r="N15" t="n">
-        <v>33</v>
+        <v>31.3</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1269,13 +1269,13 @@
         <v>4.336</v>
       </c>
       <c r="L16" t="n">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="M16" t="n">
         <v>4.276</v>
       </c>
       <c r="N16" t="n">
-        <v>56.8</v>
+        <v>54.5</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1317,13 +1317,13 @@
         <v>4.042</v>
       </c>
       <c r="L17" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="M17" t="n">
         <v>4.201</v>
       </c>
       <c r="N17" t="n">
-        <v>47</v>
+        <v>44.9</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -1369,13 +1369,13 @@
         <v>4.092</v>
       </c>
       <c r="L18" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="M18" t="n">
         <v>3.881</v>
       </c>
       <c r="N18" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1417,13 +1417,13 @@
         <v>4.252</v>
       </c>
       <c r="L19" t="n">
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="M19" t="n">
         <v>4.212</v>
       </c>
       <c r="N19" t="n">
-        <v>48.1</v>
+        <v>46.5</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1469,13 +1469,13 @@
         <v>3.985</v>
       </c>
       <c r="L20" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="M20" t="n">
         <v>3.827</v>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1521,13 +1521,13 @@
         <v>4.387</v>
       </c>
       <c r="L21" t="n">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="M21" t="n">
         <v>4.649</v>
       </c>
       <c r="N21" t="n">
-        <v>95.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1565,13 +1565,13 @@
         <v>4.095</v>
       </c>
       <c r="L22" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="M22" t="n">
         <v>4.116</v>
       </c>
       <c r="N22" t="n">
-        <v>36.8</v>
+        <v>34.8</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -1617,13 +1617,13 @@
         <v>4.544</v>
       </c>
       <c r="L23" t="n">
-        <v>95.7</v>
+        <v>95</v>
       </c>
       <c r="M23" t="n">
         <v>4.509</v>
       </c>
       <c r="N23" t="n">
-        <v>85.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -1669,13 +1669,13 @@
         <v>4.142</v>
       </c>
       <c r="L24" t="n">
-        <v>39.6</v>
+        <v>38.5</v>
       </c>
       <c r="M24" t="n">
         <v>4.142</v>
       </c>
       <c r="N24" t="n">
-        <v>39.5</v>
+        <v>37.4</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -1721,13 +1721,13 @@
         <v>4.636</v>
       </c>
       <c r="L25" t="n">
-        <v>97.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="M25" t="n">
         <v>4.69</v>
       </c>
       <c r="N25" t="n">
-        <v>97.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -1779,7 +1779,7 @@
         <v>4.045</v>
       </c>
       <c r="N26" t="n">
-        <v>29.7</v>
+        <v>28.3</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -1825,13 +1825,13 @@
         <v>4.494</v>
       </c>
       <c r="L27" t="n">
-        <v>94.7</v>
+        <v>94</v>
       </c>
       <c r="M27" t="n">
         <v>4.378</v>
       </c>
       <c r="N27" t="n">
-        <v>68.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -1877,13 +1877,13 @@
         <v>3.982</v>
       </c>
       <c r="L28" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="M28" t="n">
         <v>4.191</v>
       </c>
       <c r="N28" t="n">
-        <v>45.4</v>
+        <v>43.4</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -1929,13 +1929,13 @@
         <v>4.219</v>
       </c>
       <c r="L29" t="n">
-        <v>49.2</v>
+        <v>48</v>
       </c>
       <c r="M29" t="n">
         <v>4.54</v>
       </c>
       <c r="N29" t="n">
-        <v>87.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -1977,13 +1977,13 @@
         <v>3.982</v>
       </c>
       <c r="L30" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="M30" t="n">
         <v>4.212</v>
       </c>
       <c r="N30" t="n">
-        <v>48.1</v>
+        <v>46.5</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -2029,13 +2029,13 @@
         <v>4.368</v>
       </c>
       <c r="L31" t="n">
-        <v>82.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="M31" t="n">
         <v>4.39</v>
       </c>
       <c r="N31" t="n">
-        <v>69.2</v>
+        <v>66.2</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -2081,13 +2081,13 @@
         <v>4.242</v>
       </c>
       <c r="L32" t="n">
-        <v>52.9</v>
+        <v>51.5</v>
       </c>
       <c r="M32" t="n">
         <v>4.479</v>
       </c>
       <c r="N32" t="n">
-        <v>81.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -2129,13 +2129,13 @@
         <v>4.554</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>96.3</v>
+        <v>95.5</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>4.607</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>93</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>3.871</v>
       </c>
       <c r="L34" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -2220,13 +2220,13 @@
         <v>4.238</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>51.9</v>
+        <v>50.5</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>4.398</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>70.8</v>
+        <v>67.7</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         <v>4.47</v>
       </c>
       <c r="L36" t="n">
-        <v>92.5</v>
+        <v>91</v>
       </c>
       <c r="M36" t="n">
         <v>4.543</v>
       </c>
       <c r="N36" t="n">
-        <v>88.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -2328,13 +2328,13 @@
         <v>4.284</v>
       </c>
       <c r="L37" t="n">
-        <v>65.2</v>
+        <v>63</v>
       </c>
       <c r="M37" t="n">
         <v>4.114</v>
       </c>
       <c r="N37" t="n">
-        <v>36.2</v>
+        <v>34.3</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -2377,7 +2377,7 @@
         <v>3.48</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -2423,13 +2423,13 @@
         <v>4.149</v>
       </c>
       <c r="L39" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="M39" t="n">
         <v>4.785</v>
       </c>
       <c r="N39" t="n">
-        <v>99.5</v>
+        <v>97.5</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -2475,13 +2475,13 @@
         <v>3.865</v>
       </c>
       <c r="L40" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
         <v>3.881</v>
       </c>
       <c r="N40" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -2527,13 +2527,13 @@
         <v>4.261</v>
       </c>
       <c r="L41" t="n">
-        <v>56.1</v>
+        <v>54.5</v>
       </c>
       <c r="M41" t="n">
         <v>4.316</v>
       </c>
       <c r="N41" t="n">
-        <v>61.6</v>
+        <v>59.1</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -2579,13 +2579,13 @@
         <v>3.951</v>
       </c>
       <c r="L42" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="M42" t="n">
         <v>3.951</v>
       </c>
       <c r="N42" t="n">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -2627,13 +2627,13 @@
         <v>4.167</v>
       </c>
       <c r="L43" t="n">
-        <v>42.8</v>
+        <v>41.5</v>
       </c>
       <c r="M43" t="n">
         <v>4.188</v>
       </c>
       <c r="N43" t="n">
-        <v>44.3</v>
+        <v>42.4</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -2685,7 +2685,7 @@
         <v>4.732</v>
       </c>
       <c r="N44" t="n">
-        <v>97.8</v>
+        <v>96</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -2727,13 +2727,13 @@
         <v>3.869</v>
       </c>
       <c r="L45" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="M45" t="n">
         <v>3.889</v>
       </c>
       <c r="N45" t="n">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -2779,13 +2779,13 @@
         <v>3.913</v>
       </c>
       <c r="L46" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="M46" t="n">
         <v>4.027</v>
       </c>
       <c r="N46" t="n">
-        <v>28.6</v>
+        <v>27.3</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -2831,13 +2831,13 @@
         <v>3.652</v>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="M47" t="n">
         <v>3.843</v>
       </c>
       <c r="N47" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
@@ -2879,13 +2879,13 @@
         <v>4.141</v>
       </c>
       <c r="L48" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
         <v>4.245</v>
       </c>
       <c r="N48" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -2931,13 +2931,13 @@
         <v>4.583</v>
       </c>
       <c r="L49" t="n">
-        <v>96.8</v>
+        <v>96</v>
       </c>
       <c r="M49" t="n">
         <v>4.756</v>
       </c>
       <c r="N49" t="n">
-        <v>98.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -2983,13 +2983,13 @@
         <v>3.817</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>3.825</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3039,13 +3039,13 @@
         <v>4.122</v>
       </c>
       <c r="L51" t="n">
-        <v>35.8</v>
+        <v>35</v>
       </c>
       <c r="M51" t="n">
         <v>4.237</v>
       </c>
       <c r="N51" t="n">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -3091,13 +3091,13 @@
         <v>4.273</v>
       </c>
       <c r="L52" t="n">
-        <v>61.5</v>
+        <v>59.5</v>
       </c>
       <c r="M52" t="n">
         <v>4.461</v>
       </c>
       <c r="N52" t="n">
-        <v>79.5</v>
+        <v>75.8</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -3143,13 +3143,13 @@
         <v>4.345</v>
       </c>
       <c r="L53" t="n">
-        <v>78.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="M53" t="n">
         <v>4.509</v>
       </c>
       <c r="N53" t="n">
-        <v>85.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -3195,13 +3195,13 @@
         <v>3.872</v>
       </c>
       <c r="L54" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="M54" t="n">
         <v>3.88</v>
       </c>
       <c r="N54" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -3247,13 +3247,13 @@
         <v>3.937</v>
       </c>
       <c r="L55" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="M55" t="n">
         <v>3.866</v>
       </c>
       <c r="N55" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -3299,13 +3299,13 @@
         <v>4.29</v>
       </c>
       <c r="L56" t="n">
-        <v>67.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="M56" t="n">
         <v>4.415</v>
       </c>
       <c r="N56" t="n">
-        <v>74.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -3351,13 +3351,13 @@
         <v>4.143</v>
       </c>
       <c r="L57" t="n">
-        <v>40.1</v>
+        <v>39</v>
       </c>
       <c r="M57" t="n">
         <v>4.068</v>
       </c>
       <c r="N57" t="n">
-        <v>31.9</v>
+        <v>30.3</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -3399,13 +3399,13 @@
         <v>4.316</v>
       </c>
       <c r="L58" t="n">
-        <v>73.8</v>
+        <v>71.5</v>
       </c>
       <c r="M58" t="n">
         <v>4.442</v>
       </c>
       <c r="N58" t="n">
-        <v>76.8</v>
+        <v>73.2</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -3451,13 +3451,13 @@
         <v>3.801</v>
       </c>
       <c r="L59" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="M59" t="n">
         <v>3.555</v>
       </c>
       <c r="N59" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -3503,13 +3503,13 @@
         <v>4.424</v>
       </c>
       <c r="L60" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="M60" t="n">
         <v>4.553</v>
       </c>
       <c r="N60" t="n">
-        <v>89.2</v>
+        <v>84.8</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -3555,13 +3555,13 @@
         <v>4.647</v>
       </c>
       <c r="L61" t="n">
-        <v>98.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="M61" t="n">
         <v>4.611</v>
       </c>
       <c r="N61" t="n">
-        <v>94.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -3607,13 +3607,13 @@
         <v>3.782</v>
       </c>
       <c r="L62" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="M62" t="n">
         <v>3.73</v>
       </c>
       <c r="N62" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -3659,13 +3659,13 @@
         <v>4.138</v>
       </c>
       <c r="L63" t="n">
-        <v>37.4</v>
+        <v>36.5</v>
       </c>
       <c r="M63" t="n">
         <v>3.913</v>
       </c>
       <c r="N63" t="n">
-        <v>22.7</v>
+        <v>21.7</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -3711,13 +3711,13 @@
         <v>4.084</v>
       </c>
       <c r="L64" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="M64" t="n">
         <v>4.377</v>
       </c>
       <c r="N64" t="n">
-        <v>67.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -3759,13 +3759,13 @@
         <v>4.397</v>
       </c>
       <c r="L65" t="n">
-        <v>86.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="M65" t="n">
         <v>4.359</v>
       </c>
       <c r="N65" t="n">
-        <v>65.90000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -3811,13 +3811,13 @@
         <v>4.067</v>
       </c>
       <c r="L66" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="M66" t="n">
         <v>4.186</v>
       </c>
       <c r="N66" t="n">
-        <v>43.8</v>
+        <v>41.9</v>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -3863,13 +3863,13 @@
         <v>4.168</v>
       </c>
       <c r="L67" t="n">
-        <v>43.3</v>
+        <v>42</v>
       </c>
       <c r="M67" t="n">
         <v>4.189</v>
       </c>
       <c r="N67" t="n">
-        <v>44.9</v>
+        <v>42.9</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -3915,13 +3915,13 @@
         <v>4.328</v>
       </c>
       <c r="L68" t="n">
-        <v>75.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="M68" t="n">
         <v>4.498</v>
       </c>
       <c r="N68" t="n">
-        <v>84.3</v>
+        <v>80.3</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -3963,13 +3963,13 @@
         <v>4.25</v>
       </c>
       <c r="L69" t="n">
-        <v>53.5</v>
+        <v>52</v>
       </c>
       <c r="M69" t="n">
         <v>4.272</v>
       </c>
       <c r="N69" t="n">
-        <v>55.7</v>
+        <v>53.5</v>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -4011,13 +4011,13 @@
         <v>4.222</v>
       </c>
       <c r="L70" t="n">
-        <v>49.7</v>
+        <v>48.5</v>
       </c>
       <c r="M70" t="n">
         <v>4.375</v>
       </c>
       <c r="N70" t="n">
-        <v>67</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -4063,13 +4063,13 @@
         <v>4.403</v>
       </c>
       <c r="L71" t="n">
-        <v>87.2</v>
+        <v>85</v>
       </c>
       <c r="M71" t="n">
         <v>4.412</v>
       </c>
       <c r="N71" t="n">
-        <v>74.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -4115,13 +4115,13 @@
         <v>4.229</v>
       </c>
       <c r="L72" t="n">
-        <v>50.8</v>
+        <v>49.5</v>
       </c>
       <c r="M72" t="n">
         <v>4.035</v>
       </c>
       <c r="N72" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -4167,13 +4167,13 @@
         <v>3.884</v>
       </c>
       <c r="L73" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="M73" t="n">
         <v>4.101</v>
       </c>
       <c r="N73" t="n">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -4219,13 +4219,13 @@
         <v>4.309</v>
       </c>
       <c r="L74" t="n">
-        <v>71.7</v>
+        <v>69.5</v>
       </c>
       <c r="M74" t="n">
         <v>4.313</v>
       </c>
       <c r="N74" t="n">
-        <v>61.1</v>
+        <v>58.6</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -4271,13 +4271,13 @@
         <v>4.357</v>
       </c>
       <c r="L75" t="n">
-        <v>80.7</v>
+        <v>78</v>
       </c>
       <c r="M75" t="n">
         <v>4.408</v>
       </c>
       <c r="N75" t="n">
-        <v>73</v>
+        <v>69.7</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -4319,13 +4319,13 @@
         <v>4.114</v>
       </c>
       <c r="L76" t="n">
-        <v>34.2</v>
+        <v>33.5</v>
       </c>
       <c r="M76" t="n">
         <v>4.217</v>
       </c>
       <c r="N76" t="n">
-        <v>49.2</v>
+        <v>47.5</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -4371,13 +4371,13 @@
         <v>4.14</v>
       </c>
       <c r="L77" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M77" t="n">
         <v>3.525</v>
       </c>
       <c r="N77" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -4419,13 +4419,13 @@
         <v>4.454</v>
       </c>
       <c r="L78" t="n">
-        <v>91.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="M78" t="n">
         <v>4.506</v>
       </c>
       <c r="N78" t="n">
-        <v>84.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -4471,13 +4471,13 @@
         <v>4.277</v>
       </c>
       <c r="L79" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="M79" t="n">
         <v>4.299</v>
       </c>
       <c r="N79" t="n">
-        <v>58.9</v>
+        <v>56.6</v>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -4523,13 +4523,13 @@
         <v>4.188</v>
       </c>
       <c r="L80" t="n">
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
       <c r="M80" t="n">
         <v>4.022</v>
       </c>
       <c r="N80" t="n">
-        <v>28.1</v>
+        <v>26.8</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -4575,13 +4575,13 @@
         <v>4.021</v>
       </c>
       <c r="L81" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="M81" t="n">
         <v>4.064</v>
       </c>
       <c r="N81" t="n">
-        <v>31.4</v>
+        <v>29.8</v>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -4627,13 +4627,13 @@
         <v>4.352</v>
       </c>
       <c r="L82" t="n">
-        <v>79.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="M82" t="n">
         <v>4.223</v>
       </c>
       <c r="N82" t="n">
-        <v>50.3</v>
+        <v>48.5</v>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -4679,13 +4679,13 @@
         <v>4.156</v>
       </c>
       <c r="L83" t="n">
-        <v>42.2</v>
+        <v>41</v>
       </c>
       <c r="M83" t="n">
         <v>3.991</v>
       </c>
       <c r="N83" t="n">
-        <v>26.5</v>
+        <v>25.3</v>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -4737,7 +4737,7 @@
         <v>4.488</v>
       </c>
       <c r="N84" t="n">
-        <v>83.2</v>
+        <v>79.3</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -4783,13 +4783,13 @@
         <v>4.289</v>
       </c>
       <c r="L85" t="n">
-        <v>66.8</v>
+        <v>64.5</v>
       </c>
       <c r="M85" t="n">
         <v>4.256</v>
       </c>
       <c r="N85" t="n">
-        <v>54.1</v>
+        <v>52</v>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -4835,13 +4835,13 @@
         <v>4.197</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>46.5</v>
+        <v>45.5</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>4.382</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -4891,13 +4891,13 @@
         <v>4.353</v>
       </c>
       <c r="L87" t="n">
-        <v>79.7</v>
+        <v>77</v>
       </c>
       <c r="M87" t="n">
         <v>4.48</v>
       </c>
       <c r="N87" t="n">
-        <v>82.2</v>
+        <v>78.3</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -4943,13 +4943,13 @@
         <v>4.298</v>
       </c>
       <c r="L88" t="n">
-        <v>70.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="M88" t="n">
         <v>4.127</v>
       </c>
       <c r="N88" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -4995,13 +4995,13 @@
         <v>4.207</v>
       </c>
       <c r="L89" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="M89" t="n">
         <v>4.252</v>
       </c>
       <c r="N89" t="n">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
@@ -5047,13 +5047,13 @@
         <v>4.519</v>
       </c>
       <c r="L90" t="n">
-        <v>95.2</v>
+        <v>94.5</v>
       </c>
       <c r="M90" t="n">
         <v>4.405</v>
       </c>
       <c r="N90" t="n">
-        <v>71.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -5099,13 +5099,13 @@
         <v>4.335</v>
       </c>
       <c r="L91" t="n">
-        <v>77</v>
+        <v>74.5</v>
       </c>
       <c r="M91" t="n">
         <v>4.406</v>
       </c>
       <c r="N91" t="n">
-        <v>71.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -5151,13 +5151,13 @@
         <v>3.892</v>
       </c>
       <c r="L92" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="M92" t="n">
         <v>3.933</v>
       </c>
       <c r="N92" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -5203,13 +5203,13 @@
         <v>4.297</v>
       </c>
       <c r="L93" t="n">
-        <v>69.5</v>
+        <v>67.5</v>
       </c>
       <c r="M93" t="n">
         <v>4.605</v>
       </c>
       <c r="N93" t="n">
-        <v>91.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -5255,13 +5255,13 @@
         <v>4.291</v>
       </c>
       <c r="L94" t="n">
-        <v>67.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="M94" t="n">
         <v>4.134</v>
       </c>
       <c r="N94" t="n">
-        <v>38.9</v>
+        <v>36.9</v>
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -5307,13 +5307,13 @@
         <v>4.324</v>
       </c>
       <c r="L95" t="n">
-        <v>74.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="M95" t="n">
         <v>4.264</v>
       </c>
       <c r="N95" t="n">
-        <v>54.6</v>
+        <v>52.5</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -5359,13 +5359,13 @@
         <v>4.72</v>
       </c>
       <c r="L96" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="M96" t="n">
         <v>4.679</v>
       </c>
       <c r="N96" t="n">
-        <v>96.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -5411,13 +5411,13 @@
         <v>4.37</v>
       </c>
       <c r="L97" t="n">
-        <v>82.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="M97" t="n">
         <v>4.416</v>
       </c>
       <c r="N97" t="n">
-        <v>75.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -5459,13 +5459,13 @@
         <v>4.266</v>
       </c>
       <c r="L98" t="n">
-        <v>59.9</v>
+        <v>58</v>
       </c>
       <c r="M98" t="n">
         <v>4.391</v>
       </c>
       <c r="N98" t="n">
-        <v>69.7</v>
+        <v>66.7</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -5507,13 +5507,13 @@
         <v>4.069</v>
       </c>
       <c r="L99" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="M99" t="n">
         <v>4.09</v>
       </c>
       <c r="N99" t="n">
-        <v>34.1</v>
+        <v>32.3</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -5555,13 +5555,13 @@
         <v>4.299</v>
       </c>
       <c r="L100" t="n">
-        <v>70.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="M100" t="n">
         <v>4.462</v>
       </c>
       <c r="N100" t="n">
-        <v>80</v>
+        <v>76.3</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -5603,13 +5603,13 @@
         <v>4.383</v>
       </c>
       <c r="L101" t="n">
-        <v>84</v>
+        <v>81.5</v>
       </c>
       <c r="M101" t="n">
         <v>4.555</v>
       </c>
       <c r="N101" t="n">
-        <v>89.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
@@ -5657,7 +5657,7 @@
         <v>3.846</v>
       </c>
       <c r="N102" t="n">
-        <v>15.1</v>
+        <v>14.6</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
@@ -5699,13 +5699,13 @@
         <v>4.313</v>
       </c>
       <c r="L103" t="n">
-        <v>72.7</v>
+        <v>70.5</v>
       </c>
       <c r="M103" t="n">
         <v>4.579</v>
       </c>
       <c r="N103" t="n">
-        <v>90.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -5751,13 +5751,13 @@
         <v>4.14</v>
       </c>
       <c r="L104" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M104" t="n">
         <v>4.049</v>
       </c>
       <c r="N104" t="n">
-        <v>30.3</v>
+        <v>28.8</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -5803,13 +5803,13 @@
         <v>4.032</v>
       </c>
       <c r="L105" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="M105" t="n">
         <v>3.872</v>
       </c>
       <c r="N105" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -5847,13 +5847,13 @@
         <v>4.228</v>
       </c>
       <c r="L106" t="n">
-        <v>50.3</v>
+        <v>49</v>
       </c>
       <c r="M106" t="n">
         <v>4.282</v>
       </c>
       <c r="N106" t="n">
-        <v>58.4</v>
+        <v>56.1</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -5899,13 +5899,13 @@
         <v>4.614</v>
       </c>
       <c r="L107" t="n">
-        <v>97.3</v>
+        <v>96.5</v>
       </c>
       <c r="M107" t="n">
         <v>4.531</v>
       </c>
       <c r="N107" t="n">
-        <v>87</v>
+        <v>82.8</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -5947,13 +5947,13 @@
         <v>4.201</v>
       </c>
       <c r="L108" t="n">
-        <v>47.1</v>
+        <v>46</v>
       </c>
       <c r="M108" t="n">
         <v>4.421</v>
       </c>
       <c r="N108" t="n">
-        <v>75.7</v>
+        <v>72.2</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
@@ -5995,13 +5995,13 @@
         <v>4.211</v>
       </c>
       <c r="L109" t="n">
-        <v>48.1</v>
+        <v>47</v>
       </c>
       <c r="M109" t="n">
         <v>4.22</v>
       </c>
       <c r="N109" t="n">
-        <v>49.7</v>
+        <v>48</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -6043,13 +6043,13 @@
         <v>3.87</v>
       </c>
       <c r="L110" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="M110" t="n">
         <v>3.878</v>
       </c>
       <c r="N110" t="n">
-        <v>18.4</v>
+        <v>17.7</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -6091,13 +6091,13 @@
         <v>3.871</v>
       </c>
       <c r="L111" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="M111" t="n">
         <v>4.074</v>
       </c>
       <c r="N111" t="n">
-        <v>32.4</v>
+        <v>30.8</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -6135,13 +6135,13 @@
         <v>4.264</v>
       </c>
       <c r="L112" t="n">
-        <v>57.2</v>
+        <v>55.5</v>
       </c>
       <c r="M112" t="n">
         <v>4.432</v>
       </c>
       <c r="N112" t="n">
-        <v>76.2</v>
+        <v>72.7</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -6187,13 +6187,13 @@
         <v>4.457</v>
       </c>
       <c r="L113" t="n">
-        <v>92</v>
+        <v>90.5</v>
       </c>
       <c r="M113" t="n">
         <v>4.587</v>
       </c>
       <c r="N113" t="n">
-        <v>91.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -6239,13 +6239,13 @@
         <v>4.265</v>
       </c>
       <c r="L114" t="n">
-        <v>59.4</v>
+        <v>57.5</v>
       </c>
       <c r="M114" t="n">
         <v>4.335</v>
       </c>
       <c r="N114" t="n">
-        <v>63.2</v>
+        <v>60.6</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -6291,13 +6291,13 @@
         <v>4.492</v>
       </c>
       <c r="L115" t="n">
-        <v>94.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="M115" t="n">
         <v>4.411</v>
       </c>
       <c r="N115" t="n">
-        <v>73.5</v>
+        <v>70.2</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -6335,13 +6335,13 @@
         <v>4.401</v>
       </c>
       <c r="L116" t="n">
-        <v>86.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="M116" t="n">
         <v>4.473</v>
       </c>
       <c r="N116" t="n">
-        <v>81.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -6387,13 +6387,13 @@
         <v>4.264</v>
       </c>
       <c r="L117" t="n">
-        <v>57.2</v>
+        <v>55.5</v>
       </c>
       <c r="M117" t="n">
         <v>4.17</v>
       </c>
       <c r="N117" t="n">
-        <v>42.7</v>
+        <v>40.9</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -6435,13 +6435,13 @@
         <v>4.277</v>
       </c>
       <c r="L118" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="M118" t="n">
         <v>4.2</v>
       </c>
       <c r="N118" t="n">
-        <v>46.5</v>
+        <v>44.4</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
@@ -6483,13 +6483,13 @@
         <v>4.262</v>
       </c>
       <c r="L119" t="n">
-        <v>56.7</v>
+        <v>55</v>
       </c>
       <c r="M119" t="n">
         <v>4.312</v>
       </c>
       <c r="N119" t="n">
-        <v>60.5</v>
+        <v>58.1</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -6535,13 +6535,13 @@
         <v>3.885</v>
       </c>
       <c r="L120" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="M120" t="n">
         <v>4.089</v>
       </c>
       <c r="N120" t="n">
-        <v>33.5</v>
+        <v>31.8</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -6583,13 +6583,13 @@
         <v>4.367</v>
       </c>
       <c r="L121" t="n">
-        <v>81.8</v>
+        <v>79</v>
       </c>
       <c r="M121" t="n">
         <v>4.545</v>
       </c>
       <c r="N121" t="n">
-        <v>88.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
@@ -6631,13 +6631,13 @@
         <v>3.867</v>
       </c>
       <c r="L122" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="M122" t="n">
         <v>3.782</v>
       </c>
       <c r="N122" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
@@ -6683,13 +6683,13 @@
         <v>4.135</v>
       </c>
       <c r="L123" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="M123" t="n">
         <v>4.156</v>
       </c>
       <c r="N123" t="n">
-        <v>41.1</v>
+        <v>38.9</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -6727,13 +6727,13 @@
         <v>4.143</v>
       </c>
       <c r="L124" t="n">
-        <v>40.1</v>
+        <v>39</v>
       </c>
       <c r="M124" t="n">
         <v>4.192</v>
       </c>
       <c r="N124" t="n">
-        <v>45.9</v>
+        <v>43.9</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -6771,13 +6771,13 @@
         <v>4.115</v>
       </c>
       <c r="L125" t="n">
-        <v>35.3</v>
+        <v>34.5</v>
       </c>
       <c r="M125" t="n">
         <v>4.235</v>
       </c>
       <c r="N125" t="n">
-        <v>51.4</v>
+        <v>49.5</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -6823,13 +6823,13 @@
         <v>4.26</v>
       </c>
       <c r="L126" t="n">
-        <v>55.6</v>
+        <v>54</v>
       </c>
       <c r="M126" t="n">
         <v>4.448</v>
       </c>
       <c r="N126" t="n">
-        <v>77.8</v>
+        <v>74.2</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -6871,13 +6871,13 @@
         <v>4.349</v>
       </c>
       <c r="L127" t="n">
-        <v>78.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M127" t="n">
         <v>4.278</v>
       </c>
       <c r="N127" t="n">
-        <v>57.3</v>
+        <v>55.1</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -6915,13 +6915,13 @@
         <v>4.095</v>
       </c>
       <c r="L128" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="M128" t="n">
         <v>4.021</v>
       </c>
       <c r="N128" t="n">
-        <v>27.6</v>
+        <v>26.3</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -6967,13 +6967,13 @@
         <v>4.053</v>
       </c>
       <c r="L129" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="M129" t="n">
         <v>4.16</v>
       </c>
       <c r="N129" t="n">
-        <v>41.6</v>
+        <v>39.4</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -7011,13 +7011,13 @@
         <v>3.697</v>
       </c>
       <c r="L130" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="M130" t="n">
         <v>3.805</v>
       </c>
       <c r="N130" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -7055,13 +7055,13 @@
         <v>3.82</v>
       </c>
       <c r="L131" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M131" t="n">
         <v>3.869</v>
       </c>
       <c r="N131" t="n">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -7103,13 +7103,13 @@
         <v>3.864</v>
       </c>
       <c r="L132" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M132" t="n">
         <v>4.33</v>
       </c>
       <c r="N132" t="n">
-        <v>62.2</v>
+        <v>59.6</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
@@ -7155,13 +7155,13 @@
         <v>4.178</v>
       </c>
       <c r="L133" t="n">
-        <v>44.4</v>
+        <v>43</v>
       </c>
       <c r="M133" t="n">
         <v>4.336</v>
       </c>
       <c r="N133" t="n">
-        <v>63.8</v>
+        <v>61.1</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -7207,13 +7207,13 @@
         <v>4.386</v>
       </c>
       <c r="L134" t="n">
-        <v>84.5</v>
+        <v>82</v>
       </c>
       <c r="M134" t="n">
         <v>4.656</v>
       </c>
       <c r="N134" t="n">
-        <v>96.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -7259,13 +7259,13 @@
         <v>3.906</v>
       </c>
       <c r="L135" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M135" t="n">
         <v>4.281</v>
       </c>
       <c r="N135" t="n">
-        <v>57.8</v>
+        <v>55.6</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -7311,13 +7311,13 @@
         <v>4.136</v>
       </c>
       <c r="L136" t="n">
-        <v>36.9</v>
+        <v>36</v>
       </c>
       <c r="M136" t="n">
         <v>3.985</v>
       </c>
       <c r="N136" t="n">
-        <v>25.9</v>
+        <v>24.7</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -7363,13 +7363,13 @@
         <v>4.479</v>
       </c>
       <c r="L137" t="n">
-        <v>93.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="M137" t="n">
         <v>4.61</v>
       </c>
       <c r="N137" t="n">
-        <v>93.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
@@ -7415,13 +7415,13 @@
         <v>3.783</v>
       </c>
       <c r="L138" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="M138" t="n">
         <v>3.362</v>
       </c>
       <c r="N138" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -7467,13 +7467,13 @@
         <v>4.438</v>
       </c>
       <c r="L139" t="n">
-        <v>89.8</v>
+        <v>88.5</v>
       </c>
       <c r="M139" t="n">
         <v>4.365</v>
       </c>
       <c r="N139" t="n">
-        <v>66.5</v>
+        <v>63.6</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -7511,13 +7511,13 @@
         <v>4.271</v>
       </c>
       <c r="L140" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M140" t="n">
         <v>4.101</v>
       </c>
       <c r="N140" t="n">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -7563,13 +7563,13 @@
         <v>3.52</v>
       </c>
       <c r="L141" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M141" t="n">
         <v>3.599</v>
       </c>
       <c r="N141" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -7615,13 +7615,13 @@
         <v>4.171</v>
       </c>
       <c r="L142" t="n">
-        <v>43.9</v>
+        <v>42.5</v>
       </c>
       <c r="M142" t="n">
         <v>4.131</v>
       </c>
       <c r="N142" t="n">
-        <v>38.4</v>
+        <v>36.4</v>
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -7667,13 +7667,13 @@
         <v>4.323</v>
       </c>
       <c r="L143" t="n">
-        <v>74.3</v>
+        <v>72</v>
       </c>
       <c r="M143" t="n">
         <v>4.606</v>
       </c>
       <c r="N143" t="n">
-        <v>92.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -7711,13 +7711,13 @@
         <v>4.282</v>
       </c>
       <c r="L144" t="n">
-        <v>64.2</v>
+        <v>62</v>
       </c>
       <c r="M144" t="n">
         <v>4.205</v>
       </c>
       <c r="N144" t="n">
-        <v>47.6</v>
+        <v>46</v>
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -7763,13 +7763,13 @@
         <v>4.189</v>
       </c>
       <c r="L145" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M145" t="n">
         <v>4.341</v>
       </c>
       <c r="N145" t="n">
-        <v>64.3</v>
+        <v>61.6</v>
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -7815,13 +7815,13 @@
         <v>4.478</v>
       </c>
       <c r="L146" t="n">
-        <v>93</v>
+        <v>91.5</v>
       </c>
       <c r="M146" t="n">
         <v>4.483</v>
       </c>
       <c r="N146" t="n">
-        <v>82.7</v>
+        <v>78.8</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -7863,13 +7863,13 @@
         <v>4.42</v>
       </c>
       <c r="L147" t="n">
-        <v>88.2</v>
+        <v>86.5</v>
       </c>
       <c r="M147" t="n">
         <v>4.492</v>
       </c>
       <c r="N147" t="n">
-        <v>83.8</v>
+        <v>79.8</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -7915,13 +7915,13 @@
         <v>4.286</v>
       </c>
       <c r="L148" t="n">
-        <v>65.8</v>
+        <v>63.5</v>
       </c>
       <c r="M148" t="n">
         <v>4.356</v>
       </c>
       <c r="N148" t="n">
-        <v>65.40000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -7967,13 +7967,13 @@
         <v>4.103</v>
       </c>
       <c r="L149" t="n">
-        <v>32.1</v>
+        <v>31.5</v>
       </c>
       <c r="M149" t="n">
         <v>4.17</v>
       </c>
       <c r="N149" t="n">
-        <v>42.7</v>
+        <v>40.9</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -8019,13 +8019,13 @@
         <v>4.276</v>
       </c>
       <c r="L150" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M150" t="n">
         <v>4.268</v>
       </c>
       <c r="N150" t="n">
-        <v>55.1</v>
+        <v>53</v>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -8071,13 +8071,13 @@
         <v>4.38</v>
       </c>
       <c r="L151" t="n">
-        <v>83.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="M151" t="n">
         <v>4.452</v>
       </c>
       <c r="N151" t="n">
-        <v>78.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -8123,13 +8123,13 @@
         <v>3.943</v>
       </c>
       <c r="L152" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="M152" t="n">
         <v>4.008</v>
       </c>
       <c r="N152" t="n">
-        <v>27</v>
+        <v>25.8</v>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -8175,13 +8175,13 @@
         <v>4.441</v>
       </c>
       <c r="L153" t="n">
-        <v>90.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="M153" t="n">
         <v>4.407</v>
       </c>
       <c r="N153" t="n">
-        <v>72.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -8227,13 +8227,13 @@
         <v>4.446</v>
       </c>
       <c r="L154" t="n">
-        <v>90.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="M154" t="n">
         <v>4.455</v>
       </c>
       <c r="N154" t="n">
-        <v>78.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -8279,13 +8279,13 @@
         <v>4.286</v>
       </c>
       <c r="L155" t="n">
-        <v>65.8</v>
+        <v>63.5</v>
       </c>
       <c r="M155" t="n">
         <v>4.526</v>
       </c>
       <c r="N155" t="n">
-        <v>86.5</v>
+        <v>82.3</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
@@ -8331,13 +8331,13 @@
         <v>4.312</v>
       </c>
       <c r="L156" t="n">
-        <v>72.2</v>
+        <v>70</v>
       </c>
       <c r="M156" t="n">
         <v>3.71</v>
       </c>
       <c r="N156" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
@@ -8389,7 +8389,7 @@
         <v>3.578</v>
       </c>
       <c r="N157" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -8435,13 +8435,13 @@
         <v>4.277</v>
       </c>
       <c r="L158" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="M158" t="n">
         <v>3.832</v>
       </c>
       <c r="N158" t="n">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -8487,13 +8487,13 @@
         <v>4.109</v>
       </c>
       <c r="L159" t="n">
-        <v>33.2</v>
+        <v>32.5</v>
       </c>
       <c r="M159" t="n">
         <v>3.946</v>
       </c>
       <c r="N159" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
@@ -8591,13 +8591,13 @@
         <v>4.436</v>
       </c>
       <c r="L161" t="n">
-        <v>89.3</v>
+        <v>88</v>
       </c>
       <c r="M161" t="n">
         <v>3.862</v>
       </c>
       <c r="N161" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
@@ -8643,13 +8643,13 @@
         <v>3.866</v>
       </c>
       <c r="L162" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="M162" t="n">
         <v>3.573</v>
       </c>
       <c r="N162" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -8695,13 +8695,13 @@
         <v>4.178</v>
       </c>
       <c r="L163" t="n">
-        <v>44.4</v>
+        <v>43</v>
       </c>
       <c r="M163" t="n">
         <v>3.908</v>
       </c>
       <c r="N163" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
@@ -8747,13 +8747,13 @@
         <v>4.414</v>
       </c>
       <c r="L164" t="n">
-        <v>87.7</v>
+        <v>86</v>
       </c>
       <c r="M164" t="n">
         <v>4.393</v>
       </c>
       <c r="N164" t="n">
-        <v>70.3</v>
+        <v>67.2</v>
       </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -8799,13 +8799,13 @@
         <v>4.283</v>
       </c>
       <c r="L165" t="n">
-        <v>64.7</v>
+        <v>62.5</v>
       </c>
       <c r="M165" t="n">
         <v>4.127</v>
       </c>
       <c r="N165" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
@@ -8851,13 +8851,13 @@
         <v>4.308</v>
       </c>
       <c r="L166" t="n">
-        <v>71.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="M166" t="n">
         <v>4.098</v>
       </c>
       <c r="N166" t="n">
-        <v>34.6</v>
+        <v>32.8</v>
       </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -8903,13 +8903,13 @@
         <v>3.966</v>
       </c>
       <c r="L167" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="M167" t="n">
         <v>3.432</v>
       </c>
       <c r="N167" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -8955,13 +8955,13 @@
         <v>4.296</v>
       </c>
       <c r="L168" t="n">
-        <v>68.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="M168" t="n">
         <v>4.169</v>
       </c>
       <c r="N168" t="n">
-        <v>42.2</v>
+        <v>39.9</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -9007,13 +9007,13 @@
         <v>4.02</v>
       </c>
       <c r="L169" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="M169" t="n">
         <v>3.532</v>
       </c>
       <c r="N169" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -9059,7 +9059,7 @@
         <v>4.314</v>
       </c>
       <c r="L170" t="n">
-        <v>73.3</v>
+        <v>71</v>
       </c>
       <c r="M170" t="n">
         <v>3.688</v>
@@ -9111,13 +9111,13 @@
         <v>4.268</v>
       </c>
       <c r="L171" t="n">
-        <v>60.4</v>
+        <v>58.5</v>
       </c>
       <c r="M171" t="n">
         <v>3.864</v>
       </c>
       <c r="N171" t="n">
-        <v>16.2</v>
+        <v>15.7</v>
       </c>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -9163,7 +9163,7 @@
         <v>4.02</v>
       </c>
       <c r="L172" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="M172" t="n">
         <v>3.602</v>
@@ -9215,13 +9215,13 @@
         <v>4.083</v>
       </c>
       <c r="L173" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="M173" t="n">
         <v>3.554</v>
       </c>
       <c r="N173" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
@@ -9267,7 +9267,7 @@
         <v>3.93</v>
       </c>
       <c r="L174" t="n">
-        <v>16.6</v>
+        <v>17</v>
       </c>
       <c r="M174" t="n">
         <v>3.138</v>
@@ -9319,13 +9319,13 @@
         <v>3.93</v>
       </c>
       <c r="L175" t="n">
-        <v>16.6</v>
+        <v>17</v>
       </c>
       <c r="M175" t="n">
         <v>3.533</v>
       </c>
       <c r="N175" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
@@ -9371,13 +9371,13 @@
         <v>3.845</v>
       </c>
       <c r="L176" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="M176" t="n">
         <v>3.445</v>
       </c>
       <c r="N176" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
@@ -9423,7 +9423,7 @@
         <v>3.897</v>
       </c>
       <c r="L177" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="M177" t="n">
         <v>3.636</v>
@@ -9475,13 +9475,13 @@
         <v>4.264</v>
       </c>
       <c r="L178" t="n">
-        <v>57.2</v>
+        <v>55.5</v>
       </c>
       <c r="M178" t="n">
         <v>4.227</v>
       </c>
       <c r="N178" t="n">
-        <v>50.8</v>
+        <v>49</v>
       </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
@@ -9527,13 +9527,13 @@
         <v>3.906</v>
       </c>
       <c r="L179" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M179" t="n">
         <v>3.751</v>
       </c>
       <c r="N179" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
@@ -9579,13 +9579,13 @@
         <v>3.973</v>
       </c>
       <c r="L180" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="M180" t="n">
         <v>3.828</v>
       </c>
       <c r="N180" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -9631,13 +9631,13 @@
         <v>4.363</v>
       </c>
       <c r="L181" t="n">
-        <v>81.3</v>
+        <v>78.5</v>
       </c>
       <c r="M181" t="n">
         <v>4.632</v>
       </c>
       <c r="N181" t="n">
-        <v>94.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -9683,13 +9683,13 @@
         <v>4.255</v>
       </c>
       <c r="L182" t="n">
-        <v>55.1</v>
+        <v>53.5</v>
       </c>
       <c r="M182" t="n">
         <v>4.351</v>
       </c>
       <c r="N182" t="n">
-        <v>64.90000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -9735,13 +9735,13 @@
         <v>4.264</v>
       </c>
       <c r="L183" t="n">
-        <v>57.2</v>
+        <v>55.5</v>
       </c>
       <c r="M183" t="n">
         <v>4.273</v>
       </c>
       <c r="N183" t="n">
-        <v>56.2</v>
+        <v>54</v>
       </c>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
@@ -9787,13 +9787,13 @@
         <v>4.353</v>
       </c>
       <c r="L184" t="n">
-        <v>79.7</v>
+        <v>77</v>
       </c>
       <c r="M184" t="n">
         <v>4.24</v>
       </c>
       <c r="N184" t="n">
-        <v>52.4</v>
+        <v>50.5</v>
       </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
@@ -9839,13 +9839,13 @@
         <v>4.218</v>
       </c>
       <c r="L185" t="n">
-        <v>48.7</v>
+        <v>47.5</v>
       </c>
       <c r="M185" t="n">
         <v>3.977</v>
       </c>
       <c r="N185" t="n">
-        <v>25.4</v>
+        <v>24.2</v>
       </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
@@ -9891,13 +9891,13 @@
         <v>4.113</v>
       </c>
       <c r="L186" t="n">
-        <v>33.7</v>
+        <v>33</v>
       </c>
       <c r="M186" t="n">
         <v>4.639</v>
       </c>
       <c r="N186" t="n">
-        <v>95.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -9943,13 +9943,13 @@
         <v>4.238</v>
       </c>
       <c r="L187" t="n">
-        <v>51.9</v>
+        <v>50.5</v>
       </c>
       <c r="M187" t="n">
         <v>4.561</v>
       </c>
       <c r="N187" t="n">
-        <v>90.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
@@ -9995,13 +9995,13 @@
         <v>4.114</v>
       </c>
       <c r="L188" t="n">
-        <v>34.2</v>
+        <v>33.5</v>
       </c>
       <c r="M188" t="n">
         <v>4.33</v>
       </c>
       <c r="N188" t="n">
-        <v>62.2</v>
+        <v>59.6</v>
       </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
@@ -10047,18 +10047,694 @@
         <v>3.865</v>
       </c>
       <c r="L189" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M189" t="n">
         <v>3.737</v>
       </c>
       <c r="N189" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Nigiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Wagyu Place</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Queens (Flushing)</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>68</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AYCE wagyu yakiniku with complimentary omakase sushi set (A5 tier $159)</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1686</v>
+      </c>
+      <c r="K190" t="n">
+        <v>4.394</v>
+      </c>
+      <c r="L190" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="M190" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="N190" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Wagyu Place BBQ 和牛公馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Niku X NYC</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Manhattan (Midtown/Koreatown)</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>119</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Self-described 'only unlimited A5 Wagyu Steakhouse in the U.S.' with unlimited sushi+wagyu nigiri</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J191" t="n">
+        <v>2965</v>
+      </c>
+      <c r="K191" t="n">
+        <v>4.716</v>
+      </c>
+      <c r="L191" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="M191" t="n">
+        <v>4.635</v>
+      </c>
+      <c r="N191" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>NIKU X | Limitless Wagyu BBQ &amp; Seafood</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Mikiya Wagyu Shabu House (Flushing)</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Queens (Flushing)</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>45</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Shabu AYCE with A5 wagyu tiers; wagyu nigiri+tartare in every tier</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1147</v>
+      </c>
+      <c r="K192" t="n">
+        <v>4.481</v>
+      </c>
+      <c r="L192" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="M192" t="n">
+        <v>4.853</v>
+      </c>
+      <c r="N192" t="n">
+        <v>98</v>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Mikiya Wagyu Shabu House 味喜屋 | Flushing</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Mikiya Wagyu Shabu House (Manhattan)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Manhattan (Midtown East)</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>68</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Manhattan sister of Mikiya Flushing; explicit AYCE wagyu nigiri program</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J193" t="n">
+        <v>345</v>
+      </c>
+      <c r="K193" t="n">
+        <v>4.409</v>
+      </c>
+      <c r="L193" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="M193" t="n">
+        <v>4.582</v>
+      </c>
+      <c r="N193" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Mikiya Wagyu Shabu House | Manhattan</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Chubby Cattle BBQ NYC</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Manhattan (SoHo)</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>58</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Signature Wagyu Uni Caviar Nigiri served as part of AYCE wagyu yakiniku</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J194" t="n">
+        <v>2382</v>
+      </c>
+      <c r="K194" t="n">
+        <v>4.711</v>
+      </c>
+      <c r="L194" t="n">
+        <v>98</v>
+      </c>
+      <c r="M194" t="n">
+        <v>4.975</v>
+      </c>
+      <c r="N194" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Chubby Cattle BBQ | New York</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Y Space BBQ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Queens (Flushing)</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>49</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Space-themed AYCE wagyu yakiniku with A5 Wagyu Nigiri Sushi as part of AYCE</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K195" t="n">
+        <v>4.289</v>
+      </c>
+      <c r="L195" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="M195" t="n">
+        <v>4.606</v>
+      </c>
+      <c r="N195" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Y Space BBQ 烤肉火焱星</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Wagyu Yama Yakiniku &amp; Seafood Shabu</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Queens (Flushing)</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>68</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>A5 yakiniku + seafood shabu hybrid; AYCE BBQ + hotpot combo with sashimi rounds</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1147</v>
+      </c>
+      <c r="K196" t="n">
+        <v>4.481</v>
+      </c>
+      <c r="L196" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="M196" t="n">
+        <v>4.657</v>
+      </c>
+      <c r="N196" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Mikiya Wagyu Shabu House 味喜屋 | Flushing</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Hiyake Omakase (Bowery)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Manhattan (Lower East Side/Chinatown)</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>29</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AYCE wagyu yakiniku with Uni Wagyu Handroll; despite the name, it's not counter omakase</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J197" t="n">
+        <v>98</v>
+      </c>
+      <c r="K197" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="L197" t="n">
+        <v>79</v>
+      </c>
+      <c r="M197" t="n">
+        <v>4.942</v>
+      </c>
+      <c r="N197" t="n">
+        <v>99</v>
+      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Genki east omakase</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Hiyake Omakase (Williamsburg)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Brooklyn (Williamsburg)</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>48</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Brooklyn sister of Hiyake; AYCE wagyu yakiniku with sushi+sashimi rounds in private booths</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J198" t="n">
+        <v>171</v>
+      </c>
+      <c r="K198" t="n">
+        <v>3.904</v>
+      </c>
+      <c r="L198" t="n">
+        <v>15</v>
+      </c>
+      <c r="M198" t="n">
+        <v>4.201</v>
+      </c>
+      <c r="N198" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Hiyake Yakiniku BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Gyu-Ichiro</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Manhattan (Lower East Side/Chinatown)</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>29</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Same operator/space as Hiyake; markets unlimited wagyu + sushi combo</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="n">
+        <v>4</v>
+      </c>
+      <c r="J199" t="n">
+        <v>353</v>
+      </c>
+      <c r="K199" t="n">
+        <v>3.684</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="n">
+        <v>4.169</v>
+      </c>
+      <c r="N199" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Gyu-Ichiro Japanese BBQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Nikushou Sakai</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Queens (Flushing)</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>55</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>New 2025 Flushing AYCE wagyu yakiniku with sashimi inclusion (iPad ordering)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J200" t="n">
+        <v>264</v>
+      </c>
+      <c r="K200" t="n">
+        <v>3.351</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M200" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="N200" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Nikushou Sakai 肉匠坂井</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Umiya Sushi LIC</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Queens (Long Island City)</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>40</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AYCE sushi bar with A5 Japanese Wagyu in Premium tier ($67.95)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J201" t="n">
+        <v>482</v>
+      </c>
+      <c r="K201" t="n">
+        <v>4.435</v>
+      </c>
+      <c r="L201" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="M201" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="N201" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Umiya Sushi</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Asuka Sushi</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Manhattan (Chelsea)</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>30</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>varies (AYCE 90-120min)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Chelsea sushi bar with signature Big Mac (wagyu+uni+scallop+toro) and AYCE wagyu sushi</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1436</v>
+      </c>
+      <c r="K202" t="n">
+        <v>4.185</v>
+      </c>
+      <c r="L202" t="n">
+        <v>44</v>
+      </c>
+      <c r="M202" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="N202" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Asuka Sushi</t>
         </is>
       </c>
     </row>

--- a/Omakase_Ratings.xlsx
+++ b/Omakase_Ratings.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omakase" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,17 +29,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -73,15 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,16 +569,16 @@
         <v>1471</v>
       </c>
       <c r="K2" t="n">
-        <v>4.107</v>
+        <v>4.102</v>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>34.7</v>
       </c>
       <c r="M2" t="n">
-        <v>4.061</v>
+        <v>4.056</v>
       </c>
       <c r="N2" t="n">
-        <v>29.3</v>
+        <v>30.5</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -636,16 +621,16 @@
         <v>87</v>
       </c>
       <c r="K3" t="n">
-        <v>3.545</v>
+        <v>3.46</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.563</v>
+        <v>3.478</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -691,13 +676,13 @@
         <v>4.143</v>
       </c>
       <c r="L4" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
       <c r="M4" t="n">
         <v>4.143</v>
       </c>
       <c r="N4" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -736,16 +721,16 @@
         <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>3.86</v>
+        <v>3.822</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.88</v>
+        <v>3.842</v>
       </c>
       <c r="N5" t="n">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -784,16 +769,16 @@
         <v>137</v>
       </c>
       <c r="K6" t="n">
-        <v>3.958</v>
+        <v>3.929</v>
       </c>
       <c r="L6" t="n">
-        <v>19.5</v>
+        <v>18.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.886</v>
+        <v>3.858</v>
       </c>
       <c r="N6" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -832,16 +817,16 @@
         <v>98</v>
       </c>
       <c r="K7" t="n">
-        <v>4.324</v>
+        <v>4.287</v>
       </c>
       <c r="L7" t="n">
-        <v>72.5</v>
+        <v>64.8</v>
       </c>
       <c r="M7" t="n">
-        <v>4.152</v>
+        <v>4.116</v>
       </c>
       <c r="N7" t="n">
-        <v>38.4</v>
+        <v>35</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -884,16 +869,16 @@
         <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>4.25</v>
+        <v>4.223</v>
       </c>
       <c r="L8" t="n">
-        <v>52</v>
+        <v>48.2</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>4.272</v>
       </c>
       <c r="N8" t="n">
-        <v>57.1</v>
+        <v>54.3</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -936,16 +921,16 @@
         <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>4.234</v>
+        <v>4.239</v>
       </c>
       <c r="L9" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.776</v>
+        <v>4.781</v>
       </c>
       <c r="N9" t="n">
-        <v>97</v>
+        <v>97.5</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1010,16 +995,16 @@
         <v>426</v>
       </c>
       <c r="K11" t="n">
-        <v>3.865</v>
+        <v>3.86</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>13.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.957</v>
+        <v>3.952</v>
       </c>
       <c r="N11" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1061,13 +1046,13 @@
         <v>4.389</v>
       </c>
       <c r="L12" t="n">
-        <v>83</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>4.445</v>
       </c>
       <c r="N12" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1113,13 +1098,13 @@
         <v>4.33</v>
       </c>
       <c r="L13" t="n">
-        <v>74</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>4.309</v>
       </c>
       <c r="N13" t="n">
-        <v>57.6</v>
+        <v>58.9</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1162,16 +1147,16 @@
         <v>415</v>
       </c>
       <c r="K14" t="n">
-        <v>4.296</v>
+        <v>4.28</v>
       </c>
       <c r="L14" t="n">
-        <v>66.5</v>
+        <v>60.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4.465</v>
+        <v>4.449</v>
       </c>
       <c r="N14" t="n">
-        <v>76.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1217,13 +1202,13 @@
         <v>4.078</v>
       </c>
       <c r="L15" t="n">
-        <v>28.5</v>
+        <v>30.7</v>
       </c>
       <c r="M15" t="n">
         <v>4.078</v>
       </c>
       <c r="N15" t="n">
-        <v>31.3</v>
+        <v>32</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1266,16 +1251,16 @@
         <v>235</v>
       </c>
       <c r="K16" t="n">
-        <v>4.336</v>
+        <v>4.334</v>
       </c>
       <c r="L16" t="n">
-        <v>75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>4.276</v>
+        <v>4.274</v>
       </c>
       <c r="N16" t="n">
-        <v>54.5</v>
+        <v>55.8</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1314,16 +1299,16 @@
         <v>149</v>
       </c>
       <c r="K17" t="n">
-        <v>4.042</v>
+        <v>4.021</v>
       </c>
       <c r="L17" t="n">
-        <v>26.5</v>
+        <v>26.1</v>
       </c>
       <c r="M17" t="n">
-        <v>4.201</v>
+        <v>4.179</v>
       </c>
       <c r="N17" t="n">
-        <v>44.9</v>
+        <v>43.1</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -1366,16 +1351,16 @@
         <v>1563</v>
       </c>
       <c r="K18" t="n">
-        <v>4.092</v>
+        <v>4.065</v>
       </c>
       <c r="L18" t="n">
-        <v>30</v>
+        <v>29.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.881</v>
+        <v>3.855</v>
       </c>
       <c r="N18" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1414,16 +1399,16 @@
         <v>92</v>
       </c>
       <c r="K19" t="n">
-        <v>4.252</v>
+        <v>4.286</v>
       </c>
       <c r="L19" t="n">
-        <v>53</v>
+        <v>64.3</v>
       </c>
       <c r="M19" t="n">
-        <v>4.212</v>
+        <v>4.246</v>
       </c>
       <c r="N19" t="n">
-        <v>46.5</v>
+        <v>52.3</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1466,16 +1451,16 @@
         <v>63</v>
       </c>
       <c r="K20" t="n">
-        <v>3.985</v>
+        <v>4.001</v>
       </c>
       <c r="L20" t="n">
-        <v>22</v>
+        <v>23.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.827</v>
+        <v>3.842</v>
       </c>
       <c r="N20" t="n">
-        <v>12.6</v>
+        <v>16.2</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1518,16 +1503,16 @@
         <v>762</v>
       </c>
       <c r="K21" t="n">
-        <v>4.387</v>
+        <v>4.364</v>
       </c>
       <c r="L21" t="n">
-        <v>82.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>4.649</v>
+        <v>4.625</v>
       </c>
       <c r="N21" t="n">
-        <v>92.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1562,16 +1547,16 @@
         <v>158</v>
       </c>
       <c r="K22" t="n">
-        <v>4.095</v>
+        <v>4.055</v>
       </c>
       <c r="L22" t="n">
-        <v>30.5</v>
+        <v>28.6</v>
       </c>
       <c r="M22" t="n">
-        <v>4.116</v>
+        <v>4.076</v>
       </c>
       <c r="N22" t="n">
-        <v>34.8</v>
+        <v>31.5</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -1617,13 +1602,13 @@
         <v>4.544</v>
       </c>
       <c r="L23" t="n">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="M23" t="n">
         <v>4.509</v>
       </c>
       <c r="N23" t="n">
-        <v>81.3</v>
+        <v>80.7</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -1666,16 +1651,16 @@
         <v>238</v>
       </c>
       <c r="K24" t="n">
-        <v>4.142</v>
+        <v>4.153</v>
       </c>
       <c r="L24" t="n">
-        <v>38.5</v>
+        <v>40.7</v>
       </c>
       <c r="M24" t="n">
-        <v>4.142</v>
+        <v>4.153</v>
       </c>
       <c r="N24" t="n">
-        <v>37.4</v>
+        <v>40.1</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -1718,16 +1703,16 @@
         <v>654</v>
       </c>
       <c r="K25" t="n">
-        <v>4.636</v>
+        <v>4.646</v>
       </c>
       <c r="L25" t="n">
-        <v>97</v>
+        <v>97.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4.69</v>
+        <v>4.701</v>
       </c>
       <c r="N25" t="n">
-        <v>94.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -1770,16 +1755,16 @@
         <v>326</v>
       </c>
       <c r="K26" t="n">
-        <v>4.003</v>
+        <v>3.991</v>
       </c>
       <c r="L26" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="M26" t="n">
-        <v>4.045</v>
+        <v>4.033</v>
       </c>
       <c r="N26" t="n">
-        <v>28.3</v>
+        <v>28.9</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -1822,16 +1807,16 @@
         <v>187</v>
       </c>
       <c r="K27" t="n">
-        <v>4.494</v>
+        <v>4.498</v>
       </c>
       <c r="L27" t="n">
-        <v>94</v>
+        <v>94.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.378</v>
+        <v>4.381</v>
       </c>
       <c r="N27" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -1874,16 +1859,16 @@
         <v>1135</v>
       </c>
       <c r="K28" t="n">
-        <v>3.982</v>
+        <v>3.983</v>
       </c>
       <c r="L28" t="n">
-        <v>21</v>
+        <v>21.6</v>
       </c>
       <c r="M28" t="n">
-        <v>4.191</v>
+        <v>4.192</v>
       </c>
       <c r="N28" t="n">
-        <v>43.4</v>
+        <v>45.7</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -1926,16 +1911,16 @@
         <v>631</v>
       </c>
       <c r="K29" t="n">
-        <v>4.219</v>
+        <v>4.257</v>
       </c>
       <c r="L29" t="n">
-        <v>48</v>
+        <v>54.8</v>
       </c>
       <c r="M29" t="n">
-        <v>4.54</v>
+        <v>4.581</v>
       </c>
       <c r="N29" t="n">
-        <v>83.3</v>
+        <v>87.3</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -1974,16 +1959,16 @@
         <v>195</v>
       </c>
       <c r="K30" t="n">
-        <v>3.982</v>
+        <v>3.962</v>
       </c>
       <c r="L30" t="n">
-        <v>21</v>
+        <v>20.1</v>
       </c>
       <c r="M30" t="n">
-        <v>4.212</v>
+        <v>4.191</v>
       </c>
       <c r="N30" t="n">
-        <v>46.5</v>
+        <v>45.2</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -2026,16 +2011,16 @@
         <v>297</v>
       </c>
       <c r="K31" t="n">
-        <v>4.368</v>
+        <v>4.351</v>
       </c>
       <c r="L31" t="n">
-        <v>80</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>4.39</v>
+        <v>4.373</v>
       </c>
       <c r="N31" t="n">
-        <v>66.2</v>
+        <v>64.5</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -2078,16 +2063,16 @@
         <v>619</v>
       </c>
       <c r="K32" t="n">
-        <v>4.242</v>
+        <v>4.322</v>
       </c>
       <c r="L32" t="n">
-        <v>51.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>4.479</v>
+        <v>4.564</v>
       </c>
       <c r="N32" t="n">
-        <v>77.8</v>
+        <v>85.8</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -2126,16 +2111,16 @@
         <v>221</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4.554</v>
+        <v>4.564</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>95.5</v>
+        <v>96</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4.607</v>
+        <v>4.618</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2171,10 +2156,10 @@
         <v>110</v>
       </c>
       <c r="K34" t="n">
-        <v>3.871</v>
+        <v>3.863</v>
       </c>
       <c r="L34" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -2217,16 +2202,16 @@
         <v>574</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4.238</v>
+        <v>4.283</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>50.5</v>
+        <v>62.8</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4.398</v>
+        <v>4.445</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>67.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2273,13 +2258,13 @@
         <v>442</v>
       </c>
       <c r="K36" t="n">
-        <v>4.47</v>
+        <v>4.461</v>
       </c>
       <c r="L36" t="n">
         <v>91</v>
       </c>
       <c r="M36" t="n">
-        <v>4.543</v>
+        <v>4.534</v>
       </c>
       <c r="N36" t="n">
         <v>83.8</v>
@@ -2325,16 +2310,16 @@
         <v>421</v>
       </c>
       <c r="K37" t="n">
-        <v>4.284</v>
+        <v>4.281</v>
       </c>
       <c r="L37" t="n">
-        <v>63</v>
+        <v>60.8</v>
       </c>
       <c r="M37" t="n">
-        <v>4.114</v>
+        <v>4.11</v>
       </c>
       <c r="N37" t="n">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -2374,7 +2359,7 @@
         <v>469</v>
       </c>
       <c r="K38" t="n">
-        <v>3.48</v>
+        <v>3.438</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2420,16 +2405,16 @@
         <v>3088</v>
       </c>
       <c r="K39" t="n">
-        <v>4.149</v>
+        <v>4.145</v>
       </c>
       <c r="L39" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
       <c r="M39" t="n">
-        <v>4.785</v>
+        <v>4.781</v>
       </c>
       <c r="N39" t="n">
-        <v>97.5</v>
+        <v>98</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -2472,16 +2457,16 @@
         <v>442</v>
       </c>
       <c r="K40" t="n">
-        <v>3.865</v>
+        <v>3.834</v>
       </c>
       <c r="L40" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.881</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>19.2</v>
+        <v>17.3</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -2524,16 +2509,16 @@
         <v>157</v>
       </c>
       <c r="K41" t="n">
-        <v>4.261</v>
+        <v>4.224</v>
       </c>
       <c r="L41" t="n">
-        <v>54.5</v>
+        <v>48.7</v>
       </c>
       <c r="M41" t="n">
-        <v>4.316</v>
+        <v>4.278</v>
       </c>
       <c r="N41" t="n">
-        <v>59.1</v>
+        <v>56.3</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -2576,16 +2561,16 @@
         <v>171</v>
       </c>
       <c r="K42" t="n">
-        <v>3.951</v>
+        <v>3.931</v>
       </c>
       <c r="L42" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.951</v>
+        <v>3.931</v>
       </c>
       <c r="N42" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -2624,16 +2609,16 @@
         <v>73</v>
       </c>
       <c r="K43" t="n">
-        <v>4.167</v>
+        <v>4.149</v>
       </c>
       <c r="L43" t="n">
-        <v>41.5</v>
+        <v>40.2</v>
       </c>
       <c r="M43" t="n">
-        <v>4.188</v>
+        <v>4.17</v>
       </c>
       <c r="N43" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -2676,16 +2661,16 @@
         <v>868</v>
       </c>
       <c r="K44" t="n">
-        <v>4.732</v>
+        <v>4.724</v>
       </c>
       <c r="L44" t="n">
         <v>99.5</v>
       </c>
       <c r="M44" t="n">
-        <v>4.732</v>
+        <v>4.724</v>
       </c>
       <c r="N44" t="n">
-        <v>96</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -2724,16 +2709,16 @@
         <v>855</v>
       </c>
       <c r="K45" t="n">
-        <v>3.869</v>
+        <v>3.859</v>
       </c>
       <c r="L45" t="n">
-        <v>10.5</v>
+        <v>12.1</v>
       </c>
       <c r="M45" t="n">
-        <v>3.889</v>
+        <v>3.879</v>
       </c>
       <c r="N45" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -2776,16 +2761,16 @@
         <v>198</v>
       </c>
       <c r="K46" t="n">
-        <v>3.913</v>
+        <v>3.884</v>
       </c>
       <c r="L46" t="n">
-        <v>16.5</v>
+        <v>15.1</v>
       </c>
       <c r="M46" t="n">
-        <v>4.027</v>
+        <v>3.998</v>
       </c>
       <c r="N46" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -2828,16 +2813,16 @@
         <v>34</v>
       </c>
       <c r="K47" t="n">
-        <v>3.652</v>
+        <v>3.612</v>
       </c>
       <c r="L47" t="n">
         <v>2.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.843</v>
+        <v>3.802</v>
       </c>
       <c r="N47" t="n">
-        <v>14.1</v>
+        <v>12.7</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
@@ -2876,16 +2861,16 @@
         <v>273</v>
       </c>
       <c r="K48" t="n">
-        <v>4.141</v>
+        <v>4.179</v>
       </c>
       <c r="L48" t="n">
-        <v>38</v>
+        <v>43.7</v>
       </c>
       <c r="M48" t="n">
-        <v>4.245</v>
+        <v>4.284</v>
       </c>
       <c r="N48" t="n">
-        <v>51</v>
+        <v>56.9</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -2928,16 +2913,16 @@
         <v>967</v>
       </c>
       <c r="K49" t="n">
-        <v>4.583</v>
+        <v>4.571</v>
       </c>
       <c r="L49" t="n">
-        <v>96</v>
+        <v>96.5</v>
       </c>
       <c r="M49" t="n">
-        <v>4.756</v>
+        <v>4.744</v>
       </c>
       <c r="N49" t="n">
-        <v>96.5</v>
+        <v>97</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -2980,16 +2965,16 @@
         <v>768</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>3.817</v>
+        <v>3.72</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3.825</v>
+        <v>3.727</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>12.1</v>
+        <v>10.2</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3036,16 +3021,16 @@
         <v>2038</v>
       </c>
       <c r="K51" t="n">
-        <v>4.122</v>
+        <v>4.117</v>
       </c>
       <c r="L51" t="n">
-        <v>35</v>
+        <v>36.2</v>
       </c>
       <c r="M51" t="n">
-        <v>4.237</v>
+        <v>4.231</v>
       </c>
       <c r="N51" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -3088,16 +3073,16 @@
         <v>34</v>
       </c>
       <c r="K52" t="n">
-        <v>4.273</v>
+        <v>4.29</v>
       </c>
       <c r="L52" t="n">
-        <v>59.5</v>
+        <v>65.8</v>
       </c>
       <c r="M52" t="n">
-        <v>4.461</v>
+        <v>4.478</v>
       </c>
       <c r="N52" t="n">
-        <v>75.8</v>
+        <v>77.7</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -3140,16 +3125,16 @@
         <v>951</v>
       </c>
       <c r="K53" t="n">
-        <v>4.345</v>
+        <v>4.354</v>
       </c>
       <c r="L53" t="n">
-        <v>75.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>4.509</v>
+        <v>4.518</v>
       </c>
       <c r="N53" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -3192,16 +3177,16 @@
         <v>432</v>
       </c>
       <c r="K54" t="n">
-        <v>3.872</v>
+        <v>3.819</v>
       </c>
       <c r="L54" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="M54" t="n">
-        <v>3.88</v>
+        <v>3.827</v>
       </c>
       <c r="N54" t="n">
-        <v>18.2</v>
+        <v>14.2</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -3244,16 +3229,16 @@
         <v>359</v>
       </c>
       <c r="K55" t="n">
-        <v>3.937</v>
+        <v>3.888</v>
       </c>
       <c r="L55" t="n">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="M55" t="n">
-        <v>3.866</v>
+        <v>3.817</v>
       </c>
       <c r="N55" t="n">
-        <v>16.2</v>
+        <v>13.2</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -3296,16 +3281,16 @@
         <v>436</v>
       </c>
       <c r="K56" t="n">
-        <v>4.29</v>
+        <v>4.332</v>
       </c>
       <c r="L56" t="n">
-        <v>65.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>4.415</v>
+        <v>4.458</v>
       </c>
       <c r="N56" t="n">
-        <v>71.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -3348,16 +3333,16 @@
         <v>1467</v>
       </c>
       <c r="K57" t="n">
-        <v>4.143</v>
+        <v>4.159</v>
       </c>
       <c r="L57" t="n">
-        <v>39</v>
+        <v>41.2</v>
       </c>
       <c r="M57" t="n">
-        <v>4.068</v>
+        <v>4.084</v>
       </c>
       <c r="N57" t="n">
-        <v>30.3</v>
+        <v>32.5</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -3396,16 +3381,16 @@
         <v>1401</v>
       </c>
       <c r="K58" t="n">
-        <v>4.316</v>
+        <v>4.362</v>
       </c>
       <c r="L58" t="n">
-        <v>71.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>4.442</v>
+        <v>4.489</v>
       </c>
       <c r="N58" t="n">
-        <v>73.2</v>
+        <v>80.2</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -3448,16 +3433,16 @@
         <v>656</v>
       </c>
       <c r="K59" t="n">
-        <v>3.801</v>
+        <v>3.772</v>
       </c>
       <c r="L59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M59" t="n">
-        <v>3.555</v>
+        <v>3.528</v>
       </c>
       <c r="N59" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -3500,16 +3485,16 @@
         <v>330</v>
       </c>
       <c r="K60" t="n">
-        <v>4.424</v>
+        <v>4.483</v>
       </c>
       <c r="L60" t="n">
-        <v>87</v>
+        <v>93.5</v>
       </c>
       <c r="M60" t="n">
-        <v>4.553</v>
+        <v>4.614</v>
       </c>
       <c r="N60" t="n">
-        <v>84.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -3555,13 +3540,13 @@
         <v>4.647</v>
       </c>
       <c r="L61" t="n">
-        <v>97.5</v>
+        <v>98</v>
       </c>
       <c r="M61" t="n">
         <v>4.611</v>
       </c>
       <c r="N61" t="n">
-        <v>90.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -3604,13 +3589,13 @@
         <v>95</v>
       </c>
       <c r="K62" t="n">
-        <v>3.782</v>
+        <v>3.72</v>
       </c>
       <c r="L62" t="n">
         <v>4</v>
       </c>
       <c r="M62" t="n">
-        <v>3.73</v>
+        <v>3.668</v>
       </c>
       <c r="N62" t="n">
         <v>9.6</v>
@@ -3656,16 +3641,16 @@
         <v>161</v>
       </c>
       <c r="K63" t="n">
-        <v>4.138</v>
+        <v>4.128</v>
       </c>
       <c r="L63" t="n">
-        <v>36.5</v>
+        <v>38.2</v>
       </c>
       <c r="M63" t="n">
-        <v>3.913</v>
+        <v>3.904</v>
       </c>
       <c r="N63" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -3708,16 +3693,16 @@
         <v>39</v>
       </c>
       <c r="K64" t="n">
-        <v>4.084</v>
+        <v>4.055</v>
       </c>
       <c r="L64" t="n">
-        <v>29.5</v>
+        <v>28.1</v>
       </c>
       <c r="M64" t="n">
-        <v>4.377</v>
+        <v>4.346</v>
       </c>
       <c r="N64" t="n">
-        <v>64.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -3756,16 +3741,16 @@
         <v>197</v>
       </c>
       <c r="K65" t="n">
-        <v>4.397</v>
+        <v>4.375</v>
       </c>
       <c r="L65" t="n">
-        <v>84</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M65" t="n">
-        <v>4.359</v>
+        <v>4.337</v>
       </c>
       <c r="N65" t="n">
-        <v>63.1</v>
+        <v>61.4</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -3811,13 +3796,13 @@
         <v>4.067</v>
       </c>
       <c r="L66" t="n">
-        <v>27.5</v>
+        <v>30.2</v>
       </c>
       <c r="M66" t="n">
-        <v>4.186</v>
+        <v>4.185</v>
       </c>
       <c r="N66" t="n">
-        <v>41.9</v>
+        <v>44.2</v>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -3860,16 +3845,16 @@
         <v>309</v>
       </c>
       <c r="K67" t="n">
-        <v>4.168</v>
+        <v>4.182</v>
       </c>
       <c r="L67" t="n">
-        <v>42</v>
+        <v>44.2</v>
       </c>
       <c r="M67" t="n">
-        <v>4.189</v>
+        <v>4.203</v>
       </c>
       <c r="N67" t="n">
-        <v>42.9</v>
+        <v>47.2</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -3912,16 +3897,16 @@
         <v>211</v>
       </c>
       <c r="K68" t="n">
-        <v>4.328</v>
+        <v>4.356</v>
       </c>
       <c r="L68" t="n">
-        <v>73.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="M68" t="n">
-        <v>4.498</v>
+        <v>4.528</v>
       </c>
       <c r="N68" t="n">
-        <v>80.3</v>
+        <v>82.7</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -3963,13 +3948,13 @@
         <v>4.25</v>
       </c>
       <c r="L69" t="n">
-        <v>52</v>
+        <v>53.8</v>
       </c>
       <c r="M69" t="n">
         <v>4.272</v>
       </c>
       <c r="N69" t="n">
-        <v>53.5</v>
+        <v>54.8</v>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -4008,16 +3993,16 @@
         <v>216</v>
       </c>
       <c r="K70" t="n">
-        <v>4.222</v>
+        <v>4.233</v>
       </c>
       <c r="L70" t="n">
-        <v>48.5</v>
+        <v>50.3</v>
       </c>
       <c r="M70" t="n">
-        <v>4.375</v>
+        <v>4.387</v>
       </c>
       <c r="N70" t="n">
-        <v>64.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -4063,13 +4048,13 @@
         <v>4.403</v>
       </c>
       <c r="L71" t="n">
-        <v>85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="M71" t="n">
-        <v>4.412</v>
+        <v>4.411</v>
       </c>
       <c r="N71" t="n">
-        <v>70.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -4112,16 +4097,16 @@
         <v>1939</v>
       </c>
       <c r="K72" t="n">
-        <v>4.229</v>
+        <v>4.238</v>
       </c>
       <c r="L72" t="n">
-        <v>49.5</v>
+        <v>50.8</v>
       </c>
       <c r="M72" t="n">
-        <v>4.035</v>
+        <v>4.043</v>
       </c>
       <c r="N72" t="n">
-        <v>27.8</v>
+        <v>29.4</v>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -4164,16 +4149,16 @@
         <v>365</v>
       </c>
       <c r="K73" t="n">
-        <v>3.884</v>
+        <v>3.86</v>
       </c>
       <c r="L73" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="M73" t="n">
-        <v>4.101</v>
+        <v>4.076</v>
       </c>
       <c r="N73" t="n">
-        <v>33.3</v>
+        <v>31</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -4216,16 +4201,16 @@
         <v>142</v>
       </c>
       <c r="K74" t="n">
-        <v>4.309</v>
+        <v>4.313</v>
       </c>
       <c r="L74" t="n">
-        <v>69.5</v>
+        <v>69.8</v>
       </c>
       <c r="M74" t="n">
-        <v>4.313</v>
+        <v>4.317</v>
       </c>
       <c r="N74" t="n">
-        <v>58.6</v>
+        <v>59.9</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -4268,16 +4253,16 @@
         <v>716</v>
       </c>
       <c r="K75" t="n">
-        <v>4.357</v>
+        <v>4.407</v>
       </c>
       <c r="L75" t="n">
-        <v>78</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>4.408</v>
+        <v>4.459</v>
       </c>
       <c r="N75" t="n">
-        <v>69.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -4316,16 +4301,16 @@
         <v>724</v>
       </c>
       <c r="K76" t="n">
-        <v>4.114</v>
+        <v>4.122</v>
       </c>
       <c r="L76" t="n">
-        <v>33.5</v>
+        <v>36.7</v>
       </c>
       <c r="M76" t="n">
-        <v>4.217</v>
+        <v>4.226</v>
       </c>
       <c r="N76" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -4368,13 +4353,13 @@
         <v>168</v>
       </c>
       <c r="K77" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="L77" t="n">
-        <v>37</v>
+        <v>27.6</v>
       </c>
       <c r="M77" t="n">
-        <v>3.525</v>
+        <v>3.448</v>
       </c>
       <c r="N77" t="n">
         <v>2.5</v>
@@ -4416,16 +4401,16 @@
         <v>370</v>
       </c>
       <c r="K78" t="n">
-        <v>4.454</v>
+        <v>4.431</v>
       </c>
       <c r="L78" t="n">
-        <v>90</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M78" t="n">
-        <v>4.506</v>
+        <v>4.483</v>
       </c>
       <c r="N78" t="n">
-        <v>80.8</v>
+        <v>78.7</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -4468,16 +4453,16 @@
         <v>329</v>
       </c>
       <c r="K79" t="n">
-        <v>4.277</v>
+        <v>4.275</v>
       </c>
       <c r="L79" t="n">
-        <v>60.5</v>
+        <v>59.3</v>
       </c>
       <c r="M79" t="n">
-        <v>4.299</v>
+        <v>4.296</v>
       </c>
       <c r="N79" t="n">
-        <v>56.6</v>
+        <v>57.9</v>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -4520,16 +4505,16 @@
         <v>1867</v>
       </c>
       <c r="K80" t="n">
-        <v>4.188</v>
+        <v>4.173</v>
       </c>
       <c r="L80" t="n">
-        <v>44.5</v>
+        <v>42.2</v>
       </c>
       <c r="M80" t="n">
-        <v>4.022</v>
+        <v>4.007</v>
       </c>
       <c r="N80" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -4572,16 +4557,16 @@
         <v>200</v>
       </c>
       <c r="K81" t="n">
-        <v>4.021</v>
+        <v>4.046</v>
       </c>
       <c r="L81" t="n">
-        <v>25.5</v>
+        <v>27.1</v>
       </c>
       <c r="M81" t="n">
-        <v>4.064</v>
+        <v>4.088</v>
       </c>
       <c r="N81" t="n">
-        <v>29.8</v>
+        <v>33</v>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -4624,16 +4609,16 @@
         <v>291</v>
       </c>
       <c r="K82" t="n">
-        <v>4.352</v>
+        <v>4.347</v>
       </c>
       <c r="L82" t="n">
-        <v>76.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="M82" t="n">
-        <v>4.223</v>
+        <v>4.219</v>
       </c>
       <c r="N82" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -4676,16 +4661,16 @@
         <v>1373</v>
       </c>
       <c r="K83" t="n">
-        <v>4.156</v>
+        <v>4.127</v>
       </c>
       <c r="L83" t="n">
-        <v>41</v>
+        <v>37.7</v>
       </c>
       <c r="M83" t="n">
-        <v>3.991</v>
+        <v>3.963</v>
       </c>
       <c r="N83" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -4731,13 +4716,13 @@
         <v>4.005</v>
       </c>
       <c r="L84" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="M84" t="n">
-        <v>4.488</v>
+        <v>4.489</v>
       </c>
       <c r="N84" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -4780,16 +4765,16 @@
         <v>189</v>
       </c>
       <c r="K85" t="n">
-        <v>4.289</v>
+        <v>4.295</v>
       </c>
       <c r="L85" t="n">
-        <v>64.5</v>
+        <v>66.3</v>
       </c>
       <c r="M85" t="n">
-        <v>4.256</v>
+        <v>4.262</v>
       </c>
       <c r="N85" t="n">
-        <v>52</v>
+        <v>53.8</v>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -4832,16 +4817,16 @@
         <v>458</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>4.197</v>
+        <v>4.248</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>45.5</v>
+        <v>53.3</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4.382</v>
+        <v>4.435</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>65.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -4891,13 +4876,13 @@
         <v>4.353</v>
       </c>
       <c r="L87" t="n">
-        <v>77</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M87" t="n">
-        <v>4.48</v>
+        <v>4.481</v>
       </c>
       <c r="N87" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -4940,16 +4925,16 @@
         <v>104</v>
       </c>
       <c r="K88" t="n">
-        <v>4.298</v>
+        <v>4.316</v>
       </c>
       <c r="L88" t="n">
-        <v>68</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>4.127</v>
+        <v>4.145</v>
       </c>
       <c r="N88" t="n">
-        <v>35.4</v>
+        <v>39.6</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -4992,16 +4977,16 @@
         <v>179</v>
       </c>
       <c r="K89" t="n">
-        <v>4.207</v>
+        <v>4.184</v>
       </c>
       <c r="L89" t="n">
-        <v>46.5</v>
+        <v>44.7</v>
       </c>
       <c r="M89" t="n">
-        <v>4.252</v>
+        <v>4.228</v>
       </c>
       <c r="N89" t="n">
-        <v>51.5</v>
+        <v>50.3</v>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
@@ -5044,16 +5029,16 @@
         <v>205</v>
       </c>
       <c r="K90" t="n">
-        <v>4.519</v>
+        <v>4.526</v>
       </c>
       <c r="L90" t="n">
-        <v>94.5</v>
+        <v>95</v>
       </c>
       <c r="M90" t="n">
-        <v>4.405</v>
+        <v>4.412</v>
       </c>
       <c r="N90" t="n">
-        <v>68.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -5096,16 +5081,16 @@
         <v>249</v>
       </c>
       <c r="K91" t="n">
-        <v>4.335</v>
+        <v>4.316</v>
       </c>
       <c r="L91" t="n">
-        <v>74.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M91" t="n">
-        <v>4.406</v>
+        <v>4.386</v>
       </c>
       <c r="N91" t="n">
-        <v>68.7</v>
+        <v>66</v>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -5148,16 +5133,16 @@
         <v>177</v>
       </c>
       <c r="K92" t="n">
-        <v>3.892</v>
+        <v>3.848</v>
       </c>
       <c r="L92" t="n">
-        <v>14</v>
+        <v>11.1</v>
       </c>
       <c r="M92" t="n">
-        <v>3.933</v>
+        <v>3.889</v>
       </c>
       <c r="N92" t="n">
-        <v>22.2</v>
+        <v>21.3</v>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -5200,16 +5185,16 @@
         <v>521</v>
       </c>
       <c r="K93" t="n">
-        <v>4.297</v>
+        <v>4.239</v>
       </c>
       <c r="L93" t="n">
-        <v>67.5</v>
+        <v>52.3</v>
       </c>
       <c r="M93" t="n">
-        <v>4.605</v>
+        <v>4.543</v>
       </c>
       <c r="N93" t="n">
-        <v>88.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -5252,16 +5237,16 @@
         <v>167</v>
       </c>
       <c r="K94" t="n">
-        <v>4.291</v>
+        <v>4.296</v>
       </c>
       <c r="L94" t="n">
-        <v>66</v>
+        <v>67.3</v>
       </c>
       <c r="M94" t="n">
-        <v>4.134</v>
+        <v>4.139</v>
       </c>
       <c r="N94" t="n">
-        <v>36.9</v>
+        <v>37.6</v>
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -5304,16 +5289,16 @@
         <v>222</v>
       </c>
       <c r="K95" t="n">
-        <v>4.324</v>
+        <v>4.304</v>
       </c>
       <c r="L95" t="n">
-        <v>72.5</v>
+        <v>68.8</v>
       </c>
       <c r="M95" t="n">
-        <v>4.264</v>
+        <v>4.244</v>
       </c>
       <c r="N95" t="n">
-        <v>52.5</v>
+        <v>51.8</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -5356,16 +5341,16 @@
         <v>231</v>
       </c>
       <c r="K96" t="n">
-        <v>4.72</v>
+        <v>4.736</v>
       </c>
       <c r="L96" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M96" t="n">
-        <v>4.679</v>
+        <v>4.695</v>
       </c>
       <c r="N96" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -5408,16 +5393,16 @@
         <v>315</v>
       </c>
       <c r="K97" t="n">
-        <v>4.37</v>
+        <v>4.352</v>
       </c>
       <c r="L97" t="n">
-        <v>80.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M97" t="n">
-        <v>4.416</v>
+        <v>4.398</v>
       </c>
       <c r="N97" t="n">
-        <v>71.7</v>
+        <v>68.5</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -5456,16 +5441,16 @@
         <v>334</v>
       </c>
       <c r="K98" t="n">
-        <v>4.266</v>
+        <v>4.257</v>
       </c>
       <c r="L98" t="n">
-        <v>58</v>
+        <v>55.3</v>
       </c>
       <c r="M98" t="n">
-        <v>4.391</v>
+        <v>4.381</v>
       </c>
       <c r="N98" t="n">
-        <v>66.7</v>
+        <v>65.5</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -5504,16 +5489,16 @@
         <v>138</v>
       </c>
       <c r="K99" t="n">
-        <v>4.069</v>
+        <v>4.081</v>
       </c>
       <c r="L99" t="n">
-        <v>28</v>
+        <v>31.7</v>
       </c>
       <c r="M99" t="n">
-        <v>4.09</v>
+        <v>4.102</v>
       </c>
       <c r="N99" t="n">
-        <v>32.3</v>
+        <v>33.5</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -5552,16 +5537,16 @@
         <v>444</v>
       </c>
       <c r="K100" t="n">
-        <v>4.299</v>
+        <v>4.282</v>
       </c>
       <c r="L100" t="n">
-        <v>68.5</v>
+        <v>62.3</v>
       </c>
       <c r="M100" t="n">
-        <v>4.462</v>
+        <v>4.444</v>
       </c>
       <c r="N100" t="n">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -5600,16 +5585,16 @@
         <v>208</v>
       </c>
       <c r="K101" t="n">
-        <v>4.383</v>
+        <v>4.385</v>
       </c>
       <c r="L101" t="n">
-        <v>81.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="M101" t="n">
-        <v>4.555</v>
+        <v>4.558</v>
       </c>
       <c r="N101" t="n">
-        <v>85.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
@@ -5648,16 +5633,16 @@
         <v>83</v>
       </c>
       <c r="K102" t="n">
-        <v>4.005</v>
+        <v>4.003</v>
       </c>
       <c r="L102" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="M102" t="n">
-        <v>3.846</v>
+        <v>3.843</v>
       </c>
       <c r="N102" t="n">
-        <v>14.6</v>
+        <v>16.8</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
@@ -5696,16 +5681,16 @@
         <v>326</v>
       </c>
       <c r="K103" t="n">
-        <v>4.313</v>
+        <v>4.302</v>
       </c>
       <c r="L103" t="n">
-        <v>70.5</v>
+        <v>68.3</v>
       </c>
       <c r="M103" t="n">
-        <v>4.579</v>
+        <v>4.567</v>
       </c>
       <c r="N103" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -5748,16 +5733,16 @@
         <v>254</v>
       </c>
       <c r="K104" t="n">
-        <v>4.14</v>
+        <v>4.082</v>
       </c>
       <c r="L104" t="n">
-        <v>37</v>
+        <v>32.2</v>
       </c>
       <c r="M104" t="n">
-        <v>4.049</v>
+        <v>3.992</v>
       </c>
       <c r="N104" t="n">
-        <v>28.8</v>
+        <v>26.4</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -5800,16 +5785,16 @@
         <v>1968</v>
       </c>
       <c r="K105" t="n">
-        <v>4.032</v>
+        <v>4.012</v>
       </c>
       <c r="L105" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="M105" t="n">
-        <v>3.872</v>
+        <v>3.853</v>
       </c>
       <c r="N105" t="n">
-        <v>17.2</v>
+        <v>18.8</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -5844,16 +5829,16 @@
         <v>218</v>
       </c>
       <c r="K106" t="n">
-        <v>4.228</v>
+        <v>4.197</v>
       </c>
       <c r="L106" t="n">
-        <v>49</v>
+        <v>46.7</v>
       </c>
       <c r="M106" t="n">
-        <v>4.282</v>
+        <v>4.251</v>
       </c>
       <c r="N106" t="n">
-        <v>56.1</v>
+        <v>52.8</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -5899,13 +5884,13 @@
         <v>4.614</v>
       </c>
       <c r="L107" t="n">
-        <v>96.5</v>
+        <v>97</v>
       </c>
       <c r="M107" t="n">
         <v>4.531</v>
       </c>
       <c r="N107" t="n">
-        <v>82.8</v>
+        <v>83.2</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -5944,16 +5929,16 @@
         <v>295</v>
       </c>
       <c r="K108" t="n">
-        <v>4.201</v>
+        <v>4.217</v>
       </c>
       <c r="L108" t="n">
-        <v>46</v>
+        <v>47.2</v>
       </c>
       <c r="M108" t="n">
-        <v>4.421</v>
+        <v>4.438</v>
       </c>
       <c r="N108" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
@@ -5992,16 +5977,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="n">
-        <v>4.211</v>
+        <v>4.196</v>
       </c>
       <c r="L109" t="n">
-        <v>47</v>
+        <v>46.2</v>
       </c>
       <c r="M109" t="n">
-        <v>4.22</v>
+        <v>4.204</v>
       </c>
       <c r="N109" t="n">
-        <v>48</v>
+        <v>47.7</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -6040,16 +6025,16 @@
         <v>344</v>
       </c>
       <c r="K110" t="n">
-        <v>3.87</v>
+        <v>3.832</v>
       </c>
       <c r="L110" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M110" t="n">
-        <v>3.878</v>
+        <v>3.84</v>
       </c>
       <c r="N110" t="n">
-        <v>17.7</v>
+        <v>15.2</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -6088,16 +6073,16 @@
         <v>293</v>
       </c>
       <c r="K111" t="n">
-        <v>3.871</v>
+        <v>3.847</v>
       </c>
       <c r="L111" t="n">
-        <v>11.5</v>
+        <v>10.6</v>
       </c>
       <c r="M111" t="n">
-        <v>4.074</v>
+        <v>4.048</v>
       </c>
       <c r="N111" t="n">
-        <v>30.8</v>
+        <v>29.9</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -6132,16 +6117,16 @@
         <v>354</v>
       </c>
       <c r="K112" t="n">
-        <v>4.264</v>
+        <v>4.231</v>
       </c>
       <c r="L112" t="n">
-        <v>55.5</v>
+        <v>49.2</v>
       </c>
       <c r="M112" t="n">
-        <v>4.432</v>
+        <v>4.397</v>
       </c>
       <c r="N112" t="n">
-        <v>72.7</v>
+        <v>68</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -6193,7 +6178,7 @@
         <v>4.587</v>
       </c>
       <c r="N113" t="n">
-        <v>87.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -6236,16 +6221,16 @@
         <v>212</v>
       </c>
       <c r="K114" t="n">
-        <v>4.265</v>
+        <v>4.281</v>
       </c>
       <c r="L114" t="n">
-        <v>57.5</v>
+        <v>61.3</v>
       </c>
       <c r="M114" t="n">
-        <v>4.335</v>
+        <v>4.351</v>
       </c>
       <c r="N114" t="n">
-        <v>60.6</v>
+        <v>62.9</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -6288,16 +6273,16 @@
         <v>361</v>
       </c>
       <c r="K115" t="n">
-        <v>4.492</v>
+        <v>4.489</v>
       </c>
       <c r="L115" t="n">
-        <v>93.5</v>
+        <v>94</v>
       </c>
       <c r="M115" t="n">
-        <v>4.411</v>
+        <v>4.408</v>
       </c>
       <c r="N115" t="n">
-        <v>70.2</v>
+        <v>69.5</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -6332,16 +6317,16 @@
         <v>127</v>
       </c>
       <c r="K116" t="n">
-        <v>4.401</v>
+        <v>4.384</v>
       </c>
       <c r="L116" t="n">
-        <v>84.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M116" t="n">
-        <v>4.473</v>
+        <v>4.456</v>
       </c>
       <c r="N116" t="n">
-        <v>77.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -6384,16 +6369,16 @@
         <v>298</v>
       </c>
       <c r="K117" t="n">
-        <v>4.264</v>
+        <v>4.262</v>
       </c>
       <c r="L117" t="n">
-        <v>55.5</v>
+        <v>56.3</v>
       </c>
       <c r="M117" t="n">
-        <v>4.17</v>
+        <v>4.168</v>
       </c>
       <c r="N117" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -6432,16 +6417,16 @@
         <v>370</v>
       </c>
       <c r="K118" t="n">
-        <v>4.277</v>
+        <v>4.231</v>
       </c>
       <c r="L118" t="n">
-        <v>60.5</v>
+        <v>49.7</v>
       </c>
       <c r="M118" t="n">
-        <v>4.2</v>
+        <v>4.155</v>
       </c>
       <c r="N118" t="n">
-        <v>44.4</v>
+        <v>40.6</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
@@ -6480,16 +6465,16 @@
         <v>166</v>
       </c>
       <c r="K119" t="n">
-        <v>4.262</v>
+        <v>4.239</v>
       </c>
       <c r="L119" t="n">
-        <v>55</v>
+        <v>52.8</v>
       </c>
       <c r="M119" t="n">
-        <v>4.312</v>
+        <v>4.289</v>
       </c>
       <c r="N119" t="n">
-        <v>58.1</v>
+        <v>57.4</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -6532,16 +6517,16 @@
         <v>474</v>
       </c>
       <c r="K120" t="n">
-        <v>3.885</v>
+        <v>3.813</v>
       </c>
       <c r="L120" t="n">
-        <v>13.5</v>
+        <v>6.5</v>
       </c>
       <c r="M120" t="n">
-        <v>4.089</v>
+        <v>4.013</v>
       </c>
       <c r="N120" t="n">
-        <v>31.8</v>
+        <v>27.9</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -6580,16 +6565,16 @@
         <v>576</v>
       </c>
       <c r="K121" t="n">
-        <v>4.367</v>
+        <v>4.344</v>
       </c>
       <c r="L121" t="n">
-        <v>79</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M121" t="n">
-        <v>4.545</v>
+        <v>4.522</v>
       </c>
       <c r="N121" t="n">
-        <v>84.3</v>
+        <v>81.7</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
@@ -6628,16 +6613,16 @@
         <v>62</v>
       </c>
       <c r="K122" t="n">
-        <v>3.867</v>
+        <v>3.846</v>
       </c>
       <c r="L122" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M122" t="n">
-        <v>3.782</v>
+        <v>3.761</v>
       </c>
       <c r="N122" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
@@ -6680,16 +6665,16 @@
         <v>145</v>
       </c>
       <c r="K123" t="n">
-        <v>4.135</v>
+        <v>4.123</v>
       </c>
       <c r="L123" t="n">
-        <v>35.5</v>
+        <v>37.2</v>
       </c>
       <c r="M123" t="n">
-        <v>4.156</v>
+        <v>4.145</v>
       </c>
       <c r="N123" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -6724,16 +6709,16 @@
         <v>143</v>
       </c>
       <c r="K124" t="n">
-        <v>4.143</v>
+        <v>4.093</v>
       </c>
       <c r="L124" t="n">
-        <v>39</v>
+        <v>34.2</v>
       </c>
       <c r="M124" t="n">
-        <v>4.192</v>
+        <v>4.14</v>
       </c>
       <c r="N124" t="n">
-        <v>43.9</v>
+        <v>38.1</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -6768,16 +6753,16 @@
         <v>112</v>
       </c>
       <c r="K125" t="n">
-        <v>4.115</v>
+        <v>4.066</v>
       </c>
       <c r="L125" t="n">
-        <v>34.5</v>
+        <v>29.6</v>
       </c>
       <c r="M125" t="n">
-        <v>4.235</v>
+        <v>4.185</v>
       </c>
       <c r="N125" t="n">
-        <v>49.5</v>
+        <v>43.7</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -6820,16 +6805,16 @@
         <v>157</v>
       </c>
       <c r="K126" t="n">
-        <v>4.26</v>
+        <v>4.268</v>
       </c>
       <c r="L126" t="n">
-        <v>54</v>
+        <v>58.3</v>
       </c>
       <c r="M126" t="n">
-        <v>4.448</v>
+        <v>4.456</v>
       </c>
       <c r="N126" t="n">
-        <v>74.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -6868,16 +6853,16 @@
         <v>269</v>
       </c>
       <c r="K127" t="n">
-        <v>4.349</v>
+        <v>4.33</v>
       </c>
       <c r="L127" t="n">
-        <v>76</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M127" t="n">
-        <v>4.278</v>
+        <v>4.259</v>
       </c>
       <c r="N127" t="n">
-        <v>55.1</v>
+        <v>53.3</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -6912,16 +6897,16 @@
         <v>93</v>
       </c>
       <c r="K128" t="n">
-        <v>4.095</v>
+        <v>4.091</v>
       </c>
       <c r="L128" t="n">
-        <v>30.5</v>
+        <v>33.7</v>
       </c>
       <c r="M128" t="n">
-        <v>4.021</v>
+        <v>4.017</v>
       </c>
       <c r="N128" t="n">
-        <v>26.3</v>
+        <v>28.4</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -6964,16 +6949,16 @@
         <v>809</v>
       </c>
       <c r="K129" t="n">
-        <v>4.053</v>
+        <v>4.027</v>
       </c>
       <c r="L129" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="M129" t="n">
-        <v>4.16</v>
+        <v>4.134</v>
       </c>
       <c r="N129" t="n">
-        <v>39.4</v>
+        <v>37.1</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -7008,16 +6993,16 @@
         <v>92</v>
       </c>
       <c r="K130" t="n">
-        <v>3.697</v>
+        <v>3.685</v>
       </c>
       <c r="L130" t="n">
         <v>3.5</v>
       </c>
       <c r="M130" t="n">
-        <v>3.805</v>
+        <v>3.793</v>
       </c>
       <c r="N130" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -7052,16 +7037,16 @@
         <v>477</v>
       </c>
       <c r="K131" t="n">
-        <v>3.82</v>
+        <v>3.769</v>
       </c>
       <c r="L131" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M131" t="n">
-        <v>3.869</v>
+        <v>3.818</v>
       </c>
       <c r="N131" t="n">
-        <v>16.7</v>
+        <v>13.7</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -7100,16 +7085,16 @@
         <v>1007</v>
       </c>
       <c r="K132" t="n">
-        <v>3.864</v>
+        <v>3.851</v>
       </c>
       <c r="L132" t="n">
-        <v>7.5</v>
+        <v>11.6</v>
       </c>
       <c r="M132" t="n">
-        <v>4.33</v>
+        <v>4.316</v>
       </c>
       <c r="N132" t="n">
-        <v>59.6</v>
+        <v>59.4</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
@@ -7152,16 +7137,16 @@
         <v>376</v>
       </c>
       <c r="K133" t="n">
-        <v>4.178</v>
+        <v>4.189</v>
       </c>
       <c r="L133" t="n">
-        <v>43</v>
+        <v>45.7</v>
       </c>
       <c r="M133" t="n">
-        <v>4.336</v>
+        <v>4.347</v>
       </c>
       <c r="N133" t="n">
-        <v>61.1</v>
+        <v>62.4</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
@@ -7204,16 +7189,16 @@
         <v>607</v>
       </c>
       <c r="K134" t="n">
-        <v>4.386</v>
+        <v>4.378</v>
       </c>
       <c r="L134" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M134" t="n">
-        <v>4.656</v>
+        <v>4.648</v>
       </c>
       <c r="N134" t="n">
-        <v>93.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -7256,16 +7241,16 @@
         <v>395</v>
       </c>
       <c r="K135" t="n">
-        <v>3.906</v>
+        <v>3.837</v>
       </c>
       <c r="L135" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="M135" t="n">
-        <v>4.281</v>
+        <v>4.205</v>
       </c>
       <c r="N135" t="n">
-        <v>55.6</v>
+        <v>48.2</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -7308,16 +7293,16 @@
         <v>80</v>
       </c>
       <c r="K136" t="n">
-        <v>4.136</v>
+        <v>4.081</v>
       </c>
       <c r="L136" t="n">
-        <v>36</v>
+        <v>31.2</v>
       </c>
       <c r="M136" t="n">
-        <v>3.985</v>
+        <v>3.932</v>
       </c>
       <c r="N136" t="n">
-        <v>24.7</v>
+        <v>23.9</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -7360,16 +7345,16 @@
         <v>209</v>
       </c>
       <c r="K137" t="n">
-        <v>4.479</v>
+        <v>4.465</v>
       </c>
       <c r="L137" t="n">
         <v>92</v>
       </c>
       <c r="M137" t="n">
-        <v>4.61</v>
+        <v>4.596</v>
       </c>
       <c r="N137" t="n">
-        <v>90.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
@@ -7412,13 +7397,13 @@
         <v>128</v>
       </c>
       <c r="K138" t="n">
-        <v>3.783</v>
+        <v>3.746</v>
       </c>
       <c r="L138" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M138" t="n">
-        <v>3.362</v>
+        <v>3.329</v>
       </c>
       <c r="N138" t="n">
         <v>1</v>
@@ -7464,16 +7449,16 @@
         <v>205</v>
       </c>
       <c r="K139" t="n">
-        <v>4.438</v>
+        <v>4.434</v>
       </c>
       <c r="L139" t="n">
-        <v>88.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="M139" t="n">
-        <v>4.365</v>
+        <v>4.361</v>
       </c>
       <c r="N139" t="n">
-        <v>63.6</v>
+        <v>64</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -7508,16 +7493,16 @@
         <v>186</v>
       </c>
       <c r="K140" t="n">
-        <v>4.271</v>
+        <v>4.276</v>
       </c>
       <c r="L140" t="n">
-        <v>59</v>
+        <v>59.8</v>
       </c>
       <c r="M140" t="n">
-        <v>4.101</v>
+        <v>4.106</v>
       </c>
       <c r="N140" t="n">
-        <v>33.3</v>
+        <v>34</v>
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -7560,16 +7545,16 @@
         <v>278</v>
       </c>
       <c r="K141" t="n">
-        <v>3.52</v>
+        <v>3.464</v>
       </c>
       <c r="L141" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M141" t="n">
-        <v>3.599</v>
+        <v>3.542</v>
       </c>
       <c r="N141" t="n">
-        <v>7.1</v>
+        <v>5.1</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -7612,16 +7597,16 @@
         <v>185</v>
       </c>
       <c r="K142" t="n">
-        <v>4.171</v>
+        <v>4.163</v>
       </c>
       <c r="L142" t="n">
-        <v>42.5</v>
+        <v>41.7</v>
       </c>
       <c r="M142" t="n">
-        <v>4.131</v>
+        <v>4.124</v>
       </c>
       <c r="N142" t="n">
-        <v>36.4</v>
+        <v>35.5</v>
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -7664,16 +7649,16 @@
         <v>618</v>
       </c>
       <c r="K143" t="n">
-        <v>4.323</v>
+        <v>4.384</v>
       </c>
       <c r="L143" t="n">
-        <v>72</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="M143" t="n">
-        <v>4.606</v>
+        <v>4.672</v>
       </c>
       <c r="N143" t="n">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
@@ -7708,16 +7693,16 @@
         <v>74</v>
       </c>
       <c r="K144" t="n">
-        <v>4.282</v>
+        <v>4.263</v>
       </c>
       <c r="L144" t="n">
-        <v>62</v>
+        <v>56.8</v>
       </c>
       <c r="M144" t="n">
-        <v>4.205</v>
+        <v>4.186</v>
       </c>
       <c r="N144" t="n">
-        <v>46</v>
+        <v>44.7</v>
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -7760,16 +7745,16 @@
         <v>137</v>
       </c>
       <c r="K145" t="n">
-        <v>4.189</v>
+        <v>4.175</v>
       </c>
       <c r="L145" t="n">
-        <v>45</v>
+        <v>42.7</v>
       </c>
       <c r="M145" t="n">
-        <v>4.341</v>
+        <v>4.326</v>
       </c>
       <c r="N145" t="n">
-        <v>61.6</v>
+        <v>60.4</v>
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -7812,16 +7797,16 @@
         <v>238</v>
       </c>
       <c r="K146" t="n">
-        <v>4.478</v>
+        <v>4.463</v>
       </c>
       <c r="L146" t="n">
         <v>91.5</v>
       </c>
       <c r="M146" t="n">
-        <v>4.483</v>
+        <v>4.467</v>
       </c>
       <c r="N146" t="n">
-        <v>78.8</v>
+        <v>77.2</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -7860,16 +7845,16 @@
         <v>214</v>
       </c>
       <c r="K147" t="n">
-        <v>4.42</v>
+        <v>4.413</v>
       </c>
       <c r="L147" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M147" t="n">
-        <v>4.492</v>
+        <v>4.485</v>
       </c>
       <c r="N147" t="n">
-        <v>79.8</v>
+        <v>79.2</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -7912,16 +7897,16 @@
         <v>473</v>
       </c>
       <c r="K148" t="n">
-        <v>4.286</v>
+        <v>4.281</v>
       </c>
       <c r="L148" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="M148" t="n">
+        <v>4.351</v>
+      </c>
+      <c r="N148" t="n">
         <v>63.5</v>
-      </c>
-      <c r="M148" t="n">
-        <v>4.356</v>
-      </c>
-      <c r="N148" t="n">
-        <v>62.6</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -7964,16 +7949,16 @@
         <v>284</v>
       </c>
       <c r="K149" t="n">
-        <v>4.103</v>
+        <v>4.106</v>
       </c>
       <c r="L149" t="n">
-        <v>31.5</v>
+        <v>35.2</v>
       </c>
       <c r="M149" t="n">
-        <v>4.17</v>
+        <v>4.173</v>
       </c>
       <c r="N149" t="n">
-        <v>40.9</v>
+        <v>42.6</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -8016,16 +8001,16 @@
         <v>654</v>
       </c>
       <c r="K150" t="n">
-        <v>4.276</v>
+        <v>4.309</v>
       </c>
       <c r="L150" t="n">
-        <v>60</v>
+        <v>69.3</v>
       </c>
       <c r="M150" t="n">
-        <v>4.268</v>
+        <v>4.3</v>
       </c>
       <c r="N150" t="n">
-        <v>53</v>
+        <v>58.4</v>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -8068,16 +8053,16 @@
         <v>219</v>
       </c>
       <c r="K151" t="n">
-        <v>4.38</v>
+        <v>4.353</v>
       </c>
       <c r="L151" t="n">
-        <v>81</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M151" t="n">
-        <v>4.452</v>
+        <v>4.424</v>
       </c>
       <c r="N151" t="n">
-        <v>74.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -8120,16 +8105,16 @@
         <v>67</v>
       </c>
       <c r="K152" t="n">
-        <v>3.943</v>
+        <v>3.922</v>
       </c>
       <c r="L152" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="M152" t="n">
-        <v>4.008</v>
+        <v>3.986</v>
       </c>
       <c r="N152" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -8146,7 +8131,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Queens (Long Island City)</t>
+          <t>Queens — Long Island City</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -8175,13 +8160,13 @@
         <v>4.441</v>
       </c>
       <c r="L153" t="n">
-        <v>89</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="M153" t="n">
         <v>4.407</v>
       </c>
       <c r="N153" t="n">
-        <v>69.2</v>
+        <v>69</v>
       </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -8198,7 +8183,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg)</t>
+          <t>Brooklyn — Williamsburg</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -8227,13 +8212,13 @@
         <v>4.446</v>
       </c>
       <c r="L154" t="n">
-        <v>89.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="M154" t="n">
         <v>4.455</v>
       </c>
       <c r="N154" t="n">
-        <v>75.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -8250,7 +8235,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Manhattan (Lower East Side)</t>
+          <t>Manhattan — Lower East Side</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -8279,13 +8264,13 @@
         <v>4.286</v>
       </c>
       <c r="L155" t="n">
-        <v>63.5</v>
+        <v>63.8</v>
       </c>
       <c r="M155" t="n">
         <v>4.526</v>
       </c>
       <c r="N155" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
@@ -8302,7 +8287,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East (Andaz 5th Avenue))</t>
+          <t>Manhattan — Midtown East (Andaz 5th Avenue)</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -8328,13 +8313,13 @@
         <v>88</v>
       </c>
       <c r="K156" t="n">
-        <v>4.312</v>
+        <v>4.259</v>
       </c>
       <c r="L156" t="n">
-        <v>70</v>
+        <v>55.8</v>
       </c>
       <c r="M156" t="n">
-        <v>3.71</v>
+        <v>3.664</v>
       </c>
       <c r="N156" t="n">
         <v>9.1</v>
@@ -8354,7 +8339,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca)</t>
+          <t>Manhattan — Tribeca</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -8383,13 +8368,13 @@
         <v>3.987</v>
       </c>
       <c r="L157" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="M157" t="n">
-        <v>3.578</v>
+        <v>3.579</v>
       </c>
       <c r="N157" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -8406,7 +8391,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Manhattan (Chinatown)</t>
+          <t>Manhattan — Chinatown</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -8432,16 +8417,16 @@
         <v>52</v>
       </c>
       <c r="K158" t="n">
-        <v>4.277</v>
+        <v>4.297</v>
       </c>
       <c r="L158" t="n">
-        <v>60.5</v>
+        <v>67.8</v>
       </c>
       <c r="M158" t="n">
-        <v>3.832</v>
+        <v>3.85</v>
       </c>
       <c r="N158" t="n">
-        <v>13.6</v>
+        <v>18.3</v>
       </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -8458,7 +8443,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Manhattan (East Village)</t>
+          <t>Manhattan — East Village</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -8484,16 +8469,16 @@
         <v>28</v>
       </c>
       <c r="K159" t="n">
-        <v>4.109</v>
+        <v>4.084</v>
       </c>
       <c r="L159" t="n">
-        <v>32.5</v>
+        <v>33.2</v>
       </c>
       <c r="M159" t="n">
-        <v>3.946</v>
+        <v>3.922</v>
       </c>
       <c r="N159" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
@@ -8510,7 +8495,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East (Waldorf Astoria))</t>
+          <t>Manhattan — Midtown East (Waldorf Astoria)</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -8562,7 +8547,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East (37th floor, GM Bldg))</t>
+          <t>Manhattan — Midtown East (37th floor, GM Bldg)</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -8591,13 +8576,13 @@
         <v>4.436</v>
       </c>
       <c r="L161" t="n">
-        <v>88</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M161" t="n">
         <v>3.862</v>
       </c>
       <c r="N161" t="n">
-        <v>15.2</v>
+        <v>20.3</v>
       </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
@@ -8614,7 +8599,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Manhattan (Lower East Side)</t>
+          <t>Manhattan — Lower East Side</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -8643,13 +8628,13 @@
         <v>3.866</v>
       </c>
       <c r="L162" t="n">
-        <v>9.5</v>
+        <v>14.6</v>
       </c>
       <c r="M162" t="n">
         <v>3.573</v>
       </c>
       <c r="N162" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -8666,7 +8651,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg)</t>
+          <t>Brooklyn — Williamsburg</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -8695,13 +8680,13 @@
         <v>4.178</v>
       </c>
       <c r="L163" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="M163" t="n">
         <v>3.908</v>
       </c>
       <c r="N163" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
@@ -8718,7 +8703,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Brooklyn (Williamsburg)</t>
+          <t>Brooklyn — Williamsburg</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -8747,13 +8732,13 @@
         <v>4.414</v>
       </c>
       <c r="L164" t="n">
-        <v>86</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="M164" t="n">
         <v>4.393</v>
       </c>
       <c r="N164" t="n">
-        <v>67.2</v>
+        <v>67.5</v>
       </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -8770,7 +8755,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side (Carnegie Hill))</t>
+          <t>Manhattan — Upper East Side (Carnegie Hill)</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -8799,13 +8784,13 @@
         <v>4.283</v>
       </c>
       <c r="L165" t="n">
-        <v>62.5</v>
+        <v>63.3</v>
       </c>
       <c r="M165" t="n">
         <v>4.127</v>
       </c>
       <c r="N165" t="n">
-        <v>35.4</v>
+        <v>36.5</v>
       </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
@@ -8822,7 +8807,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Brooklyn (Fort Greene)</t>
+          <t>Brooklyn — Fort Greene</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -8848,16 +8833,16 @@
         <v>133</v>
       </c>
       <c r="K166" t="n">
-        <v>4.308</v>
+        <v>4.337</v>
       </c>
       <c r="L166" t="n">
-        <v>69</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M166" t="n">
-        <v>4.098</v>
+        <v>4.126</v>
       </c>
       <c r="N166" t="n">
-        <v>32.8</v>
+        <v>36</v>
       </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -8874,7 +8859,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca)</t>
+          <t>Manhattan — Tribeca</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -8903,7 +8888,7 @@
         <v>3.966</v>
       </c>
       <c r="L167" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="M167" t="n">
         <v>3.432</v>
@@ -8926,7 +8911,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side)</t>
+          <t>Manhattan — Upper East Side</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -8952,16 +8937,16 @@
         <v>462</v>
       </c>
       <c r="K168" t="n">
-        <v>4.296</v>
+        <v>4.331</v>
       </c>
       <c r="L168" t="n">
-        <v>66.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M168" t="n">
-        <v>4.169</v>
+        <v>4.203</v>
       </c>
       <c r="N168" t="n">
-        <v>39.9</v>
+        <v>46.7</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -8978,7 +8963,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Manhattan (Chinatown)</t>
+          <t>Manhattan — Chinatown</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -9004,16 +8989,16 @@
         <v>185</v>
       </c>
       <c r="K169" t="n">
-        <v>4.02</v>
+        <v>4.021</v>
       </c>
       <c r="L169" t="n">
-        <v>24.5</v>
+        <v>25.6</v>
       </c>
       <c r="M169" t="n">
-        <v>3.532</v>
+        <v>3.533</v>
       </c>
       <c r="N169" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -9030,7 +9015,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca)</t>
+          <t>Manhattan — Tribeca</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -9056,13 +9041,13 @@
         <v>241</v>
       </c>
       <c r="K170" t="n">
-        <v>4.314</v>
+        <v>4.271</v>
       </c>
       <c r="L170" t="n">
-        <v>71</v>
+        <v>58.8</v>
       </c>
       <c r="M170" t="n">
-        <v>3.688</v>
+        <v>3.651</v>
       </c>
       <c r="N170" t="n">
         <v>8.6</v>
@@ -9082,7 +9067,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Manhattan (Union Square)</t>
+          <t>Manhattan — Union Square</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -9108,16 +9093,16 @@
         <v>383</v>
       </c>
       <c r="K171" t="n">
-        <v>4.268</v>
+        <v>4.252</v>
       </c>
       <c r="L171" t="n">
-        <v>58.5</v>
+        <v>54.3</v>
       </c>
       <c r="M171" t="n">
-        <v>3.864</v>
+        <v>3.85</v>
       </c>
       <c r="N171" t="n">
-        <v>15.7</v>
+        <v>17.8</v>
       </c>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -9134,7 +9119,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan — Midtown East</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -9163,7 +9148,7 @@
         <v>4.02</v>
       </c>
       <c r="L172" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="M172" t="n">
         <v>3.602</v>
@@ -9186,7 +9171,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Manhattan (Tribeca)</t>
+          <t>Manhattan — Tribeca</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -9215,13 +9200,13 @@
         <v>4.083</v>
       </c>
       <c r="L173" t="n">
-        <v>29</v>
+        <v>32.7</v>
       </c>
       <c r="M173" t="n">
-        <v>3.554</v>
+        <v>3.555</v>
       </c>
       <c r="N173" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
@@ -9238,7 +9223,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Manhattan (Columbus Circle)</t>
+          <t>Manhattan — Columbus Circle</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -9267,7 +9252,7 @@
         <v>3.93</v>
       </c>
       <c r="L174" t="n">
-        <v>17</v>
+        <v>18.8</v>
       </c>
       <c r="M174" t="n">
         <v>3.138</v>
@@ -9290,7 +9275,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Manhattan (Columbus Circle)</t>
+          <t>Manhattan — Columbus Circle</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -9319,13 +9304,13 @@
         <v>3.93</v>
       </c>
       <c r="L175" t="n">
-        <v>17</v>
+        <v>18.8</v>
       </c>
       <c r="M175" t="n">
         <v>3.533</v>
       </c>
       <c r="N175" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
@@ -9342,7 +9327,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Manhattan (Upper East Side)</t>
+          <t>Manhattan — Upper East Side</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -9371,7 +9356,7 @@
         <v>3.845</v>
       </c>
       <c r="L176" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="M176" t="n">
         <v>3.445</v>
@@ -9394,7 +9379,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown)</t>
+          <t>Manhattan — Midtown</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -9423,7 +9408,7 @@
         <v>3.897</v>
       </c>
       <c r="L177" t="n">
-        <v>14.5</v>
+        <v>16.1</v>
       </c>
       <c r="M177" t="n">
         <v>3.636</v>
@@ -9446,7 +9431,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens — Flushing</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -9475,13 +9460,13 @@
         <v>4.264</v>
       </c>
       <c r="L178" t="n">
-        <v>55.5</v>
+        <v>57.5</v>
       </c>
       <c r="M178" t="n">
         <v>4.227</v>
       </c>
       <c r="N178" t="n">
-        <v>49</v>
+        <v>49.7</v>
       </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
@@ -9498,7 +9483,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens — Flushing</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -9527,13 +9512,13 @@
         <v>3.906</v>
       </c>
       <c r="L179" t="n">
-        <v>15.5</v>
+        <v>17.1</v>
       </c>
       <c r="M179" t="n">
         <v>3.751</v>
       </c>
       <c r="N179" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
@@ -9550,7 +9535,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens — Flushing</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -9579,13 +9564,13 @@
         <v>3.973</v>
       </c>
       <c r="L180" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="M180" t="n">
         <v>3.828</v>
       </c>
       <c r="N180" t="n">
-        <v>13.1</v>
+        <v>14.7</v>
       </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -9602,7 +9587,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens — Flushing</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -9631,13 +9616,13 @@
         <v>4.363</v>
       </c>
       <c r="L181" t="n">
-        <v>78.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M181" t="n">
-        <v>4.632</v>
+        <v>4.631</v>
       </c>
       <c r="N181" t="n">
-        <v>91.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -9654,7 +9639,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens — Flushing</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -9680,16 +9665,16 @@
         <v>2093</v>
       </c>
       <c r="K182" t="n">
-        <v>4.255</v>
+        <v>4.295</v>
       </c>
       <c r="L182" t="n">
-        <v>53.5</v>
+        <v>66.8</v>
       </c>
       <c r="M182" t="n">
-        <v>4.351</v>
+        <v>4.392</v>
       </c>
       <c r="N182" t="n">
-        <v>62.1</v>
+        <v>67</v>
       </c>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -9706,7 +9691,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens — Flushing</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -9735,13 +9720,13 @@
         <v>4.264</v>
       </c>
       <c r="L183" t="n">
-        <v>55.5</v>
+        <v>57.5</v>
       </c>
       <c r="M183" t="n">
         <v>4.273</v>
       </c>
       <c r="N183" t="n">
-        <v>54</v>
+        <v>55.3</v>
       </c>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
@@ -9758,7 +9743,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Queens (Long Island City)</t>
+          <t>Queens — Long Island City</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -9787,13 +9772,13 @@
         <v>4.353</v>
       </c>
       <c r="L184" t="n">
-        <v>77</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="M184" t="n">
-        <v>4.24</v>
+        <v>4.241</v>
       </c>
       <c r="N184" t="n">
-        <v>50.5</v>
+        <v>51.3</v>
       </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
@@ -9810,7 +9795,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Queens (Long Island City)</t>
+          <t>Queens — Long Island City</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -9839,13 +9824,13 @@
         <v>4.218</v>
       </c>
       <c r="L185" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="M185" t="n">
         <v>3.977</v>
       </c>
       <c r="N185" t="n">
-        <v>24.2</v>
+        <v>25.4</v>
       </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
@@ -9862,7 +9847,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Queens (Long Island City)</t>
+          <t>Queens — Long Island City</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -9888,16 +9873,16 @@
         <v>665</v>
       </c>
       <c r="K186" t="n">
-        <v>4.113</v>
+        <v>4.149</v>
       </c>
       <c r="L186" t="n">
-        <v>33</v>
+        <v>39.7</v>
       </c>
       <c r="M186" t="n">
-        <v>4.639</v>
+        <v>4.679</v>
       </c>
       <c r="N186" t="n">
-        <v>92.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -9914,7 +9899,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Queens (Long Island City)</t>
+          <t>Queens — Long Island City</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -9943,13 +9928,13 @@
         <v>4.238</v>
       </c>
       <c r="L187" t="n">
-        <v>50.5</v>
+        <v>51.3</v>
       </c>
       <c r="M187" t="n">
         <v>4.561</v>
       </c>
       <c r="N187" t="n">
-        <v>85.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
@@ -9966,7 +9951,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Brooklyn (Bushwick)</t>
+          <t>Brooklyn — Bushwick</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -9992,16 +9977,16 @@
         <v>476</v>
       </c>
       <c r="K188" t="n">
-        <v>4.114</v>
+        <v>4.116</v>
       </c>
       <c r="L188" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="M188" t="n">
-        <v>4.33</v>
+        <v>4.332</v>
       </c>
       <c r="N188" t="n">
-        <v>59.6</v>
+        <v>60.9</v>
       </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
@@ -10047,13 +10032,13 @@
         <v>3.865</v>
       </c>
       <c r="L189" t="n">
-        <v>8</v>
+        <v>14.1</v>
       </c>
       <c r="M189" t="n">
         <v>3.737</v>
       </c>
       <c r="N189" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
@@ -10099,13 +10084,13 @@
         <v>4.394</v>
       </c>
       <c r="L190" t="n">
-        <v>83.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M190" t="n">
-        <v>4.567</v>
+        <v>4.566</v>
       </c>
       <c r="N190" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -10151,13 +10136,13 @@
         <v>4.716</v>
       </c>
       <c r="L191" t="n">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="M191" t="n">
         <v>4.635</v>
       </c>
       <c r="N191" t="n">
-        <v>91.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -10203,13 +10188,13 @@
         <v>4.481</v>
       </c>
       <c r="L192" t="n">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="M192" t="n">
-        <v>4.853</v>
+        <v>4.854</v>
       </c>
       <c r="N192" t="n">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
@@ -10255,13 +10240,13 @@
         <v>4.409</v>
       </c>
       <c r="L193" t="n">
-        <v>85.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M193" t="n">
-        <v>4.582</v>
+        <v>4.583</v>
       </c>
       <c r="N193" t="n">
-        <v>87.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
@@ -10307,13 +10292,13 @@
         <v>4.711</v>
       </c>
       <c r="L194" t="n">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="M194" t="n">
         <v>4.975</v>
       </c>
       <c r="N194" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
@@ -10359,13 +10344,13 @@
         <v>4.289</v>
       </c>
       <c r="L195" t="n">
-        <v>64.5</v>
+        <v>65.3</v>
       </c>
       <c r="M195" t="n">
         <v>4.606</v>
       </c>
       <c r="N195" t="n">
-        <v>88.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
@@ -10411,13 +10396,13 @@
         <v>4.481</v>
       </c>
       <c r="L196" t="n">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="M196" t="n">
         <v>4.657</v>
       </c>
       <c r="N196" t="n">
-        <v>93.90000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
@@ -10463,13 +10448,13 @@
         <v>4.367</v>
       </c>
       <c r="L197" t="n">
-        <v>79</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="M197" t="n">
         <v>4.942</v>
       </c>
       <c r="N197" t="n">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
@@ -10515,13 +10500,13 @@
         <v>3.904</v>
       </c>
       <c r="L198" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
       <c r="M198" t="n">
         <v>4.201</v>
       </c>
       <c r="N198" t="n">
-        <v>44.9</v>
+        <v>46.2</v>
       </c>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
@@ -10573,7 +10558,7 @@
         <v>4.169</v>
       </c>
       <c r="N199" t="n">
-        <v>39.9</v>
+        <v>41.6</v>
       </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
@@ -10622,10 +10607,10 @@
         <v>0.5</v>
       </c>
       <c r="M200" t="n">
-        <v>3.557</v>
+        <v>3.558</v>
       </c>
       <c r="N200" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
@@ -10671,13 +10656,13 @@
         <v>4.435</v>
       </c>
       <c r="L201" t="n">
-        <v>87.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="M201" t="n">
-        <v>4.861</v>
+        <v>4.86</v>
       </c>
       <c r="N201" t="n">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
@@ -10723,190 +10708,18 @@
         <v>4.185</v>
       </c>
       <c r="L202" t="n">
-        <v>44</v>
+        <v>45.2</v>
       </c>
       <c r="M202" t="n">
         <v>4.72</v>
       </c>
       <c r="N202" t="n">
-        <v>95.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Asuka Sushi</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Omakase Value Score Methodology (v2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>1. Google Bias Correction</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   correction_factor = 0.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   corrected_rating = raw_google_rating * correction_factor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Google Maps ratings are systematically inflated. This corrects by ~3%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2. Wilson Score Lower Bound (Rating Adjustment)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   z = 1.96 (95% confidence interval)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Converts 5-star to proportion, computes Wilson lower bound, converts back.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Effect: statistically rigorous penalty for low review counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Unlike Bayesian average, penalty is based on actual statistical uncertainty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>3. Price Exponent (Empirically Derived)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Derived via log-log regression: log(rating) ~ beta * log(price)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   The regression coefficient |beta| becomes the exponent, capped to [0.1, 0.6].</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>4. Value Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   value = adj_rating * (100 / price) ^ exponent</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Higher score = better combination of quality and affordability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>5. Percentile Ranking</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Rating Pctl: where adjusted rating falls vs all others (0=worst, 100=best)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Value Pctl: where value score falls vs all others</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Since ratings cluster 4.2-5.0, percentiles make differences interpretable.</t>
         </is>
       </c>
     </row>

--- a/Omakase_Ratings.xlsx
+++ b/Omakase_Ratings.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -566,19 +566,19 @@
         <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1471</v>
+        <v>1496</v>
       </c>
       <c r="K2" t="n">
         <v>4.102</v>
       </c>
       <c r="L2" t="n">
-        <v>34.7</v>
+        <v>36.5</v>
       </c>
       <c r="M2" t="n">
         <v>4.056</v>
       </c>
       <c r="N2" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manhattan (UES/UWS/Midtown)</t>
+          <t>Manhattan (Upper East Side-Carnegie Hill)</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -618,19 +618,19 @@
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.478</v>
+        <v>3.488</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -667,22 +667,22 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="K4" t="n">
-        <v>4.143</v>
+        <v>4.099</v>
       </c>
       <c r="L4" t="n">
-        <v>38.7</v>
+        <v>35.5</v>
       </c>
       <c r="M4" t="n">
-        <v>4.143</v>
+        <v>4.099</v>
       </c>
       <c r="N4" t="n">
-        <v>38.6</v>
+        <v>34.4</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manhattan (Saks 5th Ave)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -724,13 +724,13 @@
         <v>3.822</v>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="M5" t="n">
         <v>3.842</v>
       </c>
       <c r="N5" t="n">
-        <v>15.7</v>
+        <v>17.4</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Manhattan (UWS)</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -763,27 +763,27 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>137</v>
+        <v>271</v>
       </c>
       <c r="K6" t="n">
-        <v>3.929</v>
+        <v>4.014</v>
       </c>
       <c r="L6" t="n">
-        <v>18.1</v>
+        <v>24.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.858</v>
+        <v>3.941</v>
       </c>
       <c r="N6" t="n">
-        <v>19.8</v>
+        <v>24.6</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Inase</t>
+          <t>Omakase Shihou - Upper West Side (Lunch Available)</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manhattan (UWS)</t>
+          <t>Manhattan (Upper East Side-Lenox Hill-Roosevelt Island)</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -814,19 +814,19 @@
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="K7" t="n">
-        <v>4.287</v>
+        <v>4.293</v>
       </c>
       <c r="L7" t="n">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="M7" t="n">
-        <v>4.116</v>
+        <v>4.123</v>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>36.9</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Manhattan (UWS)</t>
+          <t>Manhattan (Hell's Kitchen)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -863,22 +863,22 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="K8" t="n">
-        <v>4.223</v>
+        <v>4.278</v>
       </c>
       <c r="L8" t="n">
-        <v>48.2</v>
+        <v>59.9</v>
       </c>
       <c r="M8" t="n">
-        <v>4.272</v>
+        <v>4.328</v>
       </c>
       <c r="N8" t="n">
-        <v>54.3</v>
+        <v>62.6</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manhattan (Bryant Park)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -918,19 +918,19 @@
         <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="K9" t="n">
-        <v>4.239</v>
+        <v>4.241</v>
       </c>
       <c r="L9" t="n">
-        <v>51.8</v>
+        <v>54.3</v>
       </c>
       <c r="M9" t="n">
-        <v>4.781</v>
+        <v>4.783</v>
       </c>
       <c r="N9" t="n">
-        <v>97.5</v>
+        <v>99</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown)</t>
+          <t>Manhattan (Midtown) (unverified)</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown)</t>
+          <t>Manhattan (East Midtown-Turtle Bay)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -992,19 +992,19 @@
         <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K11" t="n">
-        <v>3.86</v>
+        <v>3.861</v>
       </c>
       <c r="L11" t="n">
-        <v>13.1</v>
+        <v>15.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.952</v>
+        <v>3.953</v>
       </c>
       <c r="N11" t="n">
-        <v>24.4</v>
+        <v>25.1</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown)</t>
+          <t>Manhattan (Murray Hill-Kips Bay)</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1037,22 +1037,22 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="K12" t="n">
-        <v>4.389</v>
+        <v>4.504</v>
       </c>
       <c r="L12" t="n">
-        <v>83.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>4.445</v>
+        <v>4.562</v>
       </c>
       <c r="N12" t="n">
-        <v>73.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown)</t>
+          <t>Manhattan (East Midtown-Turtle Bay)</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1092,19 +1092,19 @@
         <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K13" t="n">
-        <v>4.33</v>
+        <v>4.332</v>
       </c>
       <c r="L13" t="n">
-        <v>71.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>4.309</v>
+        <v>4.311</v>
       </c>
       <c r="N13" t="n">
-        <v>58.9</v>
+        <v>60.5</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1144,19 +1144,19 @@
         <v>4.7</v>
       </c>
       <c r="J14" t="n">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="K14" t="n">
-        <v>4.28</v>
+        <v>4.281</v>
       </c>
       <c r="L14" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M14" t="n">
-        <v>4.449</v>
+        <v>4.45</v>
       </c>
       <c r="N14" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1196,19 +1196,19 @@
         <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K15" t="n">
-        <v>4.078</v>
+        <v>4.09</v>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>34</v>
       </c>
       <c r="M15" t="n">
-        <v>4.078</v>
+        <v>4.09</v>
       </c>
       <c r="N15" t="n">
-        <v>32</v>
+        <v>33.3</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Manhattan (UWS)</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1248,19 +1248,19 @@
         <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K16" t="n">
-        <v>4.334</v>
+        <v>4.335</v>
       </c>
       <c r="L16" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>4.274</v>
       </c>
       <c r="N16" t="n">
-        <v>55.8</v>
+        <v>56.4</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Manhattan (UWS)</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1293,22 +1293,22 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="K17" t="n">
-        <v>4.021</v>
+        <v>4.076</v>
       </c>
       <c r="L17" t="n">
-        <v>26.1</v>
+        <v>31</v>
       </c>
       <c r="M17" t="n">
-        <v>4.179</v>
+        <v>4.236</v>
       </c>
       <c r="N17" t="n">
-        <v>43.1</v>
+        <v>51.8</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (Murray Hill-Kips Bay)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1348,19 +1348,19 @@
         <v>4.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="K18" t="n">
         <v>4.065</v>
       </c>
       <c r="L18" t="n">
-        <v>29.1</v>
+        <v>29.9</v>
       </c>
       <c r="M18" t="n">
         <v>3.855</v>
       </c>
       <c r="N18" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (East Midtown-Turtle Bay)</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1396,19 +1396,19 @@
         <v>4.8</v>
       </c>
       <c r="J19" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K19" t="n">
-        <v>4.286</v>
+        <v>4.289</v>
       </c>
       <c r="L19" t="n">
-        <v>64.3</v>
+        <v>64</v>
       </c>
       <c r="M19" t="n">
-        <v>4.246</v>
+        <v>4.248</v>
       </c>
       <c r="N19" t="n">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1454,13 +1454,13 @@
         <v>4.001</v>
       </c>
       <c r="L20" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="M20" t="n">
         <v>3.842</v>
       </c>
       <c r="N20" t="n">
-        <v>16.2</v>
+        <v>17.9</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manhattan (UWS)</t>
+          <t>Manhattan (Upper East Side-Lenox Hill-Roosevelt Island)</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1497,22 +1497,22 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>762</v>
+        <v>2444</v>
       </c>
       <c r="K21" t="n">
-        <v>4.364</v>
+        <v>4.427</v>
       </c>
       <c r="L21" t="n">
-        <v>80.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="M21" t="n">
-        <v>4.625</v>
+        <v>4.692</v>
       </c>
       <c r="N21" t="n">
-        <v>91.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Manhattan (Theater District)</t>
+          <t>Manhattan (Hell's Kitchen)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1550,13 +1550,13 @@
         <v>4.055</v>
       </c>
       <c r="L22" t="n">
-        <v>28.6</v>
+        <v>29.4</v>
       </c>
       <c r="M22" t="n">
         <v>4.076</v>
       </c>
       <c r="N22" t="n">
-        <v>31.5</v>
+        <v>31.8</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Manhattan (UWS)</t>
+          <t>Manhattan (Hell's Kitchen)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1596,19 +1596,19 @@
         <v>4.9</v>
       </c>
       <c r="J23" t="n">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="K23" t="n">
-        <v>4.544</v>
+        <v>4.573</v>
       </c>
       <c r="L23" t="n">
-        <v>95.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>4.509</v>
+        <v>4.538</v>
       </c>
       <c r="N23" t="n">
-        <v>80.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown West)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1648,19 +1648,19 @@
         <v>4.4</v>
       </c>
       <c r="J24" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="K24" t="n">
-        <v>4.153</v>
+        <v>4.155</v>
       </c>
       <c r="L24" t="n">
-        <v>40.7</v>
+        <v>42.1</v>
       </c>
       <c r="M24" t="n">
-        <v>4.153</v>
+        <v>4.155</v>
       </c>
       <c r="N24" t="n">
-        <v>40.1</v>
+        <v>41</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -1700,19 +1700,19 @@
         <v>4.8</v>
       </c>
       <c r="J25" t="n">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="K25" t="n">
-        <v>4.646</v>
+        <v>4.647</v>
       </c>
       <c r="L25" t="n">
-        <v>97.5</v>
+        <v>98</v>
       </c>
       <c r="M25" t="n">
         <v>4.701</v>
       </c>
       <c r="N25" t="n">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown West)</t>
+          <t>Manhattan (Midtown West) (unverified)</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1748,30 +1748,20 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>326</v>
-      </c>
       <c r="K26" t="n">
-        <v>3.991</v>
+        <v>3.768</v>
       </c>
       <c r="L26" t="n">
-        <v>22.6</v>
+        <v>7.1</v>
       </c>
       <c r="M26" t="n">
-        <v>4.033</v>
+        <v>3.808</v>
       </c>
       <c r="N26" t="n">
-        <v>28.9</v>
+        <v>14.4</v>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Mojo East</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1804,19 +1794,19 @@
         <v>4.8</v>
       </c>
       <c r="J27" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="K27" t="n">
-        <v>4.498</v>
+        <v>4.499</v>
       </c>
       <c r="L27" t="n">
-        <v>94.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>4.381</v>
+        <v>4.383</v>
       </c>
       <c r="N27" t="n">
-        <v>65</v>
+        <v>66.2</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -1833,7 +1823,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Manhattan (Times Sq/Midtown)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1856,19 +1846,19 @@
         <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>1135</v>
+        <v>1188</v>
       </c>
       <c r="K28" t="n">
-        <v>3.983</v>
+        <v>3.984</v>
       </c>
       <c r="L28" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.192</v>
+        <v>4.193</v>
       </c>
       <c r="N28" t="n">
-        <v>45.7</v>
+        <v>46.7</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -1885,7 +1875,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1908,19 +1898,19 @@
         <v>4.6</v>
       </c>
       <c r="J29" t="n">
-        <v>631</v>
+        <v>713</v>
       </c>
       <c r="K29" t="n">
-        <v>4.257</v>
+        <v>4.259</v>
       </c>
       <c r="L29" t="n">
-        <v>54.8</v>
+        <v>57.4</v>
       </c>
       <c r="M29" t="n">
-        <v>4.581</v>
+        <v>4.584</v>
       </c>
       <c r="N29" t="n">
-        <v>87.3</v>
+        <v>88.7</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -1937,7 +1927,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Manhattan (UES / UWS)</t>
+          <t>Manhattan (Upper East Side-Lenox Hill-Roosevelt Island)</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1956,19 +1946,19 @@
         <v>4.5</v>
       </c>
       <c r="J30" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K30" t="n">
         <v>3.962</v>
       </c>
       <c r="L30" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="M30" t="n">
-        <v>4.191</v>
+        <v>4.192</v>
       </c>
       <c r="N30" t="n">
-        <v>45.2</v>
+        <v>46.2</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -1985,7 +1975,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Manhattan (Gramercy/Midtown)</t>
+          <t>Manhattan (Gramercy)</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2008,19 +1998,19 @@
         <v>4.8</v>
       </c>
       <c r="J31" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="K31" t="n">
-        <v>4.351</v>
+        <v>4.352</v>
       </c>
       <c r="L31" t="n">
-        <v>75.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="M31" t="n">
-        <v>4.373</v>
+        <v>4.374</v>
       </c>
       <c r="N31" t="n">
-        <v>64.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -2037,7 +2027,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Manhattan (Kips Bay / UES)</t>
+          <t>Manhattan (Gramercy)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2060,19 +2050,19 @@
         <v>4.7</v>
       </c>
       <c r="J32" t="n">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="K32" t="n">
-        <v>4.322</v>
+        <v>4.323</v>
       </c>
       <c r="L32" t="n">
-        <v>71.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>4.564</v>
+        <v>4.565</v>
       </c>
       <c r="N32" t="n">
-        <v>85.8</v>
+        <v>87.2</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -2089,7 +2079,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Manhattan (UES / Lower Manh.)</t>
+          <t>Manhattan (Upper West Side (Central))</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2108,19 +2098,19 @@
         <v>4.8</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4.564</v>
+        <v>4.567</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>96</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4.618</v>
+        <v>4.621</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2131,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Manhattan (Flatiron)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2150,21 +2140,21 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="K34" t="n">
-        <v>3.863</v>
+        <v>4.069</v>
       </c>
       <c r="L34" t="n">
-        <v>13.6</v>
+        <v>30.5</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>ROKI Le Izakaya</t>
+          <t>RokuNana</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2189,19 @@
         <v>4.6</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>4.283</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>62.8</v>
+        <v>62.4</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>4.445</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2232,7 +2222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Manhattan (Chelsea/Midtown)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2255,19 +2245,19 @@
         <v>4.8</v>
       </c>
       <c r="J36" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="K36" t="n">
         <v>4.461</v>
       </c>
       <c r="L36" t="n">
-        <v>91</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>4.534</v>
+        <v>4.535</v>
       </c>
       <c r="N36" t="n">
-        <v>83.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -2284,7 +2274,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Manhattan (NoMad)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2307,19 +2297,19 @@
         <v>4.6</v>
       </c>
       <c r="J37" t="n">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="K37" t="n">
-        <v>4.281</v>
+        <v>4.282</v>
       </c>
       <c r="L37" t="n">
-        <v>60.8</v>
+        <v>61.9</v>
       </c>
       <c r="M37" t="n">
-        <v>4.11</v>
+        <v>4.112</v>
       </c>
       <c r="N37" t="n">
-        <v>34.5</v>
+        <v>35.9</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -2336,7 +2326,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Manhattan (Upper West Side (Central))</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2353,21 +2343,21 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
-        <v>469</v>
+        <v>832</v>
       </c>
       <c r="K38" t="n">
-        <v>3.438</v>
+        <v>3.725</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tokyo Record Bar</t>
+          <t>Sushi Tokyo Manhattan</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2369,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Manhattan (NoMad/Midtown)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2402,19 +2392,19 @@
         <v>4.7</v>
       </c>
       <c r="J39" t="n">
-        <v>3088</v>
+        <v>3144</v>
       </c>
       <c r="K39" t="n">
         <v>4.145</v>
       </c>
       <c r="L39" t="n">
-        <v>39.2</v>
+        <v>40.6</v>
       </c>
       <c r="M39" t="n">
         <v>4.781</v>
       </c>
       <c r="N39" t="n">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -2454,19 +2444,19 @@
         <v>4.4</v>
       </c>
       <c r="J40" t="n">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="K40" t="n">
-        <v>3.834</v>
+        <v>3.835</v>
       </c>
       <c r="L40" t="n">
-        <v>8.5</v>
+        <v>11.2</v>
       </c>
       <c r="M40" t="n">
         <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -2506,19 +2496,19 @@
         <v>4.9</v>
       </c>
       <c r="J41" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="K41" t="n">
-        <v>4.224</v>
+        <v>4.227</v>
       </c>
       <c r="L41" t="n">
-        <v>48.7</v>
+        <v>50.8</v>
       </c>
       <c r="M41" t="n">
-        <v>4.278</v>
+        <v>4.282</v>
       </c>
       <c r="N41" t="n">
-        <v>56.3</v>
+        <v>57.9</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -2535,7 +2525,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Manhattan (Flatiron / UES)</t>
+          <t>Manhattan (Upper East Side-Lenox Hill-Roosevelt Island)</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2555,27 +2545,27 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
-        <v>171</v>
+        <v>415</v>
       </c>
       <c r="K42" t="n">
-        <v>3.931</v>
+        <v>3.793</v>
       </c>
       <c r="L42" t="n">
-        <v>19.6</v>
+        <v>8.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.931</v>
+        <v>3.793</v>
       </c>
       <c r="N42" t="n">
-        <v>23.4</v>
+        <v>13.3</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kissaki Japanese Restaurant</t>
+          <t>Sushi Seki</t>
         </is>
       </c>
     </row>
@@ -2612,13 +2602,13 @@
         <v>4.149</v>
       </c>
       <c r="L43" t="n">
-        <v>40.2</v>
+        <v>41.1</v>
       </c>
       <c r="M43" t="n">
         <v>4.17</v>
       </c>
       <c r="N43" t="n">
-        <v>42.1</v>
+        <v>42.6</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -2658,19 +2648,19 @@
         <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>868</v>
+        <v>917</v>
       </c>
       <c r="K44" t="n">
-        <v>4.724</v>
+        <v>4.725</v>
       </c>
       <c r="L44" t="n">
         <v>99.5</v>
       </c>
       <c r="M44" t="n">
-        <v>4.724</v>
+        <v>4.725</v>
       </c>
       <c r="N44" t="n">
-        <v>96.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -2706,19 +2696,19 @@
         <v>4.2</v>
       </c>
       <c r="J45" t="n">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="K45" t="n">
         <v>3.859</v>
       </c>
       <c r="L45" t="n">
-        <v>12.1</v>
+        <v>14.7</v>
       </c>
       <c r="M45" t="n">
         <v>3.879</v>
       </c>
       <c r="N45" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -2755,27 +2745,27 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>198</v>
+        <v>59</v>
       </c>
       <c r="K46" t="n">
-        <v>3.884</v>
+        <v>4.052</v>
       </c>
       <c r="L46" t="n">
-        <v>15.1</v>
+        <v>27.9</v>
       </c>
       <c r="M46" t="n">
-        <v>3.998</v>
+        <v>4.17</v>
       </c>
       <c r="N46" t="n">
-        <v>26.9</v>
+        <v>42.1</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>OMAKASE by TEISUI</t>
+          <t>Omakase By Tento</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2777,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Manhattan (East Village)</t>
+          <t>Manhattan (East Village) (unverified)</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2806,30 +2796,20 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>34</v>
-      </c>
       <c r="K47" t="n">
-        <v>3.612</v>
+        <v>3.333</v>
       </c>
       <c r="L47" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>3.802</v>
+        <v>3.508</v>
       </c>
       <c r="N47" t="n">
-        <v>12.7</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Sushi By Bou - East Village NYC</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2839,7 +2819,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Manhattan (Chelsea)</t>
+          <t>Manhattan (Chelsea-Hudson Yards)</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2858,19 +2838,19 @@
         <v>4.7</v>
       </c>
       <c r="J48" t="n">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="K48" t="n">
-        <v>4.179</v>
+        <v>4.18</v>
       </c>
       <c r="L48" t="n">
-        <v>43.7</v>
+        <v>46.2</v>
       </c>
       <c r="M48" t="n">
-        <v>4.284</v>
+        <v>4.285</v>
       </c>
       <c r="N48" t="n">
-        <v>56.9</v>
+        <v>58.5</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -2910,19 +2890,19 @@
         <v>4.9</v>
       </c>
       <c r="J49" t="n">
-        <v>967</v>
+        <v>996</v>
       </c>
       <c r="K49" t="n">
         <v>4.571</v>
       </c>
       <c r="L49" t="n">
-        <v>96.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="M49" t="n">
         <v>4.744</v>
       </c>
       <c r="N49" t="n">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -2962,19 +2942,19 @@
         <v>4.4</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>768</v>
+        <v>796</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>3.72</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3.727</v>
+        <v>3.728</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -2995,7 +2975,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3018,19 +2998,19 @@
         <v>4.5</v>
       </c>
       <c r="J51" t="n">
-        <v>2038</v>
+        <v>2063</v>
       </c>
       <c r="K51" t="n">
         <v>4.117</v>
       </c>
       <c r="L51" t="n">
-        <v>36.2</v>
+        <v>37.6</v>
       </c>
       <c r="M51" t="n">
         <v>4.231</v>
       </c>
       <c r="N51" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -3047,7 +3027,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3070,19 +3050,19 @@
         <v>4.7</v>
       </c>
       <c r="J52" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K52" t="n">
-        <v>4.29</v>
+        <v>4.312</v>
       </c>
       <c r="L52" t="n">
-        <v>65.8</v>
+        <v>69.5</v>
       </c>
       <c r="M52" t="n">
-        <v>4.478</v>
+        <v>4.502</v>
       </c>
       <c r="N52" t="n">
-        <v>77.7</v>
+        <v>81.5</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -3122,19 +3102,19 @@
         <v>4.5</v>
       </c>
       <c r="J53" t="n">
-        <v>951</v>
+        <v>975</v>
       </c>
       <c r="K53" t="n">
         <v>4.354</v>
       </c>
       <c r="L53" t="n">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="M53" t="n">
-        <v>4.518</v>
+        <v>4.519</v>
       </c>
       <c r="N53" t="n">
-        <v>81.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -3174,19 +3154,19 @@
         <v>4.2</v>
       </c>
       <c r="J54" t="n">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K54" t="n">
         <v>3.819</v>
       </c>
       <c r="L54" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="M54" t="n">
         <v>3.827</v>
       </c>
       <c r="N54" t="n">
-        <v>14.2</v>
+        <v>15.9</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -3203,7 +3183,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Manhattan (Chelsea / UES)</t>
+          <t>Manhattan (Chelsea-Hudson Yards)</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3226,19 +3206,19 @@
         <v>4.4</v>
       </c>
       <c r="J55" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="K55" t="n">
         <v>3.888</v>
       </c>
       <c r="L55" t="n">
-        <v>15.6</v>
+        <v>17.3</v>
       </c>
       <c r="M55" t="n">
-        <v>3.817</v>
+        <v>3.818</v>
       </c>
       <c r="N55" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -3278,19 +3258,19 @@
         <v>4.6</v>
       </c>
       <c r="J56" t="n">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="K56" t="n">
         <v>4.332</v>
       </c>
       <c r="L56" t="n">
-        <v>73.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>4.458</v>
+        <v>4.459</v>
       </c>
       <c r="N56" t="n">
-        <v>76.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -3307,7 +3287,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Manhattan (Flatiron/SoHo)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3330,19 +3310,19 @@
         <v>4.5</v>
       </c>
       <c r="J57" t="n">
-        <v>1467</v>
+        <v>1507</v>
       </c>
       <c r="K57" t="n">
-        <v>4.159</v>
+        <v>4.16</v>
       </c>
       <c r="L57" t="n">
-        <v>41.2</v>
+        <v>42.6</v>
       </c>
       <c r="M57" t="n">
-        <v>4.084</v>
+        <v>4.085</v>
       </c>
       <c r="N57" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -3378,24 +3358,24 @@
         <v>4.8</v>
       </c>
       <c r="J58" t="n">
-        <v>1401</v>
+        <v>1408</v>
       </c>
       <c r="K58" t="n">
         <v>4.362</v>
       </c>
       <c r="L58" t="n">
-        <v>79.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="M58" t="n">
         <v>4.489</v>
       </c>
       <c r="N58" t="n">
-        <v>80.2</v>
+        <v>81</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Genki Omakase</t>
+          <t>Genki Omakase | Sushi • Japanese</t>
         </is>
       </c>
     </row>
@@ -3430,19 +3410,19 @@
         <v>4.3</v>
       </c>
       <c r="J59" t="n">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="K59" t="n">
         <v>3.772</v>
       </c>
       <c r="L59" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="M59" t="n">
-        <v>3.528</v>
+        <v>3.529</v>
       </c>
       <c r="N59" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -3482,19 +3462,19 @@
         <v>4.9</v>
       </c>
       <c r="J60" t="n">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="K60" t="n">
-        <v>4.483</v>
+        <v>4.485</v>
       </c>
       <c r="L60" t="n">
-        <v>93.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>4.614</v>
+        <v>4.616</v>
       </c>
       <c r="N60" t="n">
-        <v>90.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -3511,7 +3491,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Manhattan &amp; Brooklyn</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3534,19 +3514,19 @@
         <v>4.9</v>
       </c>
       <c r="J61" t="n">
-        <v>438</v>
+        <v>528</v>
       </c>
       <c r="K61" t="n">
-        <v>4.647</v>
+        <v>4.658</v>
       </c>
       <c r="L61" t="n">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="M61" t="n">
-        <v>4.611</v>
+        <v>4.622</v>
       </c>
       <c r="N61" t="n">
-        <v>89.8</v>
+        <v>92.8</v>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -3563,7 +3543,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Manhattan (Meatpacking)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3583,22 +3563,22 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K62" t="n">
-        <v>3.72</v>
+        <v>3.685</v>
       </c>
       <c r="L62" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.668</v>
+        <v>3.634</v>
       </c>
       <c r="N62" t="n">
-        <v>9.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -3638,19 +3618,19 @@
         <v>4.6</v>
       </c>
       <c r="J63" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="K63" t="n">
-        <v>4.128</v>
+        <v>4.134</v>
       </c>
       <c r="L63" t="n">
-        <v>38.2</v>
+        <v>40.1</v>
       </c>
       <c r="M63" t="n">
-        <v>3.904</v>
+        <v>3.909</v>
       </c>
       <c r="N63" t="n">
-        <v>21.8</v>
+        <v>23.1</v>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -3667,7 +3647,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Manhattan / Brooklyn</t>
+          <t>Brooklyn (Park Slope)</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3687,27 +3667,27 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="J64" t="n">
-        <v>39</v>
+        <v>266</v>
       </c>
       <c r="K64" t="n">
-        <v>4.055</v>
+        <v>3.9</v>
       </c>
       <c r="L64" t="n">
-        <v>28.1</v>
+        <v>17.8</v>
       </c>
       <c r="M64" t="n">
-        <v>4.346</v>
+        <v>4.18</v>
       </c>
       <c r="N64" t="n">
-        <v>61.9</v>
+        <v>45.1</v>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sushi Hayashi Williamsburg</t>
+          <t>Sushi Yashin</t>
         </is>
       </c>
     </row>
@@ -3735,22 +3715,22 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K65" t="n">
-        <v>4.375</v>
+        <v>4.326</v>
       </c>
       <c r="L65" t="n">
-        <v>81.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>4.337</v>
+        <v>4.289</v>
       </c>
       <c r="N65" t="n">
-        <v>61.4</v>
+        <v>59</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -3767,7 +3747,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Brooklyn (Greenpoint)</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3787,22 +3767,22 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J66" t="n">
-        <v>271</v>
+        <v>325</v>
       </c>
       <c r="K66" t="n">
-        <v>4.067</v>
+        <v>4.19</v>
       </c>
       <c r="L66" t="n">
-        <v>30.2</v>
+        <v>48.2</v>
       </c>
       <c r="M66" t="n">
-        <v>4.185</v>
+        <v>4.313</v>
       </c>
       <c r="N66" t="n">
-        <v>44.2</v>
+        <v>61</v>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -3819,7 +3799,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Manhattan (LES)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3842,19 +3822,19 @@
         <v>4.5</v>
       </c>
       <c r="J67" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="K67" t="n">
-        <v>4.182</v>
+        <v>4.184</v>
       </c>
       <c r="L67" t="n">
-        <v>44.2</v>
+        <v>47.2</v>
       </c>
       <c r="M67" t="n">
-        <v>4.203</v>
+        <v>4.205</v>
       </c>
       <c r="N67" t="n">
-        <v>47.2</v>
+        <v>48.7</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -3871,7 +3851,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Manhattan (LES / Bowery)</t>
+          <t>Queens (Long Island City-Hunters Point)</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3891,22 +3871,22 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="K68" t="n">
-        <v>4.356</v>
+        <v>4.319</v>
       </c>
       <c r="L68" t="n">
-        <v>78.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M68" t="n">
-        <v>4.528</v>
+        <v>4.489</v>
       </c>
       <c r="N68" t="n">
-        <v>82.7</v>
+        <v>80</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -3923,7 +3903,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Manhattan (Hudson Square)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3942,19 +3922,19 @@
         <v>4.6</v>
       </c>
       <c r="J69" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="K69" t="n">
-        <v>4.25</v>
+        <v>4.257</v>
       </c>
       <c r="L69" t="n">
-        <v>53.8</v>
+        <v>56.3</v>
       </c>
       <c r="M69" t="n">
-        <v>4.272</v>
+        <v>4.279</v>
       </c>
       <c r="N69" t="n">
-        <v>54.8</v>
+        <v>57.4</v>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -3990,19 +3970,19 @@
         <v>4.6</v>
       </c>
       <c r="J70" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="K70" t="n">
-        <v>4.233</v>
+        <v>4.234</v>
       </c>
       <c r="L70" t="n">
-        <v>50.3</v>
+        <v>52.3</v>
       </c>
       <c r="M70" t="n">
-        <v>4.387</v>
+        <v>4.388</v>
       </c>
       <c r="N70" t="n">
-        <v>66.5</v>
+        <v>67.2</v>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -4039,22 +4019,22 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J71" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="K71" t="n">
-        <v>4.403</v>
+        <v>4.385</v>
       </c>
       <c r="L71" t="n">
-        <v>84.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="M71" t="n">
-        <v>4.411</v>
+        <v>4.394</v>
       </c>
       <c r="N71" t="n">
-        <v>70.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -4094,19 +4074,19 @@
         <v>4.5</v>
       </c>
       <c r="J72" t="n">
-        <v>1939</v>
+        <v>1958</v>
       </c>
       <c r="K72" t="n">
         <v>4.238</v>
       </c>
       <c r="L72" t="n">
-        <v>50.8</v>
+        <v>52.8</v>
       </c>
       <c r="M72" t="n">
-        <v>4.043</v>
+        <v>4.044</v>
       </c>
       <c r="N72" t="n">
-        <v>29.4</v>
+        <v>28.7</v>
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
@@ -4123,7 +4103,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Manhattan/Brooklyn</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4152,13 +4132,13 @@
         <v>3.86</v>
       </c>
       <c r="L73" t="n">
-        <v>12.6</v>
+        <v>15.2</v>
       </c>
       <c r="M73" t="n">
         <v>4.076</v>
       </c>
       <c r="N73" t="n">
-        <v>31</v>
+        <v>31.3</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -4175,7 +4155,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Brooklyn / Queens</t>
+          <t>Queens (Elmhurst)</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4195,27 +4175,27 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
-        <v>142</v>
+        <v>552</v>
       </c>
       <c r="K74" t="n">
-        <v>4.313</v>
+        <v>4.475</v>
       </c>
       <c r="L74" t="n">
-        <v>69.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="M74" t="n">
-        <v>4.317</v>
+        <v>4.479</v>
       </c>
       <c r="N74" t="n">
-        <v>59.9</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sushi On Me - Williamsburg</t>
+          <t>Sushi On Me</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4207,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Manhattan (LES)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4250,19 +4230,19 @@
         <v>4.8</v>
       </c>
       <c r="J75" t="n">
-        <v>716</v>
+        <v>1076</v>
       </c>
       <c r="K75" t="n">
-        <v>4.407</v>
+        <v>4.414</v>
       </c>
       <c r="L75" t="n">
-        <v>85.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="M75" t="n">
-        <v>4.459</v>
+        <v>4.465</v>
       </c>
       <c r="N75" t="n">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -4298,19 +4278,19 @@
         <v>4.3</v>
       </c>
       <c r="J76" t="n">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="K76" t="n">
-        <v>4.122</v>
+        <v>4.123</v>
       </c>
       <c r="L76" t="n">
-        <v>36.7</v>
+        <v>38.6</v>
       </c>
       <c r="M76" t="n">
         <v>4.226</v>
       </c>
       <c r="N76" t="n">
-        <v>49.2</v>
+        <v>50.8</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -4327,7 +4307,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Manhattan (NoHo)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4350,19 +4330,19 @@
         <v>4.5</v>
       </c>
       <c r="J77" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K77" t="n">
-        <v>4.05</v>
+        <v>4.052</v>
       </c>
       <c r="L77" t="n">
-        <v>27.6</v>
+        <v>28.4</v>
       </c>
       <c r="M77" t="n">
-        <v>3.448</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -4379,7 +4359,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Manhattan (LES)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4398,19 +4378,19 @@
         <v>4.9</v>
       </c>
       <c r="J78" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="K78" t="n">
-        <v>4.431</v>
+        <v>4.433</v>
       </c>
       <c r="L78" t="n">
-        <v>87.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="M78" t="n">
-        <v>4.483</v>
+        <v>4.485</v>
       </c>
       <c r="N78" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -4427,7 +4407,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Manhattan (Murray Hill/Midtown)</t>
+          <t>Manhattan (Murray Hill-Kips Bay)</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4450,19 +4430,19 @@
         <v>4.6</v>
       </c>
       <c r="J79" t="n">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="K79" t="n">
-        <v>4.275</v>
+        <v>4.277</v>
       </c>
       <c r="L79" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="M79" t="n">
-        <v>4.296</v>
+        <v>4.299</v>
       </c>
       <c r="N79" t="n">
-        <v>57.9</v>
+        <v>59.5</v>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -4479,7 +4459,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -4502,19 +4482,19 @@
         <v>4.6</v>
       </c>
       <c r="J80" t="n">
-        <v>1867</v>
+        <v>1896</v>
       </c>
       <c r="K80" t="n">
         <v>4.173</v>
       </c>
       <c r="L80" t="n">
-        <v>42.2</v>
+        <v>44.2</v>
       </c>
       <c r="M80" t="n">
-        <v>4.007</v>
+        <v>4.008</v>
       </c>
       <c r="N80" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -4531,7 +4511,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4560,13 +4540,13 @@
         <v>4.046</v>
       </c>
       <c r="L81" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="M81" t="n">
         <v>4.088</v>
       </c>
       <c r="N81" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -4583,7 +4563,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo / West Vil.)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4606,19 +4586,19 @@
         <v>4.7</v>
       </c>
       <c r="J82" t="n">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="K82" t="n">
-        <v>4.347</v>
+        <v>4.349</v>
       </c>
       <c r="L82" t="n">
-        <v>75.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="M82" t="n">
-        <v>4.219</v>
+        <v>4.221</v>
       </c>
       <c r="N82" t="n">
-        <v>48.7</v>
+        <v>50.3</v>
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -4635,7 +4615,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -4658,19 +4638,19 @@
         <v>4.6</v>
       </c>
       <c r="J83" t="n">
-        <v>1373</v>
+        <v>1546</v>
       </c>
       <c r="K83" t="n">
-        <v>4.127</v>
+        <v>4.129</v>
       </c>
       <c r="L83" t="n">
-        <v>37.7</v>
+        <v>39.6</v>
       </c>
       <c r="M83" t="n">
-        <v>3.963</v>
+        <v>3.965</v>
       </c>
       <c r="N83" t="n">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -4687,7 +4667,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo/West Village)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4710,19 +4690,19 @@
         <v>4.4</v>
       </c>
       <c r="J84" t="n">
-        <v>1812</v>
+        <v>1867</v>
       </c>
       <c r="K84" t="n">
-        <v>4.005</v>
+        <v>4.006</v>
       </c>
       <c r="L84" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="M84" t="n">
         <v>4.489</v>
       </c>
       <c r="N84" t="n">
-        <v>79.7</v>
+        <v>80.5</v>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
@@ -4739,7 +4719,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Manhattan (South Village)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4762,19 +4742,19 @@
         <v>4.6</v>
       </c>
       <c r="J85" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K85" t="n">
-        <v>4.295</v>
+        <v>4.296</v>
       </c>
       <c r="L85" t="n">
-        <v>66.3</v>
+        <v>66</v>
       </c>
       <c r="M85" t="n">
-        <v>4.262</v>
+        <v>4.263</v>
       </c>
       <c r="N85" t="n">
-        <v>53.8</v>
+        <v>55.9</v>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -4791,7 +4771,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -4814,19 +4794,19 @@
         <v>4.5</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>4.248</v>
+        <v>4.249</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>53.3</v>
+        <v>55.3</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4.435</v>
+        <v>4.436</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -4847,7 +4827,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo)</t>
+          <t>Manhattan (Gramercy)</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -4867,27 +4847,27 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="K87" t="n">
-        <v>4.353</v>
+        <v>3.953</v>
       </c>
       <c r="L87" t="n">
-        <v>77.90000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="M87" t="n">
-        <v>4.481</v>
+        <v>4.068</v>
       </c>
       <c r="N87" t="n">
-        <v>78.2</v>
+        <v>30.8</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rei Restaurant</t>
+          <t>Sushi By Bae</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4879,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -4922,19 +4902,19 @@
         <v>4.6</v>
       </c>
       <c r="J88" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K88" t="n">
-        <v>4.316</v>
+        <v>4.319</v>
       </c>
       <c r="L88" t="n">
-        <v>70.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M88" t="n">
-        <v>4.145</v>
+        <v>4.147</v>
       </c>
       <c r="N88" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -4951,7 +4931,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4971,27 +4951,27 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="K89" t="n">
-        <v>4.184</v>
+        <v>4.231</v>
       </c>
       <c r="L89" t="n">
-        <v>44.7</v>
+        <v>51.3</v>
       </c>
       <c r="M89" t="n">
-        <v>4.228</v>
+        <v>4.276</v>
       </c>
       <c r="N89" t="n">
-        <v>50.3</v>
+        <v>56.9</v>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sushi Lin SoHo</t>
+          <t>Sushi Lin Upper West Side</t>
         </is>
       </c>
     </row>
@@ -5003,7 +4983,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo / Lower Manh.)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -5026,19 +5006,19 @@
         <v>4.8</v>
       </c>
       <c r="J90" t="n">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="K90" t="n">
-        <v>4.526</v>
+        <v>4.53</v>
       </c>
       <c r="L90" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="M90" t="n">
-        <v>4.412</v>
+        <v>4.416</v>
       </c>
       <c r="N90" t="n">
-        <v>70.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
@@ -5055,7 +5035,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Manhattan (UES)</t>
+          <t>Manhattan (East Midtown-Turtle Bay)</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -5078,19 +5058,19 @@
         <v>4.8</v>
       </c>
       <c r="J91" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="K91" t="n">
-        <v>4.316</v>
+        <v>4.317</v>
       </c>
       <c r="L91" t="n">
-        <v>70.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="M91" t="n">
-        <v>4.386</v>
+        <v>4.388</v>
       </c>
       <c r="N91" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -5107,7 +5087,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Manhattan (UES)</t>
+          <t>Manhattan (Upper East Side-Carnegie Hill)</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -5130,19 +5110,19 @@
         <v>4.4</v>
       </c>
       <c r="J92" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="K92" t="n">
-        <v>3.848</v>
+        <v>3.851</v>
       </c>
       <c r="L92" t="n">
-        <v>11.1</v>
+        <v>13.7</v>
       </c>
       <c r="M92" t="n">
-        <v>3.889</v>
+        <v>3.891</v>
       </c>
       <c r="N92" t="n">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -5159,7 +5139,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Manhattan (UES)</t>
+          <t>Manhattan (Upper East Side-Yorkville)</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -5182,19 +5162,19 @@
         <v>5</v>
       </c>
       <c r="J93" t="n">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="K93" t="n">
-        <v>4.239</v>
+        <v>4.24</v>
       </c>
       <c r="L93" t="n">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
       <c r="M93" t="n">
-        <v>4.543</v>
+        <v>4.544</v>
       </c>
       <c r="N93" t="n">
-        <v>84.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -5211,7 +5191,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Manhattan (UES)</t>
+          <t>Manhattan (Upper East Side-Yorkville)</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -5234,19 +5214,19 @@
         <v>4.9</v>
       </c>
       <c r="J94" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K94" t="n">
-        <v>4.296</v>
+        <v>4.297</v>
       </c>
       <c r="L94" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="M94" t="n">
-        <v>4.139</v>
+        <v>4.14</v>
       </c>
       <c r="N94" t="n">
-        <v>37.6</v>
+        <v>39.5</v>
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -5263,7 +5243,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Manhattan (UES)</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -5286,19 +5266,19 @@
         <v>4.8</v>
       </c>
       <c r="J95" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="K95" t="n">
-        <v>4.304</v>
+        <v>4.306</v>
       </c>
       <c r="L95" t="n">
-        <v>68.8</v>
+        <v>67.5</v>
       </c>
       <c r="M95" t="n">
-        <v>4.244</v>
+        <v>4.246</v>
       </c>
       <c r="N95" t="n">
-        <v>51.8</v>
+        <v>53.3</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -5315,7 +5295,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Manhattan (UES)</t>
+          <t>Manhattan (Hell's Kitchen)</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -5338,19 +5318,19 @@
         <v>4.9</v>
       </c>
       <c r="J96" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="K96" t="n">
-        <v>4.736</v>
+        <v>4.737</v>
       </c>
       <c r="L96" t="n">
         <v>100</v>
       </c>
       <c r="M96" t="n">
-        <v>4.695</v>
+        <v>4.697</v>
       </c>
       <c r="N96" t="n">
-        <v>94.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -5367,7 +5347,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Manhattan (UES)</t>
+          <t>Manhattan (Hell's Kitchen)</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -5390,19 +5370,19 @@
         <v>4.8</v>
       </c>
       <c r="J97" t="n">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="K97" t="n">
-        <v>4.352</v>
+        <v>4.355</v>
       </c>
       <c r="L97" t="n">
-        <v>76.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="M97" t="n">
-        <v>4.398</v>
+        <v>4.401</v>
       </c>
       <c r="N97" t="n">
-        <v>68.5</v>
+        <v>70.3</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -5419,7 +5399,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -5438,19 +5418,19 @@
         <v>4.8</v>
       </c>
       <c r="J98" t="n">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K98" t="n">
-        <v>4.257</v>
+        <v>4.258</v>
       </c>
       <c r="L98" t="n">
-        <v>55.3</v>
+        <v>56.9</v>
       </c>
       <c r="M98" t="n">
-        <v>4.381</v>
+        <v>4.382</v>
       </c>
       <c r="N98" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -5467,7 +5447,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -5486,19 +5466,19 @@
         <v>4.4</v>
       </c>
       <c r="J99" t="n">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="K99" t="n">
-        <v>4.081</v>
+        <v>4.092</v>
       </c>
       <c r="L99" t="n">
-        <v>31.7</v>
+        <v>34.5</v>
       </c>
       <c r="M99" t="n">
-        <v>4.102</v>
+        <v>4.113</v>
       </c>
       <c r="N99" t="n">
-        <v>33.5</v>
+        <v>36.4</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -5515,7 +5495,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -5534,19 +5514,19 @@
         <v>4.7</v>
       </c>
       <c r="J100" t="n">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="K100" t="n">
-        <v>4.282</v>
+        <v>4.283</v>
       </c>
       <c r="L100" t="n">
-        <v>62.3</v>
+        <v>62.9</v>
       </c>
       <c r="M100" t="n">
-        <v>4.444</v>
+        <v>4.445</v>
       </c>
       <c r="N100" t="n">
-        <v>72.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -5563,7 +5543,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -5579,22 +5559,22 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="K101" t="n">
-        <v>4.385</v>
+        <v>4.439</v>
       </c>
       <c r="L101" t="n">
-        <v>83.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="M101" t="n">
-        <v>4.558</v>
+        <v>4.613</v>
       </c>
       <c r="N101" t="n">
-        <v>84.8</v>
+        <v>91.3</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
@@ -5611,7 +5591,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -5630,19 +5610,19 @@
         <v>4.5</v>
       </c>
       <c r="J102" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K102" t="n">
-        <v>4.003</v>
+        <v>4.006</v>
       </c>
       <c r="L102" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="M102" t="n">
-        <v>3.843</v>
+        <v>3.847</v>
       </c>
       <c r="N102" t="n">
-        <v>16.8</v>
+        <v>18.5</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
@@ -5659,7 +5639,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -5678,19 +5658,19 @@
         <v>4.7</v>
       </c>
       <c r="J103" t="n">
-        <v>326</v>
+        <v>371</v>
       </c>
       <c r="K103" t="n">
-        <v>4.302</v>
+        <v>4.307</v>
       </c>
       <c r="L103" t="n">
-        <v>68.3</v>
+        <v>68</v>
       </c>
       <c r="M103" t="n">
-        <v>4.567</v>
+        <v>4.572</v>
       </c>
       <c r="N103" t="n">
-        <v>86.8</v>
+        <v>88.2</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -5707,7 +5687,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -5730,19 +5710,19 @@
         <v>4.9</v>
       </c>
       <c r="J104" t="n">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="K104" t="n">
-        <v>4.082</v>
+        <v>4.088</v>
       </c>
       <c r="L104" t="n">
-        <v>32.2</v>
+        <v>33</v>
       </c>
       <c r="M104" t="n">
-        <v>3.992</v>
+        <v>3.998</v>
       </c>
       <c r="N104" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -5759,7 +5739,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manhattan (FiDi)</t>
+          <t>Manhattan (Financial District-Battery Park City)</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -5782,19 +5762,19 @@
         <v>4.4</v>
       </c>
       <c r="J105" t="n">
-        <v>1968</v>
+        <v>2004</v>
       </c>
       <c r="K105" t="n">
         <v>4.012</v>
       </c>
       <c r="L105" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="M105" t="n">
         <v>3.853</v>
       </c>
       <c r="N105" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -5811,7 +5791,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manh.)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -5826,19 +5806,19 @@
         <v>4.8</v>
       </c>
       <c r="J106" t="n">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="K106" t="n">
-        <v>4.197</v>
+        <v>4.2</v>
       </c>
       <c r="L106" t="n">
-        <v>46.7</v>
+        <v>49.7</v>
       </c>
       <c r="M106" t="n">
-        <v>4.251</v>
+        <v>4.254</v>
       </c>
       <c r="N106" t="n">
-        <v>52.8</v>
+        <v>54.4</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -5855,7 +5835,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -5878,19 +5858,19 @@
         <v>4.9</v>
       </c>
       <c r="J107" t="n">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="K107" t="n">
-        <v>4.614</v>
+        <v>4.616</v>
       </c>
       <c r="L107" t="n">
-        <v>97</v>
+        <v>97.5</v>
       </c>
       <c r="M107" t="n">
-        <v>4.531</v>
+        <v>4.532</v>
       </c>
       <c r="N107" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -5907,7 +5887,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -5926,24 +5906,24 @@
         <v>4.4</v>
       </c>
       <c r="J108" t="n">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="K108" t="n">
-        <v>4.217</v>
+        <v>4.21</v>
       </c>
       <c r="L108" t="n">
-        <v>47.2</v>
+        <v>50.3</v>
       </c>
       <c r="M108" t="n">
-        <v>4.438</v>
+        <v>4.431</v>
       </c>
       <c r="N108" t="n">
-        <v>72.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sake Kawa</t>
+          <t>Kawa Sushi</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5935,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (Chinatown-Two Bridges)</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -5974,19 +5954,19 @@
         <v>4.8</v>
       </c>
       <c r="J109" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K109" t="n">
-        <v>4.196</v>
+        <v>4.2</v>
       </c>
       <c r="L109" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="M109" t="n">
-        <v>4.204</v>
+        <v>4.209</v>
       </c>
       <c r="N109" t="n">
-        <v>47.7</v>
+        <v>49.7</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
@@ -6003,7 +5983,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (Chinatown-Two Bridges)</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -6022,19 +6002,19 @@
         <v>4.2</v>
       </c>
       <c r="J110" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="K110" t="n">
-        <v>3.832</v>
+        <v>3.833</v>
       </c>
       <c r="L110" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="M110" t="n">
-        <v>3.84</v>
+        <v>3.841</v>
       </c>
       <c r="N110" t="n">
-        <v>15.2</v>
+        <v>16.9</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
@@ -6051,7 +6031,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -6070,19 +6050,19 @@
         <v>4.3</v>
       </c>
       <c r="J111" t="n">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="K111" t="n">
-        <v>3.847</v>
+        <v>3.849</v>
       </c>
       <c r="L111" t="n">
-        <v>10.6</v>
+        <v>13.2</v>
       </c>
       <c r="M111" t="n">
-        <v>4.048</v>
+        <v>4.051</v>
       </c>
       <c r="N111" t="n">
-        <v>29.9</v>
+        <v>29.2</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
@@ -6099,7 +6079,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -6114,19 +6094,19 @@
         <v>4.8</v>
       </c>
       <c r="J112" t="n">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="K112" t="n">
-        <v>4.231</v>
+        <v>4.233</v>
       </c>
       <c r="L112" t="n">
-        <v>49.2</v>
+        <v>51.8</v>
       </c>
       <c r="M112" t="n">
-        <v>4.397</v>
+        <v>4.399</v>
       </c>
       <c r="N112" t="n">
-        <v>68</v>
+        <v>69.7</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -6143,7 +6123,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Manhattan (FiDi)</t>
+          <t>Manhattan (Financial District-Battery Park City)</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -6166,19 +6146,19 @@
         <v>4.7</v>
       </c>
       <c r="J113" t="n">
-        <v>695</v>
+        <v>761</v>
       </c>
       <c r="K113" t="n">
-        <v>4.457</v>
+        <v>4.462</v>
       </c>
       <c r="L113" t="n">
-        <v>90.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M113" t="n">
-        <v>4.587</v>
+        <v>4.592</v>
       </c>
       <c r="N113" t="n">
-        <v>88.3</v>
+        <v>89.7</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -6195,7 +6175,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -6218,19 +6198,19 @@
         <v>4.7</v>
       </c>
       <c r="J114" t="n">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="K114" t="n">
-        <v>4.281</v>
+        <v>4.285</v>
       </c>
       <c r="L114" t="n">
-        <v>61.3</v>
+        <v>63.5</v>
       </c>
       <c r="M114" t="n">
-        <v>4.351</v>
+        <v>4.355</v>
       </c>
       <c r="N114" t="n">
-        <v>62.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
@@ -6247,7 +6227,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (West Village)</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -6270,19 +6250,19 @@
         <v>4.8</v>
       </c>
       <c r="J115" t="n">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="K115" t="n">
-        <v>4.489</v>
+        <v>4.49</v>
       </c>
       <c r="L115" t="n">
-        <v>94</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M115" t="n">
-        <v>4.408</v>
+        <v>4.409</v>
       </c>
       <c r="N115" t="n">
-        <v>69.5</v>
+        <v>70.8</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -6299,7 +6279,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -6314,19 +6294,19 @@
         <v>4.9</v>
       </c>
       <c r="J116" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K116" t="n">
-        <v>4.384</v>
+        <v>4.385</v>
       </c>
       <c r="L116" t="n">
-        <v>82.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="M116" t="n">
-        <v>4.456</v>
+        <v>4.457</v>
       </c>
       <c r="N116" t="n">
-        <v>75.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -6343,7 +6323,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -6366,19 +6346,19 @@
         <v>4.6</v>
       </c>
       <c r="J117" t="n">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="K117" t="n">
-        <v>4.262</v>
+        <v>4.263</v>
       </c>
       <c r="L117" t="n">
-        <v>56.3</v>
+        <v>57.9</v>
       </c>
       <c r="M117" t="n">
-        <v>4.168</v>
+        <v>4.169</v>
       </c>
       <c r="N117" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -6395,7 +6375,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -6411,27 +6391,27 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J118" t="n">
-        <v>370</v>
+        <v>236</v>
       </c>
       <c r="K118" t="n">
-        <v>4.231</v>
+        <v>4.165</v>
       </c>
       <c r="L118" t="n">
-        <v>49.7</v>
+        <v>43.1</v>
       </c>
       <c r="M118" t="n">
-        <v>4.155</v>
+        <v>4.09</v>
       </c>
       <c r="N118" t="n">
-        <v>40.6</v>
+        <v>33.8</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Zen Sushi Omakase</t>
+          <t>Omakase Sushi by No name</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6423,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Manhattan (Lower Manhattan)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -6459,22 +6439,22 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J119" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="K119" t="n">
-        <v>4.239</v>
+        <v>4.192</v>
       </c>
       <c r="L119" t="n">
-        <v>52.8</v>
+        <v>48.7</v>
       </c>
       <c r="M119" t="n">
-        <v>4.289</v>
+        <v>4.242</v>
       </c>
       <c r="N119" t="n">
-        <v>57.4</v>
+        <v>52.3</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -6491,7 +6471,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (Murray Hill-Kips Bay)</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -6514,19 +6494,19 @@
         <v>4.2</v>
       </c>
       <c r="J120" t="n">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="K120" t="n">
         <v>3.813</v>
       </c>
       <c r="L120" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="M120" t="n">
         <v>4.013</v>
       </c>
       <c r="N120" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -6543,7 +6523,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -6562,19 +6542,19 @@
         <v>4.8</v>
       </c>
       <c r="J121" t="n">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="K121" t="n">
-        <v>4.344</v>
+        <v>4.345</v>
       </c>
       <c r="L121" t="n">
-        <v>74.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="M121" t="n">
         <v>4.522</v>
       </c>
       <c r="N121" t="n">
-        <v>81.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
@@ -6591,7 +6571,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Brooklyn (DUMBO)</t>
+          <t>Brooklyn (Downtown Brooklyn-DUMBO-Boerum Hill)</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -6616,13 +6596,13 @@
         <v>3.846</v>
       </c>
       <c r="L122" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="M122" t="n">
         <v>3.761</v>
       </c>
       <c r="N122" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
@@ -6639,7 +6619,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Brooklyn (DUMBO)</t>
+          <t>Brooklyn (Downtown Brooklyn-DUMBO-Boerum Hill)</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -6659,22 +6639,22 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J123" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="K123" t="n">
-        <v>4.123</v>
+        <v>4.088</v>
       </c>
       <c r="L123" t="n">
-        <v>37.2</v>
+        <v>32.5</v>
       </c>
       <c r="M123" t="n">
-        <v>4.145</v>
+        <v>4.109</v>
       </c>
       <c r="N123" t="n">
-        <v>39.1</v>
+        <v>34.9</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -6691,7 +6671,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Brooklyn (Park Slope)</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -6706,19 +6686,19 @@
         <v>4.9</v>
       </c>
       <c r="J124" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="K124" t="n">
-        <v>4.093</v>
+        <v>4.1</v>
       </c>
       <c r="L124" t="n">
-        <v>34.2</v>
+        <v>36</v>
       </c>
       <c r="M124" t="n">
-        <v>4.14</v>
+        <v>4.148</v>
       </c>
       <c r="N124" t="n">
-        <v>38.1</v>
+        <v>40.5</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -6735,7 +6715,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Brooklyn (Bay Ridge)</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -6750,19 +6730,19 @@
         <v>4.9</v>
       </c>
       <c r="J125" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="K125" t="n">
-        <v>4.066</v>
+        <v>4.077</v>
       </c>
       <c r="L125" t="n">
-        <v>29.6</v>
+        <v>31.5</v>
       </c>
       <c r="M125" t="n">
-        <v>4.185</v>
+        <v>4.196</v>
       </c>
       <c r="N125" t="n">
-        <v>43.7</v>
+        <v>47.2</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -6779,7 +6759,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Brooklyn (Bensonhurst)</t>
+          <t>Brooklyn (Bath Beach)</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -6802,19 +6782,19 @@
         <v>4.7</v>
       </c>
       <c r="J126" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K126" t="n">
         <v>4.268</v>
       </c>
       <c r="L126" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="M126" t="n">
-        <v>4.456</v>
+        <v>4.455</v>
       </c>
       <c r="N126" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -6831,7 +6811,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Brooklyn (Sheepshead Bay)</t>
+          <t>Brooklyn (Sheepshead Bay-Manhattan Beach-Gerritsen Beach)</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -6850,19 +6830,19 @@
         <v>4.8</v>
       </c>
       <c r="J127" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="K127" t="n">
-        <v>4.33</v>
+        <v>4.331</v>
       </c>
       <c r="L127" t="n">
-        <v>72.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M127" t="n">
-        <v>4.259</v>
+        <v>4.26</v>
       </c>
       <c r="N127" t="n">
-        <v>53.3</v>
+        <v>54.9</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -6879,7 +6859,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Brooklyn (Sunset Park (Central))</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -6894,19 +6874,19 @@
         <v>4.6</v>
       </c>
       <c r="J128" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K128" t="n">
-        <v>4.091</v>
+        <v>4.092</v>
       </c>
       <c r="L128" t="n">
-        <v>33.7</v>
+        <v>35</v>
       </c>
       <c r="M128" t="n">
-        <v>4.017</v>
+        <v>4.018</v>
       </c>
       <c r="N128" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -6923,7 +6903,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Brooklyn / Manhattan</t>
+          <t>Brooklyn (Park Slope)</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -6946,19 +6926,19 @@
         <v>4.5</v>
       </c>
       <c r="J129" t="n">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="K129" t="n">
-        <v>4.027</v>
+        <v>4.028</v>
       </c>
       <c r="L129" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="M129" t="n">
         <v>4.134</v>
       </c>
       <c r="N129" t="n">
-        <v>37.1</v>
+        <v>38.5</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -6975,7 +6955,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Brooklyn (Sunset Park (West))</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -6990,19 +6970,19 @@
         <v>4.3</v>
       </c>
       <c r="J130" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K130" t="n">
-        <v>3.685</v>
+        <v>3.686</v>
       </c>
       <c r="L130" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="M130" t="n">
-        <v>3.793</v>
+        <v>3.794</v>
       </c>
       <c r="N130" t="n">
-        <v>12.2</v>
+        <v>13.8</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -7019,7 +6999,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Brooklyn (Clinton Hill)</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -7034,19 +7014,19 @@
         <v>4.5</v>
       </c>
       <c r="J131" t="n">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="K131" t="n">
-        <v>3.769</v>
+        <v>3.77</v>
       </c>
       <c r="L131" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="M131" t="n">
-        <v>3.818</v>
+        <v>3.819</v>
       </c>
       <c r="N131" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -7063,7 +7043,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Brooklyn (Flatbush)</t>
+          <t>Brooklyn (Sheepshead Bay-Manhattan Beach-Gerritsen Beach)</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -7082,19 +7062,19 @@
         <v>4.2</v>
       </c>
       <c r="J132" t="n">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="K132" t="n">
         <v>3.851</v>
       </c>
       <c r="L132" t="n">
-        <v>11.6</v>
+        <v>14.2</v>
       </c>
       <c r="M132" t="n">
         <v>4.316</v>
       </c>
       <c r="N132" t="n">
-        <v>59.4</v>
+        <v>61.5</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
@@ -7111,7 +7091,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Brooklyn (Park Slope/Downtown)</t>
+          <t>Brooklyn (Park Slope)</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -7131,27 +7111,27 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>376</v>
+        <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>4.189</v>
+        <v>3.168</v>
       </c>
       <c r="L133" t="n">
-        <v>45.7</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>4.347</v>
+        <v>3.288</v>
       </c>
       <c r="N133" t="n">
-        <v>62.4</v>
+        <v>1</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Koi Omakase</t>
+          <t>Kimyo omakase</t>
         </is>
       </c>
     </row>
@@ -7186,19 +7166,19 @@
         <v>4.7</v>
       </c>
       <c r="J134" t="n">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="K134" t="n">
-        <v>4.378</v>
+        <v>4.379</v>
       </c>
       <c r="L134" t="n">
-        <v>81.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="M134" t="n">
         <v>4.648</v>
       </c>
       <c r="N134" t="n">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -7215,7 +7195,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Brooklyn (Flatbush)</t>
+          <t>Brooklyn (Midwood)</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -7238,19 +7218,19 @@
         <v>4.6</v>
       </c>
       <c r="J135" t="n">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="K135" t="n">
-        <v>3.837</v>
+        <v>3.838</v>
       </c>
       <c r="L135" t="n">
-        <v>9</v>
+        <v>11.7</v>
       </c>
       <c r="M135" t="n">
-        <v>4.205</v>
+        <v>4.207</v>
       </c>
       <c r="N135" t="n">
-        <v>48.2</v>
+        <v>49.2</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -7267,7 +7247,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Brooklyn (Boerum Hill)</t>
+          <t>Brooklyn (Downtown Brooklyn-DUMBO-Boerum Hill)</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -7287,22 +7267,22 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J136" t="n">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K136" t="n">
-        <v>4.081</v>
+        <v>4.053</v>
       </c>
       <c r="L136" t="n">
-        <v>31.2</v>
+        <v>28.9</v>
       </c>
       <c r="M136" t="n">
-        <v>3.932</v>
+        <v>3.905</v>
       </c>
       <c r="N136" t="n">
-        <v>23.9</v>
+        <v>22.6</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -7319,7 +7299,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Manhattan (UES/Midtown)</t>
+          <t>Manhattan (Hell's Kitchen)</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -7342,19 +7322,19 @@
         <v>4.9</v>
       </c>
       <c r="J137" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="K137" t="n">
-        <v>4.465</v>
+        <v>4.469</v>
       </c>
       <c r="L137" t="n">
-        <v>92</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="M137" t="n">
-        <v>4.596</v>
+        <v>4.599</v>
       </c>
       <c r="N137" t="n">
-        <v>88.8</v>
+        <v>90.3</v>
       </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
@@ -7371,7 +7351,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -7394,19 +7374,19 @@
         <v>4.5</v>
       </c>
       <c r="J138" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K138" t="n">
-        <v>3.746</v>
+        <v>3.748</v>
       </c>
       <c r="L138" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="M138" t="n">
-        <v>3.329</v>
+        <v>3.332</v>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -7423,7 +7403,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Manhattan (UES/Theater Dist.)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -7446,19 +7426,19 @@
         <v>4.8</v>
       </c>
       <c r="J139" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="K139" t="n">
-        <v>4.434</v>
+        <v>4.437</v>
       </c>
       <c r="L139" t="n">
-        <v>87.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="M139" t="n">
-        <v>4.361</v>
+        <v>4.364</v>
       </c>
       <c r="N139" t="n">
-        <v>64</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -7475,7 +7455,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Manhattan (Upper Manhattan)</t>
+          <t>Manhattan (Midtown South-Flatiron-Union Square)</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -7490,19 +7470,19 @@
         <v>4.6</v>
       </c>
       <c r="J140" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="K140" t="n">
-        <v>4.276</v>
+        <v>4.28</v>
       </c>
       <c r="L140" t="n">
-        <v>59.8</v>
+        <v>60.4</v>
       </c>
       <c r="M140" t="n">
-        <v>4.106</v>
+        <v>4.11</v>
       </c>
       <c r="N140" t="n">
-        <v>34</v>
+        <v>35.4</v>
       </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -7519,7 +7499,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -7542,19 +7522,19 @@
         <v>4.3</v>
       </c>
       <c r="J141" t="n">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="K141" t="n">
-        <v>3.464</v>
+        <v>3.466</v>
       </c>
       <c r="L141" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M141" t="n">
-        <v>3.542</v>
+        <v>3.544</v>
       </c>
       <c r="N141" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -7571,7 +7551,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Manhattan (Upper Manhattan)</t>
+          <t>Manhattan (Upper East Side-Carnegie Hill)</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -7594,19 +7574,19 @@
         <v>4.6</v>
       </c>
       <c r="J142" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="K142" t="n">
-        <v>4.163</v>
+        <v>4.166</v>
       </c>
       <c r="L142" t="n">
-        <v>41.7</v>
+        <v>43.7</v>
       </c>
       <c r="M142" t="n">
-        <v>4.124</v>
+        <v>4.126</v>
       </c>
       <c r="N142" t="n">
-        <v>35.5</v>
+        <v>37.4</v>
       </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -7623,7 +7603,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Manhattan (UWS/UES/East Vil.)</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -7643,27 +7623,27 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J143" t="n">
-        <v>618</v>
+        <v>117</v>
       </c>
       <c r="K143" t="n">
-        <v>4.384</v>
+        <v>4.248</v>
       </c>
       <c r="L143" t="n">
-        <v>82.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="M143" t="n">
-        <v>4.672</v>
+        <v>4.527</v>
       </c>
       <c r="N143" t="n">
-        <v>93.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Sushi W - UWS</t>
+          <t>Sushi W - East Village</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7655,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Manhattan (Upper Manhattan)</t>
+          <t>Manhattan (Upper Manhattan) (unverified)</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -7686,30 +7666,20 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
-      <c r="I144" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J144" t="n">
-        <v>74</v>
-      </c>
       <c r="K144" t="n">
-        <v>4.263</v>
+        <v>4.128</v>
       </c>
       <c r="L144" t="n">
-        <v>56.8</v>
+        <v>39.1</v>
       </c>
       <c r="M144" t="n">
-        <v>4.186</v>
+        <v>4.053</v>
       </c>
       <c r="N144" t="n">
-        <v>44.7</v>
+        <v>29.7</v>
       </c>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>YUGIN</t>
-        </is>
-      </c>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7748,13 +7718,13 @@
         <v>4.175</v>
       </c>
       <c r="L145" t="n">
-        <v>42.7</v>
+        <v>44.7</v>
       </c>
       <c r="M145" t="n">
         <v>4.326</v>
       </c>
       <c r="N145" t="n">
-        <v>60.4</v>
+        <v>62.1</v>
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -7794,19 +7764,19 @@
         <v>4.9</v>
       </c>
       <c r="J146" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="K146" t="n">
-        <v>4.463</v>
+        <v>4.465</v>
       </c>
       <c r="L146" t="n">
-        <v>91.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M146" t="n">
-        <v>4.467</v>
+        <v>4.469</v>
       </c>
       <c r="N146" t="n">
-        <v>77.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -7842,19 +7812,19 @@
         <v>4.8</v>
       </c>
       <c r="J147" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K147" t="n">
-        <v>4.413</v>
+        <v>4.414</v>
       </c>
       <c r="L147" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="M147" t="n">
-        <v>4.485</v>
+        <v>4.486</v>
       </c>
       <c r="N147" t="n">
-        <v>79.2</v>
+        <v>79.5</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -7894,19 +7864,19 @@
         <v>4.6</v>
       </c>
       <c r="J148" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="K148" t="n">
-        <v>4.281</v>
+        <v>4.282</v>
       </c>
       <c r="L148" t="n">
-        <v>61.8</v>
+        <v>61.4</v>
       </c>
       <c r="M148" t="n">
-        <v>4.351</v>
+        <v>4.352</v>
       </c>
       <c r="N148" t="n">
-        <v>63.5</v>
+        <v>63.6</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -7923,7 +7893,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Brooklyn (Crown Heights)</t>
+          <t>Brooklyn (Crown Heights (North))</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -7946,19 +7916,19 @@
         <v>4.6</v>
       </c>
       <c r="J149" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K149" t="n">
         <v>4.106</v>
       </c>
       <c r="L149" t="n">
-        <v>35.2</v>
+        <v>37.1</v>
       </c>
       <c r="M149" t="n">
         <v>4.173</v>
       </c>
       <c r="N149" t="n">
-        <v>42.6</v>
+        <v>44.6</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -7975,7 +7945,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Manhattan (UES / Lenox Hill)</t>
+          <t>Manhattan (Upper East Side-Lenox Hill-Roosevelt Island)</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -7998,19 +7968,19 @@
         <v>4.7</v>
       </c>
       <c r="J150" t="n">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="K150" t="n">
         <v>4.309</v>
       </c>
       <c r="L150" t="n">
-        <v>69.3</v>
+        <v>68.5</v>
       </c>
       <c r="M150" t="n">
-        <v>4.3</v>
+        <v>4.301</v>
       </c>
       <c r="N150" t="n">
-        <v>58.4</v>
+        <v>60</v>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -8027,7 +7997,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lower East Side</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -8050,19 +8020,19 @@
         <v>4.9</v>
       </c>
       <c r="J151" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="K151" t="n">
-        <v>4.353</v>
+        <v>4.355</v>
       </c>
       <c r="L151" t="n">
-        <v>76.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="M151" t="n">
-        <v>4.424</v>
+        <v>4.427</v>
       </c>
       <c r="N151" t="n">
-        <v>71.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -8079,7 +8049,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lower East Side</t>
+          <t>Manhattan (Chinatown-Two Bridges)</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -8102,19 +8072,19 @@
         <v>4.8</v>
       </c>
       <c r="J152" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K152" t="n">
-        <v>3.922</v>
+        <v>3.929</v>
       </c>
       <c r="L152" t="n">
-        <v>17.6</v>
+        <v>19.3</v>
       </c>
       <c r="M152" t="n">
-        <v>3.986</v>
+        <v>3.994</v>
       </c>
       <c r="N152" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -8131,7 +8101,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Queens — Long Island City</t>
+          <t>Queens (Long Island City-Hunters Point)</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -8151,22 +8121,22 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J153" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="K153" t="n">
-        <v>4.441</v>
+        <v>4.294</v>
       </c>
       <c r="L153" t="n">
-        <v>89.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="M153" t="n">
-        <v>4.407</v>
+        <v>4.261</v>
       </c>
       <c r="N153" t="n">
-        <v>69</v>
+        <v>55.4</v>
       </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -8183,7 +8153,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Brooklyn — Williamsburg</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -8203,22 +8173,22 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J154" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="K154" t="n">
-        <v>4.446</v>
+        <v>4.385</v>
       </c>
       <c r="L154" t="n">
-        <v>89.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="M154" t="n">
-        <v>4.455</v>
+        <v>4.394</v>
       </c>
       <c r="N154" t="n">
-        <v>74.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -8235,7 +8205,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Manhattan — Lower East Side</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -8255,22 +8225,22 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J155" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K155" t="n">
-        <v>4.286</v>
+        <v>4.178</v>
       </c>
       <c r="L155" t="n">
-        <v>63.8</v>
+        <v>45.7</v>
       </c>
       <c r="M155" t="n">
-        <v>4.526</v>
+        <v>4.412</v>
       </c>
       <c r="N155" t="n">
-        <v>82.2</v>
+        <v>71.3</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
@@ -8287,7 +8257,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Manhattan — Midtown East (Andaz 5th Avenue)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -8307,22 +8277,22 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J156" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="K156" t="n">
-        <v>4.259</v>
+        <v>4.345</v>
       </c>
       <c r="L156" t="n">
-        <v>55.8</v>
+        <v>77.7</v>
       </c>
       <c r="M156" t="n">
-        <v>3.664</v>
+        <v>3.738</v>
       </c>
       <c r="N156" t="n">
-        <v>9.1</v>
+        <v>10.8</v>
       </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
@@ -8339,7 +8309,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Manhattan — Tribeca</t>
+          <t>Manhattan (Tribeca-Civic Center)</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -8362,19 +8332,19 @@
         <v>4.8</v>
       </c>
       <c r="J157" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K157" t="n">
-        <v>3.987</v>
+        <v>4.033</v>
       </c>
       <c r="L157" t="n">
-        <v>22.1</v>
+        <v>26.9</v>
       </c>
       <c r="M157" t="n">
-        <v>3.579</v>
+        <v>3.619</v>
       </c>
       <c r="N157" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -8391,7 +8361,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Manhattan — Chinatown</t>
+          <t>Manhattan (Chinatown-Two Bridges)</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -8414,19 +8384,19 @@
         <v>4.9</v>
       </c>
       <c r="J158" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K158" t="n">
-        <v>4.297</v>
+        <v>4.309</v>
       </c>
       <c r="L158" t="n">
-        <v>67.8</v>
+        <v>69</v>
       </c>
       <c r="M158" t="n">
-        <v>3.85</v>
+        <v>3.861</v>
       </c>
       <c r="N158" t="n">
-        <v>18.3</v>
+        <v>21</v>
       </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -8443,7 +8413,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Manhattan — East Village</t>
+          <t>Manhattan (East Village)</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -8463,22 +8433,22 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J159" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K159" t="n">
-        <v>4.084</v>
+        <v>4.079</v>
       </c>
       <c r="L159" t="n">
-        <v>33.2</v>
+        <v>32</v>
       </c>
       <c r="M159" t="n">
-        <v>3.922</v>
+        <v>3.917</v>
       </c>
       <c r="N159" t="n">
-        <v>22.8</v>
+        <v>24.1</v>
       </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
@@ -8495,7 +8465,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Manhattan — Midtown East (Waldorf Astoria)</t>
+          <t>Manhattan (East Midtown-Turtle Bay)</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -8518,19 +8488,19 @@
         <v>4.2</v>
       </c>
       <c r="J160" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K160" t="n">
-        <v>3.299</v>
+        <v>3.344</v>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M160" t="n">
-        <v>3.097</v>
+        <v>3.14</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
@@ -8547,7 +8517,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Manhattan — Midtown East (37th floor, GM Bldg)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -8567,22 +8537,22 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J161" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K161" t="n">
-        <v>4.436</v>
+        <v>4.326</v>
       </c>
       <c r="L161" t="n">
-        <v>88.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M161" t="n">
-        <v>3.862</v>
+        <v>3.766</v>
       </c>
       <c r="N161" t="n">
-        <v>20.3</v>
+        <v>12.8</v>
       </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
@@ -8599,7 +8569,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Manhattan — Lower East Side</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -8628,13 +8598,13 @@
         <v>3.866</v>
       </c>
       <c r="L162" t="n">
-        <v>14.6</v>
+        <v>16.2</v>
       </c>
       <c r="M162" t="n">
         <v>3.573</v>
       </c>
       <c r="N162" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -8651,7 +8621,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Brooklyn — Williamsburg</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -8674,19 +8644,19 @@
         <v>4.7</v>
       </c>
       <c r="J163" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K163" t="n">
-        <v>4.178</v>
+        <v>4.181</v>
       </c>
       <c r="L163" t="n">
-        <v>43.2</v>
+        <v>46.7</v>
       </c>
       <c r="M163" t="n">
-        <v>3.908</v>
+        <v>3.911</v>
       </c>
       <c r="N163" t="n">
-        <v>22.3</v>
+        <v>23.6</v>
       </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
@@ -8703,7 +8673,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Brooklyn — Williamsburg</t>
+          <t>Brooklyn (Williamsburg)</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -8732,13 +8702,13 @@
         <v>4.414</v>
       </c>
       <c r="L164" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="M164" t="n">
         <v>4.393</v>
       </c>
       <c r="N164" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -8755,7 +8725,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Manhattan — Upper East Side (Carnegie Hill)</t>
+          <t>Manhattan (Upper East Side-Carnegie Hill)</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -8778,19 +8748,19 @@
         <v>4.8</v>
       </c>
       <c r="J165" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K165" t="n">
-        <v>4.283</v>
+        <v>4.331</v>
       </c>
       <c r="L165" t="n">
-        <v>63.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M165" t="n">
-        <v>4.127</v>
+        <v>4.173</v>
       </c>
       <c r="N165" t="n">
-        <v>36.5</v>
+        <v>44.1</v>
       </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
@@ -8807,7 +8777,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Brooklyn — Fort Greene</t>
+          <t>Brooklyn (Fort Greene)</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -8830,19 +8800,19 @@
         <v>4.8</v>
       </c>
       <c r="J166" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K166" t="n">
-        <v>4.337</v>
+        <v>4.34</v>
       </c>
       <c r="L166" t="n">
-        <v>74.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M166" t="n">
-        <v>4.126</v>
+        <v>4.128</v>
       </c>
       <c r="N166" t="n">
-        <v>36</v>
+        <v>37.9</v>
       </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -8859,7 +8829,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Manhattan — Tribeca</t>
+          <t>Manhattan (Tribeca-Civic Center)</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -8888,13 +8858,13 @@
         <v>3.966</v>
       </c>
       <c r="L167" t="n">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="M167" t="n">
         <v>3.432</v>
       </c>
       <c r="N167" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -8911,7 +8881,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Manhattan — Upper East Side</t>
+          <t>Manhattan (Upper East Side-Lenox Hill-Roosevelt Island)</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -8934,19 +8904,19 @@
         <v>4.7</v>
       </c>
       <c r="J168" t="n">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K168" t="n">
-        <v>4.331</v>
+        <v>4.332</v>
       </c>
       <c r="L168" t="n">
-        <v>72.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M168" t="n">
-        <v>4.203</v>
+        <v>4.204</v>
       </c>
       <c r="N168" t="n">
-        <v>46.7</v>
+        <v>48.2</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
@@ -8963,7 +8933,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Manhattan — Chinatown</t>
+          <t>Manhattan (Chinatown-Two Bridges)</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -8986,19 +8956,19 @@
         <v>4.4</v>
       </c>
       <c r="J169" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K169" t="n">
         <v>4.021</v>
       </c>
       <c r="L169" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="M169" t="n">
         <v>3.533</v>
       </c>
       <c r="N169" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -9015,7 +8985,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Manhattan — Tribeca</t>
+          <t>Manhattan (Tribeca-Civic Center)</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -9038,19 +9008,19 @@
         <v>4.5</v>
       </c>
       <c r="J170" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K170" t="n">
         <v>4.271</v>
       </c>
       <c r="L170" t="n">
-        <v>58.8</v>
+        <v>58.9</v>
       </c>
       <c r="M170" t="n">
         <v>3.651</v>
       </c>
       <c r="N170" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
@@ -9067,7 +9037,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Manhattan — Union Square</t>
+          <t>Manhattan (Greenwich Village)</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -9096,13 +9066,13 @@
         <v>4.252</v>
       </c>
       <c r="L171" t="n">
-        <v>54.3</v>
+        <v>55.8</v>
       </c>
       <c r="M171" t="n">
         <v>3.85</v>
       </c>
       <c r="N171" t="n">
-        <v>17.8</v>
+        <v>19</v>
       </c>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -9119,7 +9089,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Manhattan — Midtown East</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -9142,19 +9112,19 @@
         <v>4.4</v>
       </c>
       <c r="J172" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K172" t="n">
-        <v>4.02</v>
+        <v>4.022</v>
       </c>
       <c r="L172" t="n">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="M172" t="n">
-        <v>3.602</v>
+        <v>3.603</v>
       </c>
       <c r="N172" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
@@ -9171,7 +9141,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Manhattan — Tribeca</t>
+          <t>Manhattan (Tribeca-Civic Center)</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -9194,19 +9164,19 @@
         <v>4.5</v>
       </c>
       <c r="J173" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K173" t="n">
-        <v>4.083</v>
+        <v>4.089</v>
       </c>
       <c r="L173" t="n">
-        <v>32.7</v>
+        <v>33.5</v>
       </c>
       <c r="M173" t="n">
-        <v>3.555</v>
+        <v>3.56</v>
       </c>
       <c r="N173" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
@@ -9223,7 +9193,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Manhattan — Columbus Circle</t>
+          <t>Manhattan — Columbus Circle (unverified)</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -9242,30 +9212,8 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
-      <c r="I174" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J174" t="n">
-        <v>582</v>
-      </c>
-      <c r="K174" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="L174" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M174" t="n">
-        <v>3.138</v>
-      </c>
-      <c r="N174" t="n">
-        <v>0.5</v>
-      </c>
       <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>Bar Masa</t>
-        </is>
-      </c>
+      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9275,7 +9223,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Manhattan — Columbus Circle</t>
+          <t>Manhattan (Upper West Side-Lincoln Square)</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -9298,19 +9246,19 @@
         <v>4.2</v>
       </c>
       <c r="J175" t="n">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="K175" t="n">
-        <v>3.93</v>
+        <v>3.931</v>
       </c>
       <c r="L175" t="n">
-        <v>18.8</v>
+        <v>19.8</v>
       </c>
       <c r="M175" t="n">
-        <v>3.533</v>
+        <v>3.534</v>
       </c>
       <c r="N175" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
@@ -9327,7 +9275,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Manhattan — Upper East Side</t>
+          <t>Manhattan (Upper East Side-Carnegie Hill)</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -9350,19 +9298,19 @@
         <v>4.2</v>
       </c>
       <c r="J176" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K176" t="n">
-        <v>3.845</v>
+        <v>3.848</v>
       </c>
       <c r="L176" t="n">
-        <v>9.5</v>
+        <v>12.7</v>
       </c>
       <c r="M176" t="n">
-        <v>3.445</v>
+        <v>3.447</v>
       </c>
       <c r="N176" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
@@ -9379,7 +9327,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Manhattan — Midtown</t>
+          <t>Manhattan (Hell's Kitchen)</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -9399,27 +9347,27 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J177" t="n">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="K177" t="n">
-        <v>3.897</v>
+        <v>3.264</v>
       </c>
       <c r="L177" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="M177" t="n">
-        <v>3.636</v>
+        <v>3.045</v>
       </c>
       <c r="N177" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Togyushi</t>
+          <t>Sushi Yoshi Time Square</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9379,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Queens — Flushing</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -9451,22 +9399,22 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J178" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K178" t="n">
-        <v>4.264</v>
+        <v>4.175</v>
       </c>
       <c r="L178" t="n">
-        <v>57.5</v>
+        <v>45.2</v>
       </c>
       <c r="M178" t="n">
-        <v>4.227</v>
+        <v>4.139</v>
       </c>
       <c r="N178" t="n">
-        <v>49.7</v>
+        <v>39</v>
       </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
@@ -9483,7 +9431,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Queens — Flushing</t>
+          <t>Queens (Murray Hill-Broadway Flushing)</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -9512,13 +9460,13 @@
         <v>3.906</v>
       </c>
       <c r="L179" t="n">
-        <v>17.1</v>
+        <v>18.8</v>
       </c>
       <c r="M179" t="n">
         <v>3.751</v>
       </c>
       <c r="N179" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
@@ -9535,7 +9483,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Queens — Flushing</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -9558,19 +9506,19 @@
         <v>4.4</v>
       </c>
       <c r="J180" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K180" t="n">
-        <v>3.973</v>
+        <v>3.976</v>
       </c>
       <c r="L180" t="n">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="M180" t="n">
-        <v>3.828</v>
+        <v>3.831</v>
       </c>
       <c r="N180" t="n">
-        <v>14.7</v>
+        <v>16.4</v>
       </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -9587,7 +9535,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Queens — Flushing</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -9610,19 +9558,19 @@
         <v>4.6</v>
       </c>
       <c r="J181" t="n">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="K181" t="n">
-        <v>4.363</v>
+        <v>4.365</v>
       </c>
       <c r="L181" t="n">
-        <v>79.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="M181" t="n">
-        <v>4.631</v>
+        <v>4.633</v>
       </c>
       <c r="N181" t="n">
-        <v>91.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -9639,7 +9587,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Queens — Flushing</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -9662,19 +9610,19 @@
         <v>4.6</v>
       </c>
       <c r="J182" t="n">
-        <v>2093</v>
+        <v>2174</v>
       </c>
       <c r="K182" t="n">
-        <v>4.295</v>
+        <v>4.296</v>
       </c>
       <c r="L182" t="n">
-        <v>66.8</v>
+        <v>66.5</v>
       </c>
       <c r="M182" t="n">
-        <v>4.392</v>
+        <v>4.393</v>
       </c>
       <c r="N182" t="n">
-        <v>67</v>
+        <v>68.2</v>
       </c>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -9691,7 +9639,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Queens — Flushing</t>
+          <t>Queens — Flushing (unverified)</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -9710,30 +9658,8 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
-      <c r="I183" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J183" t="n">
-        <v>106</v>
-      </c>
-      <c r="K183" t="n">
-        <v>4.264</v>
-      </c>
-      <c r="L183" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="M183" t="n">
-        <v>4.273</v>
-      </c>
-      <c r="N183" t="n">
-        <v>55.3</v>
-      </c>
       <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>Omi Omakase</t>
-        </is>
-      </c>
+      <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9743,7 +9669,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Queens — Long Island City</t>
+          <t>Queens (Long Island City-Hunters Point)</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -9766,19 +9692,19 @@
         <v>4.7</v>
       </c>
       <c r="J184" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="K184" t="n">
-        <v>4.353</v>
+        <v>4.356</v>
       </c>
       <c r="L184" t="n">
-        <v>77.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="M184" t="n">
-        <v>4.241</v>
+        <v>4.243</v>
       </c>
       <c r="N184" t="n">
-        <v>51.3</v>
+        <v>52.8</v>
       </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
@@ -9795,7 +9721,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Queens — Long Island City</t>
+          <t>Queens (Sunnyside)</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -9815,27 +9741,27 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J185" t="n">
-        <v>83</v>
+        <v>159</v>
       </c>
       <c r="K185" t="n">
-        <v>4.218</v>
+        <v>4.44</v>
       </c>
       <c r="L185" t="n">
-        <v>47.7</v>
+        <v>89.3</v>
       </c>
       <c r="M185" t="n">
-        <v>3.977</v>
+        <v>4.187</v>
       </c>
       <c r="N185" t="n">
-        <v>25.4</v>
+        <v>45.6</v>
       </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Omakase OSUKAA LIC</t>
+          <t>Omakase OSUKAA</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9773,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Queens — Long Island City</t>
+          <t>Queens (Long Island City-Hunters Point)</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -9870,16 +9796,16 @@
         <v>4.5</v>
       </c>
       <c r="J186" t="n">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="K186" t="n">
         <v>4.149</v>
       </c>
       <c r="L186" t="n">
-        <v>39.7</v>
+        <v>41.6</v>
       </c>
       <c r="M186" t="n">
-        <v>4.679</v>
+        <v>4.68</v>
       </c>
       <c r="N186" t="n">
         <v>94.40000000000001</v>
@@ -9899,7 +9825,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Queens — Long Island City</t>
+          <t>Queens (Long Island City-Hunters Point)</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -9922,19 +9848,19 @@
         <v>4.5</v>
       </c>
       <c r="J187" t="n">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="K187" t="n">
-        <v>4.238</v>
+        <v>4.24</v>
       </c>
       <c r="L187" t="n">
-        <v>51.3</v>
+        <v>53.3</v>
       </c>
       <c r="M187" t="n">
-        <v>4.561</v>
+        <v>4.563</v>
       </c>
       <c r="N187" t="n">
-        <v>85.3</v>
+        <v>86.7</v>
       </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
@@ -9951,7 +9877,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Brooklyn — Bushwick</t>
+          <t>Brooklyn (East Williamsburg)</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -9974,19 +9900,19 @@
         <v>4.4</v>
       </c>
       <c r="J188" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="K188" t="n">
-        <v>4.116</v>
+        <v>4.117</v>
       </c>
       <c r="L188" t="n">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="M188" t="n">
-        <v>4.332</v>
+        <v>4.333</v>
       </c>
       <c r="N188" t="n">
-        <v>60.9</v>
+        <v>63.1</v>
       </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
@@ -10003,7 +9929,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Jersey City, NJ</t>
+          <t>Jersey City, NJ (unverified)</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -10026,19 +9952,19 @@
         <v>4.5</v>
       </c>
       <c r="J189" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K189" t="n">
-        <v>3.865</v>
+        <v>3.887</v>
       </c>
       <c r="L189" t="n">
-        <v>14.1</v>
+        <v>16.8</v>
       </c>
       <c r="M189" t="n">
-        <v>3.737</v>
+        <v>3.758</v>
       </c>
       <c r="N189" t="n">
-        <v>10.7</v>
+        <v>11.8</v>
       </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
@@ -10055,7 +9981,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -10078,19 +10004,19 @@
         <v>4.6</v>
       </c>
       <c r="J190" t="n">
-        <v>1686</v>
+        <v>1724</v>
       </c>
       <c r="K190" t="n">
         <v>4.394</v>
       </c>
       <c r="L190" t="n">
-        <v>84.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="M190" t="n">
-        <v>4.566</v>
+        <v>4.567</v>
       </c>
       <c r="N190" t="n">
-        <v>86.3</v>
+        <v>87.7</v>
       </c>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -10107,7 +10033,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown/Koreatown)</t>
+          <t>Manhattan (Midtown-Times Square)</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -10127,22 +10053,22 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J191" t="n">
-        <v>2965</v>
+        <v>3026</v>
       </c>
       <c r="K191" t="n">
-        <v>4.716</v>
+        <v>4.614</v>
       </c>
       <c r="L191" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M191" t="n">
-        <v>4.635</v>
+        <v>4.534</v>
       </c>
       <c r="N191" t="n">
-        <v>92.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -10159,7 +10085,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -10179,22 +10105,22 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J192" t="n">
-        <v>1147</v>
+        <v>1163</v>
       </c>
       <c r="K192" t="n">
-        <v>4.481</v>
+        <v>4.379</v>
       </c>
       <c r="L192" t="n">
-        <v>92.7</v>
+        <v>82.2</v>
       </c>
       <c r="M192" t="n">
-        <v>4.854</v>
+        <v>4.743</v>
       </c>
       <c r="N192" t="n">
-        <v>98.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
@@ -10211,7 +10137,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Manhattan (Midtown East)</t>
+          <t>Manhattan (East Midtown-Turtle Bay)</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -10234,19 +10160,19 @@
         <v>4.7</v>
       </c>
       <c r="J193" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="K193" t="n">
-        <v>4.409</v>
+        <v>4.41</v>
       </c>
       <c r="L193" t="n">
-        <v>85.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="M193" t="n">
-        <v>4.583</v>
+        <v>4.584</v>
       </c>
       <c r="N193" t="n">
-        <v>87.8</v>
+        <v>89.2</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
@@ -10263,7 +10189,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Manhattan (SoHo)</t>
+          <t>Manhattan (SoHo-Little Italy-Hudson Square)</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -10286,16 +10212,16 @@
         <v>4.9</v>
       </c>
       <c r="J194" t="n">
-        <v>2382</v>
+        <v>2841</v>
       </c>
       <c r="K194" t="n">
-        <v>4.711</v>
+        <v>4.715</v>
       </c>
       <c r="L194" t="n">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="M194" t="n">
-        <v>4.975</v>
+        <v>4.979</v>
       </c>
       <c r="N194" t="n">
         <v>100</v>
@@ -10315,7 +10241,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -10338,19 +10264,19 @@
         <v>4.5</v>
       </c>
       <c r="J195" t="n">
-        <v>1559</v>
+        <v>1635</v>
       </c>
       <c r="K195" t="n">
-        <v>4.289</v>
+        <v>4.291</v>
       </c>
       <c r="L195" t="n">
-        <v>65.3</v>
+        <v>64.5</v>
       </c>
       <c r="M195" t="n">
-        <v>4.606</v>
+        <v>4.608</v>
       </c>
       <c r="N195" t="n">
-        <v>89.3</v>
+        <v>90.8</v>
       </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
@@ -10367,7 +10293,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -10387,27 +10313,27 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J196" t="n">
-        <v>1147</v>
+        <v>408</v>
       </c>
       <c r="K196" t="n">
-        <v>4.481</v>
+        <v>4.316</v>
       </c>
       <c r="L196" t="n">
-        <v>92.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="M196" t="n">
-        <v>4.657</v>
+        <v>4.486</v>
       </c>
       <c r="N196" t="n">
-        <v>93.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Mikiya Wagyu Shabu House 味喜屋 | Flushing</t>
+          <t>Wagyu Yama Yakiniku &amp; Seafood Shabu 牛帮主和牛烤肉海鲜火锅自助</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10345,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Manhattan (Lower East Side/Chinatown)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -10439,27 +10365,27 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J197" t="n">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="K197" t="n">
-        <v>4.367</v>
+        <v>3.686</v>
       </c>
       <c r="L197" t="n">
-        <v>80.90000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="M197" t="n">
-        <v>4.942</v>
+        <v>4.171</v>
       </c>
       <c r="N197" t="n">
-        <v>99.5</v>
+        <v>43.3</v>
       </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Genki east omakase</t>
+          <t>Gyu-Ichiro Japanese BBQ</t>
         </is>
       </c>
     </row>
@@ -10500,13 +10426,13 @@
         <v>3.904</v>
       </c>
       <c r="L198" t="n">
-        <v>16.6</v>
+        <v>18.3</v>
       </c>
       <c r="M198" t="n">
         <v>4.201</v>
       </c>
       <c r="N198" t="n">
-        <v>46.2</v>
+        <v>47.7</v>
       </c>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
@@ -10523,7 +10449,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Manhattan (Lower East Side/Chinatown)</t>
+          <t>Manhattan (Lower East Side)</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -10546,19 +10472,19 @@
         <v>4</v>
       </c>
       <c r="J199" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="K199" t="n">
-        <v>3.684</v>
+        <v>3.686</v>
       </c>
       <c r="L199" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="M199" t="n">
-        <v>4.169</v>
+        <v>4.171</v>
       </c>
       <c r="N199" t="n">
-        <v>41.6</v>
+        <v>43.3</v>
       </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
@@ -10575,7 +10501,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Queens (Flushing)</t>
+          <t>Queens (Flushing-Willets Point)</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -10595,27 +10521,27 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J200" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="K200" t="n">
-        <v>3.351</v>
+        <v>3.447</v>
       </c>
       <c r="L200" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M200" t="n">
-        <v>3.558</v>
+        <v>3.66</v>
       </c>
       <c r="N200" t="n">
-        <v>6.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Nikushou Sakai 肉匠坂井</t>
+          <t>Nikushou Sakai</t>
         </is>
       </c>
     </row>
@@ -10627,7 +10553,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Queens (Long Island City)</t>
+          <t>Queens (Long Island City-Hunters Point)</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -10650,19 +10576,19 @@
         <v>4.7</v>
       </c>
       <c r="J201" t="n">
-        <v>482</v>
+        <v>584</v>
       </c>
       <c r="K201" t="n">
-        <v>4.435</v>
+        <v>4.447</v>
       </c>
       <c r="L201" t="n">
-        <v>88.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="M201" t="n">
-        <v>4.86</v>
+        <v>4.874</v>
       </c>
       <c r="N201" t="n">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
@@ -10679,7 +10605,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manhattan (Chelsea)</t>
+          <t>Manhattan (Chelsea-Hudson Yards)</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -10702,19 +10628,19 @@
         <v>4.4</v>
       </c>
       <c r="J202" t="n">
-        <v>1436</v>
+        <v>1449</v>
       </c>
       <c r="K202" t="n">
         <v>4.185</v>
       </c>
       <c r="L202" t="n">
-        <v>45.2</v>
+        <v>47.7</v>
       </c>
       <c r="M202" t="n">
         <v>4.72</v>
       </c>
       <c r="N202" t="n">
-        <v>95.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
